--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\SEC\ratio.alpha.beta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -998,10 +998,10 @@
         <v>54</v>
       </c>
       <c r="D2">
-        <v>0.41842844126741657</v>
+        <v>0.41842843519780271</v>
       </c>
       <c r="E2">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1010,139 +1010,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H2">
-        <v>0.48972842429048552</v>
+        <v>0.4897284227825181</v>
       </c>
       <c r="I2">
-        <v>8.1388151075341142E-3</v>
+        <v>8.1388163788437273E-3</v>
       </c>
       <c r="J2">
-        <v>-3.4797002392697153E-2</v>
+        <v>-3.4796998232330907E-2</v>
       </c>
       <c r="K2">
-        <v>0.49421525964178731</v>
+        <v>0.49421526559359519</v>
       </c>
       <c r="L2">
-        <v>3.2806615936056049E-2</v>
+        <v>3.2806619165155038E-2</v>
       </c>
       <c r="M2">
-        <v>-5.3852362548961433E-2</v>
+        <v>-5.3852390280210362E-2</v>
       </c>
       <c r="N2">
-        <v>0.4956173537110643</v>
+        <v>0.49561735452763339</v>
       </c>
       <c r="O2">
-        <v>6.1661639759884812E-2</v>
+        <v>6.1661644286354789E-2</v>
       </c>
       <c r="P2">
-        <v>-5.9897405745343912E-2</v>
+        <v>-5.9897411669500307E-2</v>
       </c>
       <c r="Q2">
-        <v>0.49594335816417551</v>
+        <v>0.4959433555707316</v>
       </c>
       <c r="R2">
-        <v>9.6114302564908716E-2</v>
+        <v>9.6114306285505102E-2</v>
       </c>
       <c r="S2">
-        <v>-6.1285748729154002E-2</v>
+        <v>-6.1285739897219922E-2</v>
       </c>
       <c r="T2">
-        <v>0.49578859301752409</v>
+        <v>0.49578858986449847</v>
       </c>
       <c r="U2">
-        <v>0.127673390178658</v>
+        <v>0.1276733969380234</v>
       </c>
       <c r="V2">
-        <v>-6.0727227790227677E-2</v>
+        <v>-6.072721653017786E-2</v>
       </c>
       <c r="W2">
-        <v>0.49612088007914962</v>
+        <v>0.49612087737154159</v>
       </c>
       <c r="X2">
-        <v>0.20902971946915941</v>
+        <v>0.2090297286911528</v>
       </c>
       <c r="Y2">
-        <v>-6.2178301385081472E-2</v>
+        <v>-6.2178292070992729E-2</v>
       </c>
       <c r="Z2">
-        <v>0.48060378253189467</v>
+        <v>0.48060377976172758</v>
       </c>
       <c r="AA2">
-        <v>0.2450600611652051</v>
+        <v>0.24506007094596899</v>
       </c>
       <c r="AB2">
-        <v>3.2733503322159231E-3</v>
+        <v>3.2733596639955599E-3</v>
       </c>
       <c r="AC2">
-        <v>0.4586448263593072</v>
+        <v>0.45864482352981212</v>
       </c>
       <c r="AD2">
-        <v>0.34576785841791341</v>
+        <v>0.34576786453572578</v>
       </c>
       <c r="AE2">
-        <v>9.2123928561410856E-2</v>
+        <v>9.2123937817835899E-2</v>
       </c>
       <c r="AF2">
-        <v>0.46947524655997558</v>
+        <v>0.4694752427706374</v>
       </c>
       <c r="AG2">
-        <v>0.39549154369632589</v>
+        <v>0.39549154870625208</v>
       </c>
       <c r="AH2">
-        <v>4.8668925423998109E-2</v>
+        <v>4.8668938706028141E-2</v>
       </c>
       <c r="AI2">
-        <v>0.45722070470630122</v>
+        <v>0.45722070209966492</v>
       </c>
       <c r="AJ2">
-        <v>0.44413685074235087</v>
+        <v>0.44413685744454329</v>
       </c>
       <c r="AK2">
-        <v>9.7722210924029565E-2</v>
+        <v>9.7722219312003089E-2</v>
       </c>
       <c r="AL2">
-        <v>0.43452404954275958</v>
+        <v>0.43452404846843418</v>
       </c>
       <c r="AM2">
-        <v>0.56812731858468113</v>
+        <v>0.5681273283191447</v>
       </c>
       <c r="AN2">
-        <v>0.1849994568601051</v>
+        <v>0.18499945935423451</v>
       </c>
       <c r="AO2">
-        <v>0.4247318496996772</v>
+        <v>0.42473184523476909</v>
       </c>
       <c r="AP2">
-        <v>0.61670079220603347</v>
+        <v>0.61670080293410101</v>
       </c>
       <c r="AQ2">
-        <v>0.2213144588893225</v>
+        <v>0.2213144735208008</v>
       </c>
       <c r="AR2">
-        <v>0.40144362173557491</v>
+        <v>0.40144361505987303</v>
       </c>
       <c r="AS2">
-        <v>0.70726489151670235</v>
+        <v>0.70726490733068514</v>
       </c>
       <c r="AT2">
-        <v>0.3042350444268288</v>
+        <v>0.30423506605844658</v>
       </c>
       <c r="AU2">
-        <v>0.37787961633011091</v>
+        <v>0.37787960626080641</v>
       </c>
       <c r="AV2">
-        <v>0.78160205775592784</v>
+        <v>0.78160207281388816</v>
       </c>
       <c r="AW2">
-        <v>0.38351382896663039</v>
+        <v>0.38351386044565072</v>
       </c>
       <c r="AX2">
-        <v>0.36580497996368488</v>
+        <v>0.36580496695833542</v>
       </c>
       <c r="AY2">
-        <v>0.79854235545515861</v>
+        <v>0.79854236965689251</v>
       </c>
       <c r="AZ2">
-        <v>0.42237281923662878</v>
+        <v>0.42237285900884552</v>
       </c>
     </row>
     <row r="3" spans="1:52" x14ac:dyDescent="0.25">
@@ -1156,10 +1156,10 @@
         <v>54</v>
       </c>
       <c r="D3">
-        <v>0.4371841300768296</v>
+        <v>0.43718412788660332</v>
       </c>
       <c r="E3">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1168,139 +1168,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H3">
-        <v>0.48693007513739578</v>
+        <v>0.48693007459908128</v>
       </c>
       <c r="I3">
-        <v>4.1377617245736409E-2</v>
+        <v>4.1377617493537522E-2</v>
       </c>
       <c r="J3">
-        <v>-2.297019530262016E-2</v>
+        <v>-2.2970195240494741E-2</v>
       </c>
       <c r="K3">
-        <v>0.49234430812624719</v>
+        <v>0.49234430637081888</v>
       </c>
       <c r="L3">
-        <v>6.4926307865311172E-2</v>
+        <v>6.4926305829590913E-2</v>
       </c>
       <c r="M3">
-        <v>-4.5968467411213298E-2</v>
+        <v>-4.5968462150039691E-2</v>
       </c>
       <c r="N3">
-        <v>0.52209718826700713</v>
+        <v>0.52209719079758776</v>
       </c>
       <c r="O3">
-        <v>0.34718121984884098</v>
+        <v>0.34718121943141628</v>
       </c>
       <c r="P3">
-        <v>-0.17678579464570121</v>
+        <v>-0.17678580847881059</v>
       </c>
       <c r="Q3">
-        <v>0.47808825727616638</v>
+        <v>0.47808826048960529</v>
       </c>
       <c r="R3">
-        <v>0.38763772730841761</v>
+        <v>0.38763776386753501</v>
       </c>
       <c r="S3">
-        <v>1.327218200258222E-2</v>
+        <v>1.3272166458149741E-2</v>
       </c>
       <c r="T3">
-        <v>0.45627951564534258</v>
+        <v>0.45627951591012772</v>
       </c>
       <c r="U3">
-        <v>0.47201570472323601</v>
+        <v>0.47201571957041388</v>
       </c>
       <c r="V3">
-        <v>0.10109382899849589</v>
+        <v>0.10109382631293951</v>
       </c>
       <c r="W3">
-        <v>0.43841114400527947</v>
+        <v>0.43841114436114348</v>
       </c>
       <c r="X3">
-        <v>0.50850232147874541</v>
+        <v>0.50850231969230264</v>
       </c>
       <c r="Y3">
-        <v>0.17035300497168901</v>
+        <v>0.17035300215570209</v>
       </c>
       <c r="Z3">
-        <v>0.42434008656274602</v>
+        <v>0.424340103020792</v>
       </c>
       <c r="AA3">
-        <v>0.59964080044588686</v>
+        <v>0.59964079137868165</v>
       </c>
       <c r="AB3">
-        <v>0.22259255523281901</v>
+        <v>0.22259249349513011</v>
       </c>
       <c r="AC3">
-        <v>0.41992371786066629</v>
+        <v>0.41992372344314549</v>
       </c>
       <c r="AD3">
-        <v>0.65978723358079505</v>
+        <v>0.65978722709480087</v>
       </c>
       <c r="AE3">
-        <v>0.23866441819276701</v>
+        <v>0.23866439624510369</v>
       </c>
       <c r="AF3">
-        <v>0.40261697582974082</v>
+        <v>0.40261697622508841</v>
       </c>
       <c r="AG3">
-        <v>0.70191265135342995</v>
+        <v>0.70191265360836241</v>
       </c>
       <c r="AH3">
-        <v>0.30015143523084759</v>
+        <v>0.30015143233162561</v>
       </c>
       <c r="AI3">
-        <v>0.38976389180599308</v>
+        <v>0.389763887669274</v>
       </c>
       <c r="AJ3">
-        <v>0.74351811449912808</v>
+        <v>0.74351812196027356</v>
       </c>
       <c r="AK3">
-        <v>0.34401284560681411</v>
+        <v>0.34401285799256842</v>
       </c>
       <c r="AL3">
-        <v>0.39080430403228661</v>
+        <v>0.39080429339816408</v>
       </c>
       <c r="AM3">
-        <v>0.7659309557772922</v>
+        <v>0.76593096997832888</v>
       </c>
       <c r="AN3">
-        <v>0.34039027330502369</v>
+        <v>0.3403903072319221</v>
       </c>
       <c r="AO3">
-        <v>0.38896976020995699</v>
+        <v>0.38896973717715472</v>
       </c>
       <c r="AP3">
-        <v>0.80023261199546081</v>
+        <v>0.80023264557557561</v>
       </c>
       <c r="AQ3">
-        <v>0.34642699295282792</v>
+        <v>0.34642706827060799</v>
       </c>
       <c r="AR3">
-        <v>0.39851132582487903</v>
+        <v>0.39851128298908473</v>
       </c>
       <c r="AS3">
-        <v>0.8345596377482658</v>
+        <v>0.83455968695890848</v>
       </c>
       <c r="AT3">
-        <v>0.31375452773715001</v>
+        <v>0.31375467362049608</v>
       </c>
       <c r="AU3">
-        <v>0.40002804347199222</v>
+        <v>0.40002797364298393</v>
       </c>
       <c r="AV3">
-        <v>0.87279020962334297</v>
+        <v>0.87279027907273221</v>
       </c>
       <c r="AW3">
-        <v>0.30866869115975087</v>
+        <v>0.3086689304342054</v>
       </c>
       <c r="AX3">
-        <v>0.39124743013102831</v>
+        <v>0.39124733793749589</v>
       </c>
       <c r="AY3">
-        <v>0.89086784317436518</v>
+        <v>0.89086790919165515</v>
       </c>
       <c r="AZ3">
-        <v>0.3385053742875852</v>
+        <v>0.33850568411028747</v>
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
@@ -1314,10 +1314,10 @@
         <v>54</v>
       </c>
       <c r="D4">
-        <v>0.4265484658251012</v>
+        <v>0.42654845838422673</v>
       </c>
       <c r="E4">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1326,139 +1326,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H4">
-        <v>0.4887279150808983</v>
+        <v>0.48872791390536119</v>
       </c>
       <c r="I4">
-        <v>7.8365970407457963E-3</v>
+        <v>7.8365981833309339E-3</v>
       </c>
       <c r="J4">
-        <v>-3.0529963701704431E-2</v>
+        <v>-3.052996094336425E-2</v>
       </c>
       <c r="K4">
-        <v>0.49245718756941748</v>
+        <v>0.49245716951728991</v>
       </c>
       <c r="L4">
-        <v>1.9697632050808659E-2</v>
+        <v>1.9697633141909421E-2</v>
       </c>
       <c r="M4">
-        <v>-4.633740859492419E-2</v>
+        <v>-4.6337332411850951E-2</v>
       </c>
       <c r="N4">
-        <v>0.51222723010393378</v>
+        <v>0.51222722819603927</v>
       </c>
       <c r="O4">
-        <v>4.7965677429577913E-2</v>
+        <v>4.7965675571166037E-2</v>
       </c>
       <c r="P4">
-        <v>-0.13210348132686009</v>
+        <v>-0.13210347531939279</v>
       </c>
       <c r="Q4">
-        <v>0.5127307783848063</v>
+        <v>0.51273077327719374</v>
       </c>
       <c r="R4">
-        <v>6.2446277744168673E-2</v>
+        <v>6.2446269751799899E-2</v>
       </c>
       <c r="S4">
-        <v>-0.13446472951722441</v>
+        <v>-0.1344647094910989</v>
       </c>
       <c r="T4">
-        <v>0.52836909810507371</v>
+        <v>0.52836909826535816</v>
       </c>
       <c r="U4">
-        <v>0.16793818783702491</v>
+        <v>0.16793819638982241</v>
       </c>
       <c r="V4">
-        <v>-0.20493173416039301</v>
+        <v>-0.20493173740932669</v>
       </c>
       <c r="W4">
-        <v>0.49587054899704591</v>
+        <v>0.49587054013581161</v>
       </c>
       <c r="X4">
-        <v>0.27500888109857358</v>
+        <v>0.27500889185804339</v>
       </c>
       <c r="Y4">
-        <v>-6.1143796807262507E-2</v>
+        <v>-6.114376160883616E-2</v>
       </c>
       <c r="Z4">
-        <v>0.45939021333486307</v>
+        <v>0.45939020420055299</v>
       </c>
       <c r="AA4">
-        <v>0.40478725511240099</v>
+        <v>0.40478726435012458</v>
       </c>
       <c r="AB4">
-        <v>8.9102429296634783E-2</v>
+        <v>8.9102463486679315E-2</v>
       </c>
       <c r="AC4">
-        <v>0.45342733203679259</v>
+        <v>0.45342732604304792</v>
       </c>
       <c r="AD4">
-        <v>0.47222916316218388</v>
+        <v>0.47222916307235219</v>
       </c>
       <c r="AE4">
-        <v>0.1124041020806935</v>
+        <v>0.1124041236715061</v>
       </c>
       <c r="AF4">
-        <v>0.44936805043665429</v>
+        <v>0.44936804338276382</v>
       </c>
       <c r="AG4">
-        <v>0.49316894605713169</v>
+        <v>0.49316895534525268</v>
       </c>
       <c r="AH4">
-        <v>0.12817378062137019</v>
+        <v>0.12817380604206219</v>
       </c>
       <c r="AI4">
-        <v>0.4292430554837196</v>
+        <v>0.42924304852288941</v>
       </c>
       <c r="AJ4">
-        <v>0.59111802228956756</v>
+        <v>0.59111803564199494</v>
       </c>
       <c r="AK4">
-        <v>0.2045379271530105</v>
+        <v>0.20453795113973799</v>
       </c>
       <c r="AL4">
-        <v>0.41001135216232298</v>
+        <v>0.41001134440075337</v>
       </c>
       <c r="AM4">
-        <v>0.66760456802727797</v>
+        <v>0.66760458433301162</v>
       </c>
       <c r="AN4">
-        <v>0.27391927099005747</v>
+        <v>0.27391929705233842</v>
       </c>
       <c r="AO4">
-        <v>0.39278834158983528</v>
+        <v>0.39278833324782469</v>
       </c>
       <c r="AP4">
-        <v>0.72515755052212483</v>
+        <v>0.72515756245941765</v>
       </c>
       <c r="AQ4">
-        <v>0.33352378803126748</v>
+        <v>0.33352381496933159</v>
       </c>
       <c r="AR4">
-        <v>0.38141044296596638</v>
+        <v>0.38141043331846169</v>
       </c>
       <c r="AS4">
-        <v>0.76248735916582644</v>
+        <v>0.7624873714281184</v>
       </c>
       <c r="AT4">
-        <v>0.37164408117120118</v>
+        <v>0.37164411166749378</v>
       </c>
       <c r="AU4">
-        <v>0.37744566342548008</v>
+        <v>0.37744565528046742</v>
       </c>
       <c r="AV4">
-        <v>0.78039042297696271</v>
+        <v>0.78039043446688283</v>
       </c>
       <c r="AW4">
-        <v>0.38461116074320839</v>
+        <v>0.38461118598617289</v>
       </c>
       <c r="AX4">
-        <v>0.37946104239979228</v>
+        <v>0.3794610339577667</v>
       </c>
       <c r="AY4">
-        <v>0.79608703490880872</v>
+        <v>0.79608704967583899</v>
       </c>
       <c r="AZ4">
-        <v>0.377970184491979</v>
+        <v>0.37797021075689691</v>
       </c>
     </row>
     <row r="5" spans="1:52" x14ac:dyDescent="0.25">
@@ -1472,10 +1472,10 @@
         <v>54</v>
       </c>
       <c r="D5">
-        <v>0.39745522524434701</v>
+        <v>0.39745522192963167</v>
       </c>
       <c r="E5">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1484,139 +1484,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H5">
-        <v>0.48755636714605632</v>
+        <v>0.48755636622047183</v>
       </c>
       <c r="I5">
-        <v>1.9803835582807849E-2</v>
+        <v>1.9803837212716949E-2</v>
       </c>
       <c r="J5">
-        <v>-2.5592421513200379E-2</v>
+        <v>-2.5592419824805309E-2</v>
       </c>
       <c r="K5">
-        <v>0.49926180815580612</v>
+        <v>0.4992618086760946</v>
       </c>
       <c r="L5">
-        <v>6.1765606793263712E-2</v>
+        <v>6.176561004242076E-2</v>
       </c>
       <c r="M5">
-        <v>-7.5823678327988614E-2</v>
+        <v>-7.5823682898936595E-2</v>
       </c>
       <c r="N5">
-        <v>0.50173637327541654</v>
+        <v>0.50173637066682109</v>
       </c>
       <c r="O5">
-        <v>9.8411166708262554E-2</v>
+        <v>9.8411168091668166E-2</v>
       </c>
       <c r="P5">
-        <v>-8.6703235843808721E-2</v>
+        <v>-8.6703226827865701E-2</v>
       </c>
       <c r="Q5">
-        <v>0.51252228512701281</v>
+        <v>0.51252228408494738</v>
       </c>
       <c r="R5">
-        <v>0.33248528165993468</v>
+        <v>0.33248528911789449</v>
       </c>
       <c r="S5">
-        <v>-0.13410967754853961</v>
+        <v>-0.13410967537868279</v>
       </c>
       <c r="T5">
-        <v>0.46017539656023693</v>
+        <v>0.46017539526347218</v>
       </c>
       <c r="U5">
-        <v>0.41335793156528239</v>
+        <v>0.41335794166818018</v>
       </c>
       <c r="V5">
-        <v>8.5679900056743544E-2</v>
+        <v>8.5679903246940151E-2</v>
       </c>
       <c r="W5">
-        <v>0.43561440855788108</v>
+        <v>0.4356144051486891</v>
       </c>
       <c r="X5">
-        <v>0.56214479778687609</v>
+        <v>0.56214480359705932</v>
       </c>
       <c r="Y5">
-        <v>0.18077210974006719</v>
+        <v>0.180772120768982</v>
       </c>
       <c r="Z5">
-        <v>0.42167006606136198</v>
+        <v>0.42167006434232851</v>
       </c>
       <c r="AA5">
-        <v>0.60255057951279389</v>
+        <v>0.60255058966563324</v>
       </c>
       <c r="AB5">
-        <v>0.2322684848636255</v>
+        <v>0.23226848936947039</v>
       </c>
       <c r="AC5">
-        <v>0.40312028272063499</v>
+        <v>0.40312027612868379</v>
       </c>
       <c r="AD5">
-        <v>0.65982779017958926</v>
+        <v>0.65982780552456077</v>
       </c>
       <c r="AE5">
-        <v>0.29811458586599782</v>
+        <v>0.29811460714867949</v>
       </c>
       <c r="AF5">
-        <v>0.38189270953555338</v>
+        <v>0.38189270699110572</v>
       </c>
       <c r="AG5">
-        <v>0.69519362018011499</v>
+        <v>0.69519363717927085</v>
       </c>
       <c r="AH5">
-        <v>0.37031066127109269</v>
+        <v>0.37031066740281537</v>
       </c>
       <c r="AI5">
-        <v>0.37030939516751959</v>
+        <v>0.37030938519435153</v>
       </c>
       <c r="AJ5">
-        <v>0.72358251080551672</v>
+        <v>0.72358252771856302</v>
       </c>
       <c r="AK5">
-        <v>0.40789063508637707</v>
+        <v>0.40789066577873467</v>
       </c>
       <c r="AL5">
-        <v>0.35753367984825313</v>
+        <v>0.35753366434694173</v>
       </c>
       <c r="AM5">
-        <v>0.76150581485983715</v>
+        <v>0.76150584041378022</v>
       </c>
       <c r="AN5">
-        <v>0.44791958086994171</v>
+        <v>0.4479196277524099</v>
       </c>
       <c r="AO5">
-        <v>0.35771727660731462</v>
+        <v>0.3577172535865219</v>
       </c>
       <c r="AP5">
-        <v>0.78063873794589556</v>
+        <v>0.78063876666207666</v>
       </c>
       <c r="AQ5">
-        <v>0.44721981160569529</v>
+        <v>0.44721988156079001</v>
       </c>
       <c r="AR5">
-        <v>0.3644125221427777</v>
+        <v>0.36441249691854821</v>
       </c>
       <c r="AS5">
-        <v>0.80247178326107949</v>
+        <v>0.80247181663155986</v>
       </c>
       <c r="AT5">
-        <v>0.42620211586171591</v>
+        <v>0.42620219446977098</v>
       </c>
       <c r="AU5">
-        <v>0.37199919475905902</v>
+        <v>0.37199916503558927</v>
       </c>
       <c r="AV5">
-        <v>0.81667076381546555</v>
+        <v>0.81667080280388005</v>
       </c>
       <c r="AW5">
-        <v>0.40199667259052241</v>
+        <v>0.40199676727138489</v>
       </c>
       <c r="AX5">
-        <v>0.37887044019806337</v>
+        <v>0.37887040068106659</v>
       </c>
       <c r="AY5">
-        <v>0.83904029131018498</v>
+        <v>0.83904033875869433</v>
       </c>
       <c r="AZ5">
-        <v>0.37961432208467799</v>
+        <v>0.37961445058011167</v>
       </c>
     </row>
     <row r="6" spans="1:52" x14ac:dyDescent="0.25">
@@ -1630,10 +1630,10 @@
         <v>54</v>
       </c>
       <c r="D6">
-        <v>0.3758144351961572</v>
+        <v>0.3758144300292674</v>
       </c>
       <c r="E6">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1642,139 +1642,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H6">
-        <v>0.4876195117684492</v>
+        <v>0.48761951086036309</v>
       </c>
       <c r="I6">
-        <v>1.7537223372791181E-2</v>
+        <v>1.7537225070738072E-2</v>
       </c>
       <c r="J6">
-        <v>-2.5850253404275259E-2</v>
+        <v>-2.5850251788448929E-2</v>
       </c>
       <c r="K6">
-        <v>0.49943738837591339</v>
+        <v>0.49943739018435512</v>
       </c>
       <c r="L6">
-        <v>4.8404750052494783E-2</v>
+        <v>4.8404755028935709E-2</v>
       </c>
       <c r="M6">
-        <v>-7.6382791013304432E-2</v>
+        <v>-7.6382801091711028E-2</v>
       </c>
       <c r="N6">
-        <v>0.50159338472441772</v>
+        <v>0.50159338278896726</v>
       </c>
       <c r="O6">
-        <v>9.7232543528254833E-2</v>
+        <v>9.7232544248501807E-2</v>
       </c>
       <c r="P6">
-        <v>-8.6185639666446878E-2</v>
+        <v>-8.6185633584171903E-2</v>
       </c>
       <c r="Q6">
-        <v>0.49765582273427961</v>
+        <v>0.49765582589006341</v>
       </c>
       <c r="R6">
-        <v>0.36845316144311002</v>
+        <v>0.36845317347486789</v>
       </c>
       <c r="S6">
-        <v>-6.9191177121966416E-2</v>
+        <v>-6.9191192609653673E-2</v>
       </c>
       <c r="T6">
-        <v>0.43930224128583001</v>
+        <v>0.43930224099710208</v>
       </c>
       <c r="U6">
-        <v>0.4321599094740276</v>
+        <v>0.4321599140246225</v>
       </c>
       <c r="V6">
-        <v>0.16709037260646131</v>
+        <v>0.1670903719138398</v>
       </c>
       <c r="W6">
-        <v>0.4062477587801826</v>
+        <v>0.4062477531605006</v>
       </c>
       <c r="X6">
-        <v>0.55525100918360359</v>
+        <v>0.55525103408656618</v>
       </c>
       <c r="Y6">
-        <v>0.28760506680778042</v>
+        <v>0.28760508498729409</v>
       </c>
       <c r="Z6">
-        <v>0.39184879690863861</v>
+        <v>0.39184879431173281</v>
       </c>
       <c r="AA6">
-        <v>0.59261594251267402</v>
+        <v>0.59261595482834406</v>
       </c>
       <c r="AB6">
-        <v>0.33725096249828468</v>
+        <v>0.33725096992266268</v>
       </c>
       <c r="AC6">
-        <v>0.36996165771130352</v>
+        <v>0.3699616521905798</v>
       </c>
       <c r="AD6">
-        <v>0.66080328187490045</v>
+        <v>0.66080329468636634</v>
       </c>
       <c r="AE6">
-        <v>0.40921813673547358</v>
+        <v>0.40921815317360138</v>
       </c>
       <c r="AF6">
-        <v>0.3556679492582453</v>
+        <v>0.35566793970291088</v>
       </c>
       <c r="AG6">
-        <v>0.69986683806295136</v>
+        <v>0.6998668507704493</v>
       </c>
       <c r="AH6">
-        <v>0.45395614605220791</v>
+        <v>0.45395617413406192</v>
       </c>
       <c r="AI6">
-        <v>0.34926949251305961</v>
+        <v>0.34926948413705061</v>
       </c>
       <c r="AJ6">
-        <v>0.72060951830407993</v>
+        <v>0.72060953010764806</v>
       </c>
       <c r="AK6">
-        <v>0.47327413088068482</v>
+        <v>0.47327415502417092</v>
       </c>
       <c r="AL6">
-        <v>0.34287488244209052</v>
+        <v>0.34287487302364489</v>
       </c>
       <c r="AM6">
-        <v>0.7555295465643258</v>
+        <v>0.75552956404248373</v>
       </c>
       <c r="AN6">
-        <v>0.49241507238240562</v>
+        <v>0.49241509913539139</v>
       </c>
       <c r="AO6">
-        <v>0.34067418299801389</v>
+        <v>0.340674171633292</v>
       </c>
       <c r="AP6">
-        <v>0.77939910049954197</v>
+        <v>0.77939911853310417</v>
       </c>
       <c r="AQ6">
-        <v>0.49869984312262078</v>
+        <v>0.49869987534077997</v>
       </c>
       <c r="AR6">
-        <v>0.34346910650294998</v>
+        <v>0.34346909201960107</v>
       </c>
       <c r="AS6">
-        <v>0.80189876430960405</v>
+        <v>0.80189877864401615</v>
       </c>
       <c r="AT6">
-        <v>0.49061169270194049</v>
+        <v>0.49061173467849079</v>
       </c>
       <c r="AU6">
-        <v>0.34195064315898188</v>
+        <v>0.34195062587056702</v>
       </c>
       <c r="AV6">
-        <v>0.8173332274557632</v>
+        <v>0.81733325335052376</v>
       </c>
       <c r="AW6">
-        <v>0.49498387994264659</v>
+        <v>0.49498392957333398</v>
       </c>
       <c r="AX6">
-        <v>0.34763702668618501</v>
+        <v>0.34763701008791043</v>
       </c>
       <c r="AY6">
-        <v>0.8382870502874693</v>
+        <v>0.83828708108142003</v>
       </c>
       <c r="AZ6">
-        <v>0.47808860452312268</v>
+        <v>0.47808865340179751</v>
       </c>
     </row>
     <row r="7" spans="1:52" x14ac:dyDescent="0.25">
@@ -1788,10 +1788,10 @@
         <v>54</v>
       </c>
       <c r="D7">
-        <v>0.42639350381070362</v>
+        <v>0.42639349418019451</v>
       </c>
       <c r="E7">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1800,139 +1800,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H7">
-        <v>0.48985574931640458</v>
+        <v>0.48985574818036992</v>
       </c>
       <c r="I7">
-        <v>8.1492479969151876E-3</v>
+        <v>8.14924913292292E-3</v>
       </c>
       <c r="J7">
-        <v>-3.5313416952168407E-2</v>
+        <v>-3.5313414366568693E-2</v>
       </c>
       <c r="K7">
-        <v>0.49350061056118039</v>
+        <v>0.49350060948429619</v>
       </c>
       <c r="L7">
-        <v>2.0386376350813858E-2</v>
+        <v>2.0386377564948769E-2</v>
       </c>
       <c r="M7">
-        <v>-5.0760234490325358E-2</v>
+        <v>-5.0760232157602357E-2</v>
       </c>
       <c r="N7">
-        <v>0.51396064326894619</v>
+        <v>0.51396063998626373</v>
       </c>
       <c r="O7">
-        <v>4.0307983914214973E-2</v>
+        <v>4.0307984327773723E-2</v>
       </c>
       <c r="P7">
-        <v>-0.13980099710194779</v>
+        <v>-0.13980098496748319</v>
       </c>
       <c r="Q7">
-        <v>0.51672936153378179</v>
+        <v>0.51672935661206387</v>
       </c>
       <c r="R7">
-        <v>7.7120773502220685E-2</v>
+        <v>7.7120787246863998E-2</v>
       </c>
       <c r="S7">
-        <v>-0.15229786172990081</v>
+        <v>-0.15229784225114509</v>
       </c>
       <c r="T7">
-        <v>0.52700061358016392</v>
+        <v>0.52700061482188398</v>
       </c>
       <c r="U7">
-        <v>0.10337122972072629</v>
+        <v>0.1033712333529294</v>
       </c>
       <c r="V7">
-        <v>-0.19872465324562799</v>
+        <v>-0.19872466140160239</v>
       </c>
       <c r="W7">
-        <v>0.52663239989754962</v>
+        <v>0.52663240079928553</v>
       </c>
       <c r="X7">
-        <v>0.2144341459995576</v>
+        <v>0.21443415403172769</v>
       </c>
       <c r="Y7">
-        <v>-0.1975640377042476</v>
+        <v>-0.1975640448414322</v>
       </c>
       <c r="Z7">
-        <v>0.49020783144325908</v>
+        <v>0.49020784404431789</v>
       </c>
       <c r="AA7">
-        <v>0.30801335928909113</v>
+        <v>0.30801337149003838</v>
       </c>
       <c r="AB7">
-        <v>-3.7333180360937239E-2</v>
+        <v>-3.7333235238839788E-2</v>
       </c>
       <c r="AC7">
-        <v>0.4602840704059955</v>
+        <v>0.4602840684974252</v>
       </c>
       <c r="AD7">
-        <v>0.4129143808596254</v>
+        <v>0.41291439456261297</v>
       </c>
       <c r="AE7">
-        <v>8.5229553613779374E-2</v>
+        <v>8.5229558935943445E-2</v>
       </c>
       <c r="AF7">
-        <v>0.46045659973140768</v>
+        <v>0.4604565917701185</v>
       </c>
       <c r="AG7">
-        <v>0.50347163376527604</v>
+        <v>0.50347164162987545</v>
       </c>
       <c r="AH7">
-        <v>8.4434355404679126E-2</v>
+        <v>8.4434385144323942E-2</v>
       </c>
       <c r="AI7">
-        <v>0.44777444692530638</v>
+        <v>0.44777444061430183</v>
       </c>
       <c r="AJ7">
-        <v>0.51884187381180624</v>
+        <v>0.51884186734422655</v>
       </c>
       <c r="AK7">
-        <v>0.1343547276286095</v>
+        <v>0.13435475013807019</v>
       </c>
       <c r="AL7">
-        <v>0.42476728662181662</v>
+        <v>0.42476727694710831</v>
       </c>
       <c r="AM7">
-        <v>0.63064189352270117</v>
+        <v>0.63064191312640006</v>
       </c>
       <c r="AN7">
-        <v>0.2210376551103917</v>
+        <v>0.2210376889117156</v>
       </c>
       <c r="AO7">
-        <v>0.4036194213400261</v>
+        <v>0.40361940984829148</v>
       </c>
       <c r="AP7">
-        <v>0.72778150839579625</v>
+        <v>0.72778152133081897</v>
       </c>
       <c r="AQ7">
-        <v>0.29618177589191702</v>
+        <v>0.29618181451062708</v>
       </c>
       <c r="AR7">
-        <v>0.38666363369745621</v>
+        <v>0.38666362310002522</v>
       </c>
       <c r="AS7">
-        <v>0.75422531299580986</v>
+        <v>0.75422531174873708</v>
       </c>
       <c r="AT7">
-        <v>0.35418515249969318</v>
+        <v>0.35418518661267839</v>
       </c>
       <c r="AU7">
-        <v>0.37614383423999731</v>
+        <v>0.37614382233417581</v>
       </c>
       <c r="AV7">
-        <v>0.77776769452699701</v>
+        <v>0.77776770761540892</v>
       </c>
       <c r="AW7">
-        <v>0.38851983610111662</v>
+        <v>0.38851987361902851</v>
       </c>
       <c r="AX7">
-        <v>0.37158739716006078</v>
+        <v>0.37158738537437991</v>
       </c>
       <c r="AY7">
-        <v>0.79486064551220026</v>
+        <v>0.79486065718587329</v>
       </c>
       <c r="AZ7">
-        <v>0.40344506769835708</v>
+        <v>0.40344510442477488</v>
       </c>
     </row>
     <row r="8" spans="1:52" x14ac:dyDescent="0.25">
@@ -1946,10 +1946,10 @@
         <v>54</v>
       </c>
       <c r="D8">
-        <v>0.41387947892573229</v>
+        <v>0.41387947324522628</v>
       </c>
       <c r="E8">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1958,139 +1958,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H8">
-        <v>0.48876214825963221</v>
+        <v>0.48876214729139028</v>
       </c>
       <c r="I8">
-        <v>1.154569860863619E-2</v>
+        <v>1.1545700020051839E-2</v>
       </c>
       <c r="J8">
-        <v>-3.0673373728049659E-2</v>
+        <v>-3.0673371852327509E-2</v>
       </c>
       <c r="K8">
-        <v>0.49217686033869013</v>
+        <v>0.49217685993238081</v>
       </c>
       <c r="L8">
-        <v>2.0056808483147389E-2</v>
+        <v>2.0056809920791289E-2</v>
       </c>
       <c r="M8">
-        <v>-4.5154341286073638E-2</v>
+        <v>-4.5154341835079291E-2</v>
       </c>
       <c r="N8">
-        <v>0.50950008272538494</v>
+        <v>0.5095000802167442</v>
       </c>
       <c r="O8">
-        <v>4.7606069733048262E-2</v>
+        <v>4.7606070867476369E-2</v>
       </c>
       <c r="P8">
-        <v>-0.12013862621396559</v>
+        <v>-0.120138617643801</v>
       </c>
       <c r="Q8">
-        <v>0.51520482409924384</v>
+        <v>0.51520482353027774</v>
       </c>
       <c r="R8">
-        <v>0.145268556092087</v>
+        <v>0.1452685564544163</v>
       </c>
       <c r="S8">
-        <v>-0.14570452630148709</v>
+        <v>-0.14570452623236929</v>
       </c>
       <c r="T8">
-        <v>0.50224966005789295</v>
+        <v>0.50224965441852565</v>
       </c>
       <c r="U8">
-        <v>0.21766866261584661</v>
+        <v>0.2176686676764201</v>
       </c>
       <c r="V8">
-        <v>-8.8832582090157319E-2</v>
+        <v>-8.8832560209091554E-2</v>
       </c>
       <c r="W8">
-        <v>0.48015004486971502</v>
+        <v>0.48015004058401117</v>
       </c>
       <c r="X8">
-        <v>0.31586921209009872</v>
+        <v>0.31586922186345701</v>
       </c>
       <c r="Y8">
-        <v>5.0141516426768758E-3</v>
+        <v>5.0141671957533778E-3</v>
       </c>
       <c r="Z8">
-        <v>0.4661736316489315</v>
+        <v>0.46617362043863242</v>
       </c>
       <c r="AA8">
-        <v>0.37888793740444993</v>
+        <v>0.37888794934841052</v>
       </c>
       <c r="AB8">
-        <v>6.1920897621795049E-2</v>
+        <v>6.1920941818989987E-2</v>
       </c>
       <c r="AC8">
-        <v>0.44235129961232078</v>
+        <v>0.44235129528761519</v>
       </c>
       <c r="AD8">
-        <v>0.49119784136269828</v>
+        <v>0.49119785557770651</v>
       </c>
       <c r="AE8">
-        <v>0.15520919564922339</v>
+        <v>0.15520921003464169</v>
       </c>
       <c r="AF8">
-        <v>0.4310709117663139</v>
+        <v>0.43107090703877349</v>
       </c>
       <c r="AG8">
-        <v>0.53504238563451811</v>
+        <v>0.53504240076473786</v>
       </c>
       <c r="AH8">
-        <v>0.19761458331770529</v>
+        <v>0.19761459857275321</v>
       </c>
       <c r="AI8">
-        <v>0.39762185648146242</v>
+        <v>0.39762184723623478</v>
       </c>
       <c r="AJ8">
-        <v>0.67001579108791542</v>
+        <v>0.67001580982963493</v>
       </c>
       <c r="AK8">
-        <v>0.31732831697652147</v>
+        <v>0.31732834736179139</v>
       </c>
       <c r="AL8">
-        <v>0.39694677385277938</v>
+        <v>0.39694676384142369</v>
       </c>
       <c r="AM8">
-        <v>0.70545002261952283</v>
+        <v>0.70545003704118225</v>
       </c>
       <c r="AN8">
-        <v>0.31967382676367501</v>
+        <v>0.31967385972626677</v>
       </c>
       <c r="AO8">
-        <v>0.38236634543048481</v>
+        <v>0.38236633574754308</v>
       </c>
       <c r="AP8">
-        <v>0.74661540759766287</v>
+        <v>0.74661541898972428</v>
       </c>
       <c r="AQ8">
-        <v>0.36861382987531249</v>
+        <v>0.36861386050693129</v>
       </c>
       <c r="AR8">
-        <v>0.37037635119104761</v>
+        <v>0.37037634077757481</v>
       </c>
       <c r="AS8">
-        <v>0.76966930151064938</v>
+        <v>0.76966931538584149</v>
       </c>
       <c r="AT8">
-        <v>0.40761368752620752</v>
+        <v>0.40761371955380682</v>
       </c>
       <c r="AU8">
-        <v>0.37067230457582051</v>
+        <v>0.37067229412677372</v>
       </c>
       <c r="AV8">
-        <v>0.78485399758772911</v>
+        <v>0.78485401301614965</v>
       </c>
       <c r="AW8">
-        <v>0.40652458139807202</v>
+        <v>0.40652461348776131</v>
       </c>
       <c r="AX8">
-        <v>0.37213497626246411</v>
+        <v>0.37213496218809922</v>
       </c>
       <c r="AY8">
-        <v>0.79929928626584024</v>
+        <v>0.7992993009441538</v>
       </c>
       <c r="AZ8">
-        <v>0.40178598509664459</v>
+        <v>0.40178602906889899</v>
       </c>
     </row>
     <row r="9" spans="1:52" x14ac:dyDescent="0.25">
@@ -2104,10 +2104,10 @@
         <v>54</v>
       </c>
       <c r="D9">
-        <v>0.38757925160500439</v>
+        <v>0.38757924627414381</v>
       </c>
       <c r="E9">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -2116,139 +2116,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H9">
-        <v>0.4882154350120973</v>
+        <v>0.48821543406845941</v>
       </c>
       <c r="I9">
-        <v>1.1523134564930929E-2</v>
+        <v>1.152313597622745E-2</v>
       </c>
       <c r="J9">
-        <v>-2.8356694345300741E-2</v>
+        <v>-2.8356692576343011E-2</v>
       </c>
       <c r="K9">
-        <v>0.49190836444041619</v>
+        <v>0.49190836363055468</v>
       </c>
       <c r="L9">
-        <v>1.9912398596402151E-2</v>
+        <v>1.9912400027218499E-2</v>
       </c>
       <c r="M9">
-        <v>-4.4029789519784583E-2</v>
+        <v>-4.4029788327734617E-2</v>
       </c>
       <c r="N9">
-        <v>0.507507817299922</v>
+        <v>0.50750781405679479</v>
       </c>
       <c r="O9">
-        <v>4.4861203881223943E-2</v>
+        <v>4.4861205304624778E-2</v>
       </c>
       <c r="P9">
-        <v>-0.1113572878225689</v>
+        <v>-0.11135727599585141</v>
       </c>
       <c r="Q9">
-        <v>0.51362201501148208</v>
+        <v>0.51362201491191317</v>
       </c>
       <c r="R9">
-        <v>0.12936721950796301</v>
+        <v>0.12936722053662461</v>
       </c>
       <c r="S9">
-        <v>-0.1386696164190733</v>
+        <v>-0.13866961852662801</v>
       </c>
       <c r="T9">
-        <v>0.50021150711931506</v>
+        <v>0.50021150384900059</v>
       </c>
       <c r="U9">
-        <v>0.1919422206922079</v>
+        <v>0.19194222612683581</v>
       </c>
       <c r="V9">
-        <v>-8.0016407876304485E-2</v>
+        <v>-8.0016396036207305E-2</v>
       </c>
       <c r="W9">
-        <v>0.47844321883056462</v>
+        <v>0.47844321465822037</v>
       </c>
       <c r="X9">
-        <v>0.27826300346823329</v>
+        <v>0.27826301330976699</v>
       </c>
       <c r="Y9">
-        <v>1.211071514087647E-2</v>
+        <v>1.211073035841421E-2</v>
       </c>
       <c r="Z9">
-        <v>0.46573956492564872</v>
+        <v>0.46573956287301532</v>
       </c>
       <c r="AA9">
-        <v>0.33128034433085468</v>
+        <v>0.33128035590742749</v>
       </c>
       <c r="AB9">
-        <v>6.3673143171865773E-2</v>
+        <v>6.3673149616289254E-2</v>
       </c>
       <c r="AC9">
-        <v>0.44222210850813631</v>
+        <v>0.44222210372872622</v>
       </c>
       <c r="AD9">
-        <v>0.43263039866712988</v>
+        <v>0.43263041151636772</v>
       </c>
       <c r="AE9">
-        <v>0.15571799775814199</v>
+        <v>0.15571801419742751</v>
       </c>
       <c r="AF9">
-        <v>0.43085783488759438</v>
+        <v>0.43085782790173027</v>
       </c>
       <c r="AG9">
-        <v>0.46418459675562362</v>
+        <v>0.46418461137319561</v>
       </c>
       <c r="AH9">
-        <v>0.19852559876529699</v>
+        <v>0.19852562311392119</v>
       </c>
       <c r="AI9">
-        <v>0.38371096051455589</v>
+        <v>0.38371095463379667</v>
       </c>
       <c r="AJ9">
-        <v>0.60917093319122628</v>
+        <v>0.60917094881674916</v>
       </c>
       <c r="AK9">
-        <v>0.36400121847479838</v>
+        <v>0.36400123657163153</v>
       </c>
       <c r="AL9">
-        <v>0.38133077608557181</v>
+        <v>0.38133077136284649</v>
       </c>
       <c r="AM9">
-        <v>0.65152938363180057</v>
+        <v>0.65152939591825287</v>
       </c>
       <c r="AN9">
-        <v>0.37195380508948789</v>
+        <v>0.37195381925432869</v>
       </c>
       <c r="AO9">
-        <v>0.37014129065588047</v>
+        <v>0.37014128460350493</v>
       </c>
       <c r="AP9">
-        <v>0.66933548971403245</v>
+        <v>0.66933550506841688</v>
       </c>
       <c r="AQ9">
-        <v>0.40838180321310169</v>
+        <v>0.40838182115562932</v>
       </c>
       <c r="AR9">
-        <v>0.35908419919840051</v>
+        <v>0.35908419365831601</v>
       </c>
       <c r="AS9">
-        <v>0.69251583538047889</v>
+        <v>0.69251585122483328</v>
       </c>
       <c r="AT9">
-        <v>0.44323109846547692</v>
+        <v>0.44323111432192092</v>
       </c>
       <c r="AU9">
-        <v>0.35563641968890097</v>
+        <v>0.35563641748440072</v>
       </c>
       <c r="AV9">
-        <v>0.70783228189940961</v>
+        <v>0.70783229497112976</v>
       </c>
       <c r="AW9">
-        <v>0.45380873073644901</v>
+        <v>0.4538087359861272</v>
       </c>
       <c r="AX9">
-        <v>0.35536721674708949</v>
+        <v>0.35536721510394309</v>
       </c>
       <c r="AY9">
-        <v>0.73408954199901877</v>
+        <v>0.73408956162805072</v>
       </c>
       <c r="AZ9">
-        <v>0.45459008525786571</v>
+        <v>0.45459008946510499</v>
       </c>
     </row>
     <row r="10" spans="1:52" x14ac:dyDescent="0.25">
@@ -2262,10 +2262,10 @@
         <v>54</v>
       </c>
       <c r="D10">
-        <v>0.39364474379292302</v>
+        <v>0.39364473814638667</v>
       </c>
       <c r="E10">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -2274,139 +2274,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H10">
-        <v>0.48782123876697092</v>
+        <v>0.48782123786193449</v>
       </c>
       <c r="I10">
-        <v>1.152168948984955E-2</v>
+        <v>1.1521690900874629E-2</v>
       </c>
       <c r="J10">
-        <v>-2.6691510416025459E-2</v>
+        <v>-2.669150881312134E-2</v>
       </c>
       <c r="K10">
-        <v>0.49140228515904361</v>
+        <v>0.49140228409643472</v>
       </c>
       <c r="L10">
-        <v>1.991093147459011E-2</v>
+        <v>1.9910932904087849E-2</v>
       </c>
       <c r="M10">
-        <v>-4.1858118338935532E-2</v>
+        <v>-4.1858116068646027E-2</v>
       </c>
       <c r="N10">
-        <v>0.50951380451537154</v>
+        <v>0.50951380123140122</v>
       </c>
       <c r="O10">
-        <v>4.487432521330792E-2</v>
+        <v>4.487432664457025E-2</v>
       </c>
       <c r="P10">
-        <v>-0.1202150650534201</v>
+        <v>-0.1202150530129273</v>
       </c>
       <c r="Q10">
-        <v>0.51405537981297766</v>
+        <v>0.5140553793544782</v>
       </c>
       <c r="R10">
-        <v>0.12874213745262381</v>
+        <v>0.12874213848030699</v>
       </c>
       <c r="S10">
-        <v>-0.14060563264021159</v>
+        <v>-0.1406056330616027</v>
       </c>
       <c r="T10">
-        <v>0.50227223690886025</v>
+        <v>0.50227223273833355</v>
       </c>
       <c r="U10">
-        <v>0.19055044904380899</v>
+        <v>0.19055045455288819</v>
       </c>
       <c r="V10">
-        <v>-8.8858877643691797E-2</v>
+        <v>-8.8858861901878181E-2</v>
       </c>
       <c r="W10">
-        <v>0.48035667811901922</v>
+        <v>0.48035667332151921</v>
       </c>
       <c r="X10">
-        <v>0.27659673626495163</v>
+        <v>0.27659674624631958</v>
       </c>
       <c r="Y10">
-        <v>4.061695245481692E-3</v>
+        <v>4.0617129693045692E-3</v>
       </c>
       <c r="Z10">
-        <v>0.46613205299469151</v>
+        <v>0.46613204951339349</v>
       </c>
       <c r="AA10">
-        <v>0.32848056532223108</v>
+        <v>0.32848057704692463</v>
       </c>
       <c r="AB10">
-        <v>6.2055296756127233E-2</v>
+        <v>6.2055308806162487E-2</v>
       </c>
       <c r="AC10">
-        <v>0.44274019427345679</v>
+        <v>0.44274018772121287</v>
       </c>
       <c r="AD10">
-        <v>0.42806869300927303</v>
+        <v>0.42806870595701407</v>
       </c>
       <c r="AE10">
-        <v>0.153900068892805</v>
+        <v>0.1539000921113429</v>
       </c>
       <c r="AF10">
-        <v>0.43312759477384022</v>
+        <v>0.43312758677605229</v>
       </c>
       <c r="AG10">
-        <v>0.45871180921328281</v>
+        <v>0.45871182407152727</v>
       </c>
       <c r="AH10">
-        <v>0.19003576239502121</v>
+        <v>0.1900357903851651</v>
       </c>
       <c r="AI10">
-        <v>0.3877263198932589</v>
+        <v>0.38772631309212158</v>
       </c>
       <c r="AJ10">
-        <v>0.60176599806169029</v>
+        <v>0.60176601323821433</v>
       </c>
       <c r="AK10">
-        <v>0.35082957137821158</v>
+        <v>0.3508295927443818</v>
       </c>
       <c r="AL10">
-        <v>0.3865239865384722</v>
+        <v>0.38652398146969058</v>
       </c>
       <c r="AM10">
-        <v>0.64234199110255208</v>
+        <v>0.6423420043085013</v>
       </c>
       <c r="AN10">
-        <v>0.35496222479345929</v>
+        <v>0.3549622402925533</v>
       </c>
       <c r="AO10">
-        <v>0.37536901918126608</v>
+        <v>0.37536901399607808</v>
       </c>
       <c r="AP10">
-        <v>0.661932625463724</v>
+        <v>0.66193264343723457</v>
       </c>
       <c r="AQ10">
-        <v>0.3917028893041955</v>
+        <v>0.39170290479115177</v>
       </c>
       <c r="AR10">
-        <v>0.36577820602566108</v>
+        <v>0.36577820046673792</v>
       </c>
       <c r="AS10">
-        <v>0.68373105031312398</v>
+        <v>0.6837310725851794</v>
       </c>
       <c r="AT10">
-        <v>0.42227299535301099</v>
+        <v>0.42227301162565561</v>
       </c>
       <c r="AU10">
-        <v>0.36215702117807042</v>
+        <v>0.36215701854446403</v>
       </c>
       <c r="AV10">
-        <v>0.69592023698840177</v>
+        <v>0.69592025147791114</v>
       </c>
       <c r="AW10">
-        <v>0.43369366094920292</v>
+        <v>0.43369366795419217</v>
       </c>
       <c r="AX10">
-        <v>0.36062969117831822</v>
+        <v>0.36062968655558852</v>
       </c>
       <c r="AY10">
-        <v>0.72392308750843593</v>
+        <v>0.7239231088952689</v>
       </c>
       <c r="AZ10">
-        <v>0.43841669395064897</v>
+        <v>0.43841670732670751</v>
       </c>
     </row>
     <row r="11" spans="1:52" x14ac:dyDescent="0.25">
@@ -2420,10 +2420,10 @@
         <v>54</v>
       </c>
       <c r="D11">
-        <v>0.38884906665697871</v>
+        <v>0.38884905923797147</v>
       </c>
       <c r="E11">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -2432,139 +2432,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H11">
-        <v>0.48901373128614628</v>
+        <v>0.4890137304370793</v>
       </c>
       <c r="I11">
-        <v>1.152875063315162E-2</v>
+        <v>1.15287520439199E-2</v>
       </c>
       <c r="J11">
-        <v>-3.1722724002114053E-2</v>
+        <v>-3.172272263770673E-2</v>
       </c>
       <c r="K11">
-        <v>0.49290653765833869</v>
+        <v>0.49290653680817792</v>
       </c>
       <c r="L11">
-        <v>1.9943167569415721E-2</v>
+        <v>1.9943168998221909E-2</v>
       </c>
       <c r="M11">
-        <v>-4.8243464234574977E-2</v>
+        <v>-4.8243462879518591E-2</v>
       </c>
       <c r="N11">
-        <v>0.50916115347444191</v>
+        <v>0.50916115023997521</v>
       </c>
       <c r="O11">
-        <v>4.5191651796304688E-2</v>
+        <v>4.5191653196633992E-2</v>
       </c>
       <c r="P11">
-        <v>-0.11861049016000159</v>
+        <v>-0.1186104783500896</v>
       </c>
       <c r="Q11">
-        <v>0.51483230157151905</v>
+        <v>0.51483230094236865</v>
       </c>
       <c r="R11">
-        <v>0.12833751924724229</v>
+        <v>0.12833752042359761</v>
       </c>
       <c r="S11">
-        <v>-0.14389686322462991</v>
+        <v>-0.1438968629004351</v>
       </c>
       <c r="T11">
-        <v>0.50174759602858654</v>
+        <v>0.50174759069760622</v>
       </c>
       <c r="U11">
-        <v>0.1891380719154154</v>
+        <v>0.18913807744384711</v>
       </c>
       <c r="V11">
-        <v>-8.6595925314043143E-2</v>
+        <v>-8.6595904549573666E-2</v>
       </c>
       <c r="W11">
-        <v>0.48093501802019989</v>
+        <v>0.48093501572535741</v>
       </c>
       <c r="X11">
-        <v>0.27458611527909049</v>
+        <v>0.27458612524242698</v>
       </c>
       <c r="Y11">
-        <v>1.544607639932838E-3</v>
+        <v>1.5446148188886699E-3</v>
       </c>
       <c r="Z11">
-        <v>0.46843057249887549</v>
+        <v>0.46843057264141957</v>
       </c>
       <c r="AA11">
-        <v>0.32843417474388981</v>
+        <v>0.32843418664434237</v>
       </c>
       <c r="AB11">
-        <v>5.2442021193440748E-2</v>
+        <v>5.244201850322143E-2</v>
       </c>
       <c r="AC11">
-        <v>0.44124696033102989</v>
+        <v>0.44124695390244162</v>
       </c>
       <c r="AD11">
-        <v>0.43219819513884222</v>
+        <v>0.43219820874703602</v>
       </c>
       <c r="AE11">
-        <v>0.15932834764442569</v>
+        <v>0.15932837033714489</v>
       </c>
       <c r="AF11">
-        <v>0.43055742342171072</v>
+        <v>0.43055741320429303</v>
       </c>
       <c r="AG11">
-        <v>0.46672721346235518</v>
+        <v>0.46672722889189311</v>
       </c>
       <c r="AH11">
-        <v>0.19951507232676691</v>
+        <v>0.19951510856332089</v>
       </c>
       <c r="AI11">
-        <v>0.38334103621729698</v>
+        <v>0.38334103657372742</v>
       </c>
       <c r="AJ11">
-        <v>0.60636899815276202</v>
+        <v>0.60636901509076724</v>
       </c>
       <c r="AK11">
-        <v>0.36551557385989808</v>
+        <v>0.36551557074073582</v>
       </c>
       <c r="AL11">
-        <v>0.38029935117437219</v>
+        <v>0.38029934605688448</v>
       </c>
       <c r="AM11">
-        <v>0.64733985871961819</v>
+        <v>0.64733987305225615</v>
       </c>
       <c r="AN11">
-        <v>0.37553916005814209</v>
+        <v>0.3755391755607187</v>
       </c>
       <c r="AO11">
-        <v>0.3693065556607229</v>
+        <v>0.36930654738821211</v>
       </c>
       <c r="AP11">
-        <v>0.66937441274766363</v>
+        <v>0.66937442843433137</v>
       </c>
       <c r="AQ11">
-        <v>0.41103313543729492</v>
+        <v>0.41103316050170408</v>
       </c>
       <c r="AR11">
-        <v>0.35940793444064079</v>
+        <v>0.35940792642947939</v>
       </c>
       <c r="AS11">
-        <v>0.69086878319519451</v>
+        <v>0.69086880057736499</v>
       </c>
       <c r="AT11">
-        <v>0.44224312108231528</v>
+        <v>0.44224314480998089</v>
       </c>
       <c r="AU11">
-        <v>0.35833860565052239</v>
+        <v>0.358338599587948</v>
       </c>
       <c r="AV11">
-        <v>0.7038732612611136</v>
+        <v>0.70387327744171568</v>
       </c>
       <c r="AW11">
-        <v>0.4454911941956563</v>
+        <v>0.44549121186234392</v>
       </c>
       <c r="AX11">
-        <v>0.35711197263987071</v>
+        <v>0.35711195501044202</v>
       </c>
       <c r="AY11">
-        <v>0.72342044183446674</v>
+        <v>0.72342045851286274</v>
       </c>
       <c r="AZ11">
-        <v>0.44922050570578442</v>
+        <v>0.44922055903650748</v>
       </c>
     </row>
     <row r="12" spans="1:52" x14ac:dyDescent="0.25">
@@ -2578,10 +2578,10 @@
         <v>54</v>
       </c>
       <c r="D12">
-        <v>0.38646480563156649</v>
+        <v>0.38646479564280078</v>
       </c>
       <c r="E12">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -2590,139 +2590,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H12">
-        <v>0.48783329782282708</v>
+        <v>0.48783329690049537</v>
       </c>
       <c r="I12">
-        <v>2.0549512506126359E-2</v>
+        <v>2.054951423303808E-2</v>
       </c>
       <c r="J12">
-        <v>-2.6756720230699811E-2</v>
+        <v>-2.6756718556157251E-2</v>
       </c>
       <c r="K12">
-        <v>0.50084869624457606</v>
+        <v>0.50084869696532175</v>
       </c>
       <c r="L12">
-        <v>6.1984953456805769E-2</v>
+        <v>6.1984956944251428E-2</v>
       </c>
       <c r="M12">
-        <v>-8.262445416798482E-2</v>
+        <v>-8.2624459624374452E-2</v>
       </c>
       <c r="N12">
-        <v>0.49574144298315681</v>
+        <v>0.4957414404999807</v>
       </c>
       <c r="O12">
-        <v>9.7258798311965489E-2</v>
+        <v>9.7258799081962222E-2</v>
       </c>
       <c r="P12">
-        <v>-6.0555781754641248E-2</v>
+        <v>-6.0555773195774543E-2</v>
       </c>
       <c r="Q12">
-        <v>0.50770127734391268</v>
+        <v>0.50770127755433314</v>
       </c>
       <c r="R12">
-        <v>0.27854446402715288</v>
+        <v>0.27854447460829301</v>
       </c>
       <c r="S12">
-        <v>-0.1126078056758581</v>
+        <v>-0.11260780867528961</v>
       </c>
       <c r="T12">
-        <v>0.46087900506055768</v>
+        <v>0.46087900609843602</v>
       </c>
       <c r="U12">
-        <v>0.41793402825542292</v>
+        <v>0.41793402704051952</v>
       </c>
       <c r="V12">
-        <v>8.3038805885201808E-2</v>
+        <v>8.3038799662859597E-2</v>
       </c>
       <c r="W12">
-        <v>0.44059078651450517</v>
+        <v>0.44059078212792679</v>
       </c>
       <c r="X12">
-        <v>0.5057786907945625</v>
+        <v>0.50577869443947199</v>
       </c>
       <c r="Y12">
-        <v>0.1619302490917523</v>
+        <v>0.16193026387025361</v>
       </c>
       <c r="Z12">
-        <v>0.41325800473117269</v>
+        <v>0.41325800096646959</v>
       </c>
       <c r="AA12">
-        <v>0.60098998984583196</v>
+        <v>0.6009900001585996</v>
       </c>
       <c r="AB12">
-        <v>0.26282856067089871</v>
+        <v>0.26282857257014308</v>
       </c>
       <c r="AC12">
-        <v>0.38618551850338728</v>
+        <v>0.38618550843996963</v>
       </c>
       <c r="AD12">
-        <v>0.66796261666919243</v>
+        <v>0.66796263533973033</v>
       </c>
       <c r="AE12">
-        <v>0.3562546814911533</v>
+        <v>0.35625471360620498</v>
       </c>
       <c r="AF12">
-        <v>0.37214742482831031</v>
+        <v>0.37214741317595268</v>
       </c>
       <c r="AG12">
-        <v>0.70249412227365637</v>
+        <v>0.70249414089401174</v>
       </c>
       <c r="AH12">
-        <v>0.4022152290171252</v>
+        <v>0.40221526509828709</v>
       </c>
       <c r="AI12">
-        <v>0.36366203257066138</v>
+        <v>0.36366202096872341</v>
       </c>
       <c r="AJ12">
-        <v>0.72790960023961171</v>
+        <v>0.72790961956362543</v>
       </c>
       <c r="AK12">
-        <v>0.4291391883754393</v>
+        <v>0.42913922352796458</v>
       </c>
       <c r="AL12">
-        <v>0.35124928265076882</v>
+        <v>0.35124926253588867</v>
       </c>
       <c r="AM12">
-        <v>0.76928967862448472</v>
+        <v>0.76928970972037414</v>
       </c>
       <c r="AN12">
-        <v>0.46742864352927838</v>
+        <v>0.46742870328468122</v>
       </c>
       <c r="AO12">
-        <v>0.35024354674875102</v>
+        <v>0.35024352348330418</v>
       </c>
       <c r="AP12">
-        <v>0.78929204972172751</v>
+        <v>0.78929208450926214</v>
       </c>
       <c r="AQ12">
-        <v>0.4703000350486054</v>
+        <v>0.47030010402694827</v>
       </c>
       <c r="AR12">
-        <v>0.35491355436373512</v>
+        <v>0.35491352561181599</v>
       </c>
       <c r="AS12">
-        <v>0.81061820187881728</v>
+        <v>0.81061823896107132</v>
       </c>
       <c r="AT12">
-        <v>0.45601466572009841</v>
+        <v>0.45601475250631751</v>
       </c>
       <c r="AU12">
-        <v>0.36253351487236768</v>
+        <v>0.36253348201596342</v>
       </c>
       <c r="AV12">
-        <v>0.82525250927525362</v>
+        <v>0.82525254685237626</v>
       </c>
       <c r="AW12">
-        <v>0.43238126119911929</v>
+        <v>0.43238136269328947</v>
       </c>
       <c r="AX12">
-        <v>0.37468280639143559</v>
+        <v>0.37468276036485082</v>
       </c>
       <c r="AY12">
-        <v>0.84887021284416597</v>
+        <v>0.8488702580740447</v>
       </c>
       <c r="AZ12">
-        <v>0.39357848338742141</v>
+        <v>0.39357863096689072</v>
       </c>
     </row>
     <row r="13" spans="1:52" x14ac:dyDescent="0.25">
@@ -2736,10 +2736,10 @@
         <v>54</v>
       </c>
       <c r="D13">
-        <v>0.46320966441865091</v>
+        <v>0.46320965667876468</v>
       </c>
       <c r="E13">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -2748,139 +2748,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H13">
-        <v>0.48715502804578559</v>
+        <v>0.48715502718360482</v>
       </c>
       <c r="I13">
-        <v>2.4511611518846729E-2</v>
+        <v>2.4511613266062771E-2</v>
       </c>
       <c r="J13">
-        <v>-2.3893721743971318E-2</v>
+        <v>-2.3893720320706292E-2</v>
       </c>
       <c r="K13">
-        <v>0.50946714811057392</v>
+        <v>0.50946714886153721</v>
       </c>
       <c r="L13">
-        <v>9.3090332014055366E-2</v>
+        <v>9.3090336256451911E-2</v>
       </c>
       <c r="M13">
-        <v>-0.1201995310818109</v>
+        <v>-0.1201995368113233</v>
       </c>
       <c r="N13">
-        <v>0.50780664545863141</v>
+        <v>0.50780664310352941</v>
       </c>
       <c r="O13">
-        <v>0.15934987247888949</v>
+        <v>0.15934986890801139</v>
       </c>
       <c r="P13">
-        <v>-0.11278582961699091</v>
+        <v>-0.112785821703292</v>
       </c>
       <c r="Q13">
-        <v>0.51184398539278153</v>
+        <v>0.51184398780970697</v>
       </c>
       <c r="R13">
-        <v>0.25200000015077939</v>
+        <v>0.2519999925047266</v>
       </c>
       <c r="S13">
-        <v>-0.1307710511099584</v>
+        <v>-0.13077106419370879</v>
       </c>
       <c r="T13">
-        <v>0.51916661609536219</v>
+        <v>0.51916662223950261</v>
       </c>
       <c r="U13">
-        <v>0.33681462683150271</v>
+        <v>0.33681462197600109</v>
       </c>
       <c r="V13">
-        <v>-0.16347516271622001</v>
+        <v>-0.16347519261660201</v>
       </c>
       <c r="W13">
-        <v>0.4860202655700141</v>
+        <v>0.48602026834433742</v>
       </c>
       <c r="X13">
-        <v>0.46516379634067412</v>
+        <v>0.4651637969872956</v>
       </c>
       <c r="Y13">
-        <v>-2.0014291255418079E-2</v>
+        <v>-2.001430509131415E-2</v>
       </c>
       <c r="Z13">
-        <v>0.48011129148669363</v>
+        <v>0.48011129397549901</v>
       </c>
       <c r="AA13">
-        <v>0.56250952021066181</v>
+        <v>0.56250952199322768</v>
       </c>
       <c r="AB13">
-        <v>4.5532055195594617E-3</v>
+        <v>4.5531931522426279E-3</v>
       </c>
       <c r="AC13">
-        <v>0.46414965423944848</v>
+        <v>0.46414965644581863</v>
       </c>
       <c r="AD13">
-        <v>0.61078323280179281</v>
+        <v>0.61078322885611058</v>
       </c>
       <c r="AE13">
-        <v>6.9493762777614793E-2</v>
+        <v>6.9493752007350279E-2</v>
       </c>
       <c r="AF13">
-        <v>0.44337908439014978</v>
+        <v>0.44337907690353029</v>
       </c>
       <c r="AG13">
-        <v>0.67079848188769076</v>
+        <v>0.67079849134464942</v>
       </c>
       <c r="AH13">
-        <v>0.1507475264948315</v>
+        <v>0.1507475533145434</v>
       </c>
       <c r="AI13">
-        <v>0.42340724252104261</v>
+        <v>0.42340722876021841</v>
       </c>
       <c r="AJ13">
-        <v>0.71890257939341118</v>
+        <v>0.71890260125679029</v>
       </c>
       <c r="AK13">
-        <v>0.2255624104650143</v>
+        <v>0.22556245919183521</v>
       </c>
       <c r="AL13">
-        <v>0.41752970180877041</v>
+        <v>0.41752968502755677</v>
       </c>
       <c r="AM13">
-        <v>0.74183920705019135</v>
+        <v>0.74183923325210666</v>
       </c>
       <c r="AN13">
-        <v>0.2468114642571993</v>
+        <v>0.2468115233004245</v>
       </c>
       <c r="AO13">
-        <v>0.41059397069112469</v>
+        <v>0.41059394740757499</v>
       </c>
       <c r="AP13">
-        <v>0.77490950304260053</v>
+        <v>0.77490954092964182</v>
       </c>
       <c r="AQ13">
-        <v>0.27164830868655371</v>
+        <v>0.27164838970131661</v>
       </c>
       <c r="AR13">
-        <v>0.40827852078386262</v>
+        <v>0.40827849074038758</v>
       </c>
       <c r="AS13">
-        <v>0.78491865055556742</v>
+        <v>0.78491869166140227</v>
       </c>
       <c r="AT13">
-        <v>0.27999002813846402</v>
+        <v>0.2799901323528427</v>
       </c>
       <c r="AU13">
-        <v>0.40480801808644601</v>
+        <v>0.40480797386453371</v>
       </c>
       <c r="AV13">
-        <v>0.80660524912098697</v>
+        <v>0.80660530033976141</v>
       </c>
       <c r="AW13">
-        <v>0.29211798403815659</v>
+        <v>0.2921181368620811</v>
       </c>
       <c r="AX13">
-        <v>0.41061646623797993</v>
+        <v>0.41061641010542732</v>
       </c>
       <c r="AY13">
-        <v>0.82377384422664413</v>
+        <v>0.82377389963959524</v>
       </c>
       <c r="AZ13">
-        <v>0.27158588194184802</v>
+        <v>0.27158607941221202</v>
       </c>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.25">
@@ -2894,10 +2894,10 @@
         <v>54</v>
       </c>
       <c r="D14">
-        <v>0.39426573573478019</v>
+        <v>0.39426572879716859</v>
       </c>
       <c r="E14">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -2906,139 +2906,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H14">
-        <v>0.48909082083059607</v>
+        <v>0.48909081943020222</v>
       </c>
       <c r="I14">
-        <v>8.1424294550320742E-3</v>
+        <v>8.1424305908883721E-3</v>
       </c>
       <c r="J14">
-        <v>-3.2056823448559507E-2</v>
+        <v>-3.2056819736397242E-2</v>
       </c>
       <c r="K14">
-        <v>0.49331380709757172</v>
+        <v>0.49331380538891328</v>
       </c>
       <c r="L14">
-        <v>2.0327833357166699E-2</v>
+        <v>2.0327834566287391E-2</v>
       </c>
       <c r="M14">
-        <v>-4.9977206476293293E-2</v>
+        <v>-4.997720143126276E-2</v>
       </c>
       <c r="N14">
-        <v>0.51294426645951474</v>
+        <v>0.5129442637958781</v>
       </c>
       <c r="O14">
-        <v>3.904364454562903E-2</v>
+        <v>3.9043645160005018E-2</v>
       </c>
       <c r="P14">
-        <v>-0.13529196978565361</v>
+        <v>-0.1352919604521276</v>
       </c>
       <c r="Q14">
-        <v>0.51350552962535934</v>
+        <v>0.51350552454740328</v>
       </c>
       <c r="R14">
-        <v>7.2558592460281179E-2</v>
+        <v>7.2558605176333502E-2</v>
       </c>
       <c r="S14">
-        <v>-0.13787255983699709</v>
+        <v>-0.13787253981225989</v>
       </c>
       <c r="T14">
-        <v>0.52342171237403323</v>
+        <v>0.52342171094665191</v>
       </c>
       <c r="U14">
-        <v>9.5934686454204887E-2</v>
+        <v>9.5934690050021643E-2</v>
       </c>
       <c r="V14">
-        <v>-0.1823612950722413</v>
+        <v>-0.1823612911787198</v>
       </c>
       <c r="W14">
-        <v>0.52106949628972099</v>
+        <v>0.52106949621207188</v>
       </c>
       <c r="X14">
-        <v>0.19433655611562739</v>
+        <v>0.1943365638302634</v>
       </c>
       <c r="Y14">
-        <v>-0.17215583078290531</v>
+        <v>-0.17215583325098949</v>
       </c>
       <c r="Z14">
-        <v>0.48756789744499668</v>
+        <v>0.48756789344263191</v>
       </c>
       <c r="AA14">
-        <v>0.27657340599635311</v>
+        <v>0.27657341786012118</v>
       </c>
       <c r="AB14">
-        <v>-2.6109325064025461E-2</v>
+        <v>-2.610931046476932E-2</v>
       </c>
       <c r="AC14">
-        <v>0.4578847276714208</v>
+        <v>0.45788472229766958</v>
       </c>
       <c r="AD14">
-        <v>0.36628268535061942</v>
+        <v>0.36628269883642972</v>
       </c>
       <c r="AE14">
-        <v>9.5030643239301923E-2</v>
+        <v>9.5030662563977117E-2</v>
       </c>
       <c r="AF14">
-        <v>0.45706661297676981</v>
+        <v>0.45706660583912501</v>
       </c>
       <c r="AG14">
-        <v>0.45522159370156051</v>
+        <v>0.45522160683427287</v>
       </c>
       <c r="AH14">
-        <v>9.8049628573444791E-2</v>
+        <v>9.8049654806597789E-2</v>
       </c>
       <c r="AI14">
-        <v>0.44747736576775188</v>
+        <v>0.44747735740329397</v>
       </c>
       <c r="AJ14">
-        <v>0.55455277653933455</v>
+        <v>0.55455229923112581</v>
       </c>
       <c r="AK14">
-        <v>0.13550138432443859</v>
+        <v>0.13550141482556849</v>
       </c>
       <c r="AL14">
-        <v>0.41892761228226733</v>
+        <v>0.41892760071365742</v>
       </c>
       <c r="AM14">
-        <v>0.56916423878515876</v>
+        <v>0.56916422548417356</v>
       </c>
       <c r="AN14">
-        <v>0.2422404537912515</v>
+        <v>0.24224049351180649</v>
       </c>
       <c r="AO14">
-        <v>0.38730347423556422</v>
+        <v>0.38730346678665739</v>
       </c>
       <c r="AP14">
-        <v>0.67362526074750562</v>
+        <v>0.67362527527994365</v>
       </c>
       <c r="AQ14">
-        <v>0.35216079953019808</v>
+        <v>0.35216082304149843</v>
       </c>
       <c r="AR14">
-        <v>0.37508676949999448</v>
+        <v>0.37508676120849738</v>
       </c>
       <c r="AS14">
-        <v>0.68982004812130904</v>
+        <v>0.689820063550733</v>
       </c>
       <c r="AT14">
-        <v>0.39231027238477828</v>
+        <v>0.39231029790193089</v>
       </c>
       <c r="AU14">
-        <v>0.36586610666184199</v>
+        <v>0.36586609643726198</v>
       </c>
       <c r="AV14">
-        <v>0.72107213261162906</v>
+        <v>0.72107215237940658</v>
       </c>
       <c r="AW14">
-        <v>0.42180983474555628</v>
+        <v>0.4218098657650789</v>
       </c>
       <c r="AX14">
-        <v>0.36088746776451019</v>
+        <v>0.36088745814276169</v>
       </c>
       <c r="AY14">
-        <v>0.73428781368267493</v>
+        <v>0.73428783014497911</v>
       </c>
       <c r="AZ14">
-        <v>0.43752674323861679</v>
+        <v>0.43752677194704193</v>
       </c>
     </row>
     <row r="15" spans="1:52" x14ac:dyDescent="0.25">
@@ -3052,10 +3052,10 @@
         <v>54</v>
       </c>
       <c r="D15">
-        <v>0.40225304572761611</v>
+        <v>0.40225303927614731</v>
       </c>
       <c r="E15">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -3064,139 +3064,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H15">
-        <v>0.4891360160101717</v>
+        <v>0.48913601473345331</v>
       </c>
       <c r="I15">
-        <v>8.1388819817811431E-3</v>
+        <v>8.1388831177554577E-3</v>
       </c>
       <c r="J15">
-        <v>-3.225698793633059E-2</v>
+        <v>-3.2256984753945277E-2</v>
       </c>
       <c r="K15">
-        <v>0.49254749610802312</v>
+        <v>0.49254749527994929</v>
       </c>
       <c r="L15">
-        <v>2.0309981806298168E-2</v>
+        <v>2.0309983015503689E-2</v>
       </c>
       <c r="M15">
-        <v>-4.6693587386558801E-2</v>
+        <v>-4.669358611612854E-2</v>
       </c>
       <c r="N15">
-        <v>0.51179711127637761</v>
+        <v>0.51179710823268765</v>
       </c>
       <c r="O15">
-        <v>3.8688852611546087E-2</v>
+        <v>3.8688853313166523E-2</v>
       </c>
       <c r="P15">
-        <v>-0.13015989213235801</v>
+        <v>-0.13015988110983831</v>
       </c>
       <c r="Q15">
-        <v>0.51264142786705746</v>
+        <v>0.51264142318870465</v>
       </c>
       <c r="R15">
-        <v>7.1284654614452769E-2</v>
+        <v>7.128466715063464E-2</v>
       </c>
       <c r="S15">
-        <v>-0.13403521419605441</v>
+        <v>-0.13403519593110211</v>
       </c>
       <c r="T15">
-        <v>0.52138132354845568</v>
+        <v>0.52138132097429124</v>
       </c>
       <c r="U15">
-        <v>9.3720405601188106E-2</v>
+        <v>9.3720409480895217E-2</v>
       </c>
       <c r="V15">
-        <v>-0.1732111876770267</v>
+        <v>-0.17321117876195019</v>
       </c>
       <c r="W15">
-        <v>0.51881024557971533</v>
+        <v>0.51881024071906812</v>
       </c>
       <c r="X15">
-        <v>0.18870392051898829</v>
+        <v>0.18870392860572741</v>
       </c>
       <c r="Y15">
-        <v>-0.16227235910349719</v>
+        <v>-0.162272340220802</v>
       </c>
       <c r="Z15">
-        <v>0.48710925543105399</v>
+        <v>0.48710933896285807</v>
       </c>
       <c r="AA15">
-        <v>0.26895407716571618</v>
+        <v>0.26895408947059302</v>
       </c>
       <c r="AB15">
-        <v>-2.4050872997839721E-2</v>
+        <v>-2.405122130220785E-2</v>
       </c>
       <c r="AC15">
-        <v>0.46036010029314978</v>
+        <v>0.46036028009195518</v>
       </c>
       <c r="AD15">
-        <v>0.35616843742709808</v>
+        <v>0.3561684514700475</v>
       </c>
       <c r="AE15">
-        <v>8.5267156938324179E-2</v>
+        <v>8.5266453228886499E-2</v>
       </c>
       <c r="AF15">
-        <v>0.45909358678196133</v>
+        <v>0.45909357603519951</v>
       </c>
       <c r="AG15">
-        <v>0.44533012547866579</v>
+        <v>0.44533014050364289</v>
       </c>
       <c r="AH15">
-        <v>9.0133774746307502E-2</v>
+        <v>9.0133815025032468E-2</v>
       </c>
       <c r="AI15">
-        <v>0.44737243452525022</v>
+        <v>0.44737242180854342</v>
       </c>
       <c r="AJ15">
-        <v>0.53560264242844102</v>
+        <v>0.53560320930047478</v>
       </c>
       <c r="AK15">
-        <v>0.13606005254448769</v>
+        <v>0.13606009945592221</v>
       </c>
       <c r="AL15">
-        <v>0.42292889035933451</v>
+        <v>0.42292888125095562</v>
       </c>
       <c r="AM15">
-        <v>0.55348724423167972</v>
+        <v>0.55348727735217484</v>
       </c>
       <c r="AN15">
-        <v>0.22774902540564099</v>
+        <v>0.22774905691947431</v>
       </c>
       <c r="AO15">
-        <v>0.39303209675486078</v>
+        <v>0.39303208913517518</v>
       </c>
       <c r="AP15">
-        <v>0.65789612977627843</v>
+        <v>0.65789614440763589</v>
       </c>
       <c r="AQ15">
-        <v>0.33288180857280258</v>
+        <v>0.33288183295370788</v>
       </c>
       <c r="AR15">
-        <v>0.37984964148238431</v>
+        <v>0.37984963439841268</v>
       </c>
       <c r="AS15">
-        <v>0.6732652893878891</v>
+        <v>0.6732653046861895</v>
       </c>
       <c r="AT15">
-        <v>0.37670493129914279</v>
+        <v>0.37670495316629732</v>
       </c>
       <c r="AU15">
-        <v>0.369396498510078</v>
+        <v>0.36939648837968292</v>
       </c>
       <c r="AV15">
-        <v>0.70264653778197639</v>
+        <v>0.70264655787166108</v>
       </c>
       <c r="AW15">
-        <v>0.41065195524308212</v>
+        <v>0.41065198616882481</v>
       </c>
       <c r="AX15">
-        <v>0.36453111915687958</v>
+        <v>0.36453111139982652</v>
       </c>
       <c r="AY15">
-        <v>0.71792149471007694</v>
+        <v>0.7179215103628126</v>
       </c>
       <c r="AZ15">
-        <v>0.42595766734959561</v>
+        <v>0.42595769038004633</v>
       </c>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.25">
@@ -3210,10 +3210,10 @@
         <v>54</v>
       </c>
       <c r="D16">
-        <v>0.39719168161007562</v>
+        <v>0.39719167562527458</v>
       </c>
       <c r="E16">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -3222,139 +3222,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H16">
-        <v>0.48911168532602889</v>
+        <v>0.48911168380087788</v>
       </c>
       <c r="I16">
-        <v>8.1346985026066188E-3</v>
+        <v>8.1346996386646442E-3</v>
       </c>
       <c r="J16">
-        <v>-3.2128254400017313E-2</v>
+        <v>-3.212825016355824E-2</v>
       </c>
       <c r="K16">
-        <v>0.4930679587109788</v>
+        <v>0.49306795632266037</v>
       </c>
       <c r="L16">
-        <v>2.0290080368559619E-2</v>
+        <v>2.0290081577534199E-2</v>
       </c>
       <c r="M16">
-        <v>-4.8908083025720937E-2</v>
+        <v>-4.8908075159729968E-2</v>
       </c>
       <c r="N16">
-        <v>0.51224155285113904</v>
+        <v>0.5122415496957089</v>
       </c>
       <c r="O16">
-        <v>3.8379136430960907E-2</v>
+        <v>3.8379137192603219E-2</v>
       </c>
       <c r="P16">
-        <v>-0.1321495142724545</v>
+        <v>-0.13214950277968621</v>
       </c>
       <c r="Q16">
-        <v>0.51260037059345487</v>
+        <v>0.512600365101606</v>
       </c>
       <c r="R16">
-        <v>7.0489843936108243E-2</v>
+        <v>7.0489856395693273E-2</v>
       </c>
       <c r="S16">
-        <v>-0.1337959486829032</v>
+        <v>-0.13379592680678479</v>
       </c>
       <c r="T16">
-        <v>0.52316424972931486</v>
+        <v>0.52316424953553953</v>
       </c>
       <c r="U16">
-        <v>9.2511516930641635E-2</v>
+        <v>9.2511520942865522E-2</v>
       </c>
       <c r="V16">
-        <v>-0.18120708749362011</v>
+        <v>-0.18120708917616801</v>
       </c>
       <c r="W16">
-        <v>0.52009801256754529</v>
+        <v>0.52009801009161927</v>
       </c>
       <c r="X16">
-        <v>0.1874397842780077</v>
+        <v>0.1874397923942496</v>
       </c>
       <c r="Y16">
-        <v>-0.16770387003464651</v>
+        <v>-0.16770386191845221</v>
       </c>
       <c r="Z16">
-        <v>0.48880698455290489</v>
+        <v>0.4888069814367238</v>
       </c>
       <c r="AA16">
-        <v>0.26805416593067871</v>
+        <v>0.26805417839515178</v>
       </c>
       <c r="AB16">
-        <v>-3.1240654157292189E-2</v>
+        <v>-3.1240643095808731E-2</v>
       </c>
       <c r="AC16">
-        <v>0.4593268089288734</v>
+        <v>0.45932680320945579</v>
       </c>
       <c r="AD16">
-        <v>0.35227703366676433</v>
+        <v>0.35227704756201028</v>
       </c>
       <c r="AE16">
-        <v>8.9292872701355261E-2</v>
+        <v>8.929289337467905E-2</v>
       </c>
       <c r="AF16">
-        <v>0.4579838180565533</v>
+        <v>0.45798381174975911</v>
       </c>
       <c r="AG16">
-        <v>0.43962417099880718</v>
+        <v>0.43962418076583998</v>
       </c>
       <c r="AH16">
-        <v>9.4522768796737031E-2</v>
+        <v>9.4522791752939525E-2</v>
       </c>
       <c r="AI16">
-        <v>0.44773658939098487</v>
+        <v>0.44773658146060341</v>
       </c>
       <c r="AJ16">
-        <v>0.4586775775626446</v>
+        <v>0.45867751416328217</v>
       </c>
       <c r="AK16">
-        <v>0.13456358580573041</v>
+        <v>0.1345636136661254</v>
       </c>
       <c r="AL16">
-        <v>0.4206971572982125</v>
+        <v>0.4206971498820099</v>
       </c>
       <c r="AM16">
-        <v>0.54833072662613236</v>
+        <v>0.54833074572575402</v>
       </c>
       <c r="AN16">
-        <v>0.23600575450099401</v>
+        <v>0.23600577980826951</v>
       </c>
       <c r="AO16">
-        <v>0.38950485061243117</v>
+        <v>0.38950484441266697</v>
       </c>
       <c r="AP16">
-        <v>0.65284179811499854</v>
+        <v>0.65284181173328648</v>
       </c>
       <c r="AQ16">
-        <v>0.34486514936099449</v>
+        <v>0.3448651687301269</v>
       </c>
       <c r="AR16">
-        <v>0.37451999374486239</v>
+        <v>0.37451998723353958</v>
       </c>
       <c r="AS16">
-        <v>0.67017100935704566</v>
+        <v>0.67017102419093155</v>
       </c>
       <c r="AT16">
-        <v>0.39440695270654458</v>
+        <v>0.39440697240745998</v>
       </c>
       <c r="AU16">
-        <v>0.36484012638468438</v>
+        <v>0.36484011840604802</v>
       </c>
       <c r="AV16">
-        <v>0.70233078026627394</v>
+        <v>0.70233080020571048</v>
       </c>
       <c r="AW16">
-        <v>0.42527071049439708</v>
+        <v>0.4252707343574389</v>
       </c>
       <c r="AX16">
-        <v>0.35846925441534772</v>
+        <v>0.3584692487371795</v>
       </c>
       <c r="AY16">
-        <v>0.71833943404805678</v>
+        <v>0.71833944983393527</v>
       </c>
       <c r="AZ16">
-        <v>0.4452644167506441</v>
+        <v>0.44526443313873237</v>
       </c>
     </row>
     <row r="17" spans="1:52" x14ac:dyDescent="0.25">
@@ -3368,10 +3368,10 @@
         <v>54</v>
       </c>
       <c r="D17">
-        <v>0.40938775038778902</v>
+        <v>0.40938774679475848</v>
       </c>
       <c r="E17">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -3380,139 +3380,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H17">
-        <v>0.49015415301697451</v>
+        <v>0.49015415170874199</v>
       </c>
       <c r="I17">
-        <v>8.1298548226007572E-3</v>
+        <v>8.1298559586342467E-3</v>
       </c>
       <c r="J17">
-        <v>-3.6582284980212987E-2</v>
+        <v>-3.6582281658225579E-2</v>
       </c>
       <c r="K17">
-        <v>0.49439227983013989</v>
+        <v>0.49439227946303582</v>
       </c>
       <c r="L17">
-        <v>2.0283179563742929E-2</v>
+        <v>2.028318077342561E-2</v>
       </c>
       <c r="M17">
-        <v>-5.4604092799943778E-2</v>
+        <v>-5.4604093498480812E-2</v>
       </c>
       <c r="N17">
-        <v>0.51415244639709501</v>
+        <v>0.51415244344974065</v>
       </c>
       <c r="O17">
-        <v>3.8228219364726201E-2</v>
+        <v>3.8228220161306892E-2</v>
       </c>
       <c r="P17">
-        <v>-0.14067261097012351</v>
+        <v>-0.14067260033542681</v>
       </c>
       <c r="Q17">
-        <v>0.51581316840275793</v>
+        <v>0.51581316302172386</v>
       </c>
       <c r="R17">
-        <v>7.0196301890469881E-2</v>
+        <v>7.0196314233179957E-2</v>
       </c>
       <c r="S17">
-        <v>-0.14818844686370131</v>
+        <v>-0.14818842534719931</v>
       </c>
       <c r="T17">
-        <v>0.52471145680574249</v>
+        <v>0.52471145565519617</v>
       </c>
       <c r="U17">
-        <v>9.1332053627363186E-2</v>
+        <v>9.1332058182843401E-2</v>
       </c>
       <c r="V17">
-        <v>-0.18841560550341641</v>
+        <v>-0.18841560281711719</v>
       </c>
       <c r="W17">
-        <v>0.52197484136113825</v>
+        <v>0.52197483896541974</v>
       </c>
       <c r="X17">
-        <v>0.18414570115541509</v>
+        <v>0.1841457093605702</v>
       </c>
       <c r="Y17">
-        <v>-0.17632276146798709</v>
+        <v>-0.17632275326910291</v>
       </c>
       <c r="Z17">
-        <v>0.49073068685748189</v>
+        <v>0.49073068123049579</v>
       </c>
       <c r="AA17">
-        <v>0.26400513655024982</v>
+        <v>0.26400514917351631</v>
       </c>
       <c r="AB17">
-        <v>-3.9508510390010763E-2</v>
+        <v>-3.9508488807893753E-2</v>
       </c>
       <c r="AC17">
-        <v>0.46438703943827531</v>
+        <v>0.46438703302427697</v>
       </c>
       <c r="AD17">
-        <v>0.3413023645963188</v>
+        <v>0.34130237874552688</v>
       </c>
       <c r="AE17">
-        <v>6.9147618572639763E-2</v>
+        <v>6.9147642326625458E-2</v>
       </c>
       <c r="AF17">
-        <v>0.4650555899639211</v>
+        <v>0.46505558369937272</v>
       </c>
       <c r="AG17">
-        <v>0.42714113386318858</v>
+        <v>0.42714115055163049</v>
       </c>
       <c r="AH17">
-        <v>6.6385006526099896E-2</v>
+        <v>6.638502963959203E-2</v>
       </c>
       <c r="AI17">
-        <v>0.45506445184160199</v>
+        <v>0.45506444554228331</v>
       </c>
       <c r="AJ17">
-        <v>0.47174685409021028</v>
+        <v>0.47174725664549128</v>
       </c>
       <c r="AK17">
-        <v>0.1060623907290846</v>
+        <v>0.1060624137379409</v>
       </c>
       <c r="AL17">
-        <v>0.43200190859196308</v>
+        <v>0.43200190747507999</v>
       </c>
       <c r="AM17">
-        <v>0.53272190037726941</v>
+        <v>0.53272192081051828</v>
       </c>
       <c r="AN17">
-        <v>0.19431045832193919</v>
+        <v>0.1943104611391327</v>
       </c>
       <c r="AO17">
-        <v>0.40138541185117388</v>
+        <v>0.40138540449218629</v>
       </c>
       <c r="AP17">
-        <v>0.62785453083945186</v>
+        <v>0.62785454538242991</v>
       </c>
       <c r="AQ17">
-        <v>0.30452947036026062</v>
+        <v>0.30452949434512039</v>
       </c>
       <c r="AR17">
-        <v>0.38796959576249851</v>
+        <v>0.38796958881639593</v>
       </c>
       <c r="AS17">
-        <v>0.65060210690983367</v>
+        <v>0.65060212331947098</v>
       </c>
       <c r="AT17">
-        <v>0.35009075511671639</v>
+        <v>0.35009077690052931</v>
       </c>
       <c r="AU17">
-        <v>0.37523835138458272</v>
+        <v>0.3752383420961572</v>
       </c>
       <c r="AV17">
-        <v>0.68713815897908348</v>
+        <v>0.68713818101567581</v>
       </c>
       <c r="AW17">
-        <v>0.39194918376549698</v>
+        <v>0.3919492125221723</v>
       </c>
       <c r="AX17">
-        <v>0.36728913148177611</v>
+        <v>0.36728912310081852</v>
       </c>
       <c r="AY17">
-        <v>0.70615480634686534</v>
+        <v>0.70615482420302544</v>
       </c>
       <c r="AZ17">
-        <v>0.41770542632850249</v>
+        <v>0.41770545162945122</v>
       </c>
     </row>
     <row r="18" spans="1:52" x14ac:dyDescent="0.25">
@@ -3526,10 +3526,10 @@
         <v>54</v>
       </c>
       <c r="D18">
-        <v>0.38571122911366967</v>
+        <v>0.38571122127997648</v>
       </c>
       <c r="E18">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -3538,139 +3538,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H18">
-        <v>0.48712109902383161</v>
+        <v>0.48712109806897319</v>
       </c>
       <c r="I18">
-        <v>2.0496183791234971E-2</v>
+        <v>2.0496185520350371E-2</v>
       </c>
       <c r="J18">
-        <v>-2.3756067543613899E-2</v>
+        <v>-2.3756065729732351E-2</v>
       </c>
       <c r="K18">
-        <v>0.5000051006374735</v>
+        <v>0.50000510148231436</v>
       </c>
       <c r="L18">
-        <v>6.1550006671984847E-2</v>
+        <v>6.1550010162099489E-2</v>
       </c>
       <c r="M18">
-        <v>-7.9058614168611069E-2</v>
+        <v>-7.9058620108495695E-2</v>
       </c>
       <c r="N18">
-        <v>0.50193884353679319</v>
+        <v>0.50193884333937033</v>
       </c>
       <c r="O18">
-        <v>9.6431139342175398E-2</v>
+        <v>9.6431140492194145E-2</v>
       </c>
       <c r="P18">
-        <v>-8.751958323863368E-2</v>
+        <v>-8.7519584646252077E-2</v>
       </c>
       <c r="Q18">
-        <v>0.51286751019642263</v>
+        <v>0.51286751003858444</v>
       </c>
       <c r="R18">
-        <v>0.29575763845125252</v>
+        <v>0.29575764935243792</v>
       </c>
       <c r="S18">
-        <v>-0.13553694558072621</v>
+        <v>-0.1355369473605138</v>
       </c>
       <c r="T18">
-        <v>0.46380728393960302</v>
+        <v>0.46380728061464299</v>
       </c>
       <c r="U18">
-        <v>0.4042241232695819</v>
+        <v>0.40422413251507761</v>
       </c>
       <c r="V18">
-        <v>7.1183916496469157E-2</v>
+        <v>7.1183927818221929E-2</v>
       </c>
       <c r="W18">
-        <v>0.43293195206014629</v>
+        <v>0.43293194872240198</v>
       </c>
       <c r="X18">
-        <v>0.5504453125755322</v>
+        <v>0.550445322391375</v>
       </c>
       <c r="Y18">
-        <v>0.19076535009557491</v>
+        <v>0.1907653608871957</v>
       </c>
       <c r="Z18">
-        <v>0.41608300521560332</v>
+        <v>0.41608300233922918</v>
       </c>
       <c r="AA18">
-        <v>0.59008488652869051</v>
+        <v>0.59008489840722489</v>
       </c>
       <c r="AB18">
-        <v>0.25243138480867322</v>
+        <v>0.25243139362810141</v>
       </c>
       <c r="AC18">
-        <v>0.39082015330248132</v>
+        <v>0.39082014660804909</v>
       </c>
       <c r="AD18">
-        <v>0.68425089092951041</v>
+        <v>0.68425090756225004</v>
       </c>
       <c r="AE18">
-        <v>0.34059576714046053</v>
+        <v>0.34059578815624958</v>
       </c>
       <c r="AF18">
-        <v>0.3707911263570442</v>
+        <v>0.37079112022027427</v>
       </c>
       <c r="AG18">
-        <v>0.71423337282042221</v>
+        <v>0.71423339123057172</v>
       </c>
       <c r="AH18">
-        <v>0.40652708777689323</v>
+        <v>0.40652710599893699</v>
       </c>
       <c r="AI18">
-        <v>0.36496833500904502</v>
+        <v>0.36496834756962299</v>
       </c>
       <c r="AJ18">
-        <v>0.72858159098581288</v>
+        <v>0.7285816093583527</v>
       </c>
       <c r="AK18">
-        <v>0.42502916598843782</v>
+        <v>0.42502912403192322</v>
       </c>
       <c r="AL18">
-        <v>0.35319325504247551</v>
+        <v>0.35319323706449579</v>
       </c>
       <c r="AM18">
-        <v>0.76660222118530741</v>
+        <v>0.76660224915738506</v>
       </c>
       <c r="AN18">
-        <v>0.46147604249632479</v>
+        <v>0.46147609610972262</v>
       </c>
       <c r="AO18">
-        <v>0.35283613171208861</v>
+        <v>0.35283611150261679</v>
       </c>
       <c r="AP18">
-        <v>0.78656794768929994</v>
+        <v>0.78656797764966535</v>
       </c>
       <c r="AQ18">
-        <v>0.46247980665436988</v>
+        <v>0.46247986698914001</v>
       </c>
       <c r="AR18">
-        <v>0.36038505978024798</v>
+        <v>0.36038503536738681</v>
       </c>
       <c r="AS18">
-        <v>0.80757894231148242</v>
+        <v>0.80757897496630093</v>
       </c>
       <c r="AT18">
-        <v>0.43908841232743651</v>
+        <v>0.439088487089902</v>
       </c>
       <c r="AU18">
-        <v>0.37032900277356418</v>
+        <v>0.37032897446994922</v>
       </c>
       <c r="AV18">
-        <v>0.82314533538787604</v>
+        <v>0.8231453723348453</v>
       </c>
       <c r="AW18">
-        <v>0.4075689214923624</v>
+        <v>0.40756901073479368</v>
       </c>
       <c r="AX18">
-        <v>0.37464432429063721</v>
+        <v>0.37464428640918651</v>
       </c>
       <c r="AY18">
-        <v>0.84673031672191434</v>
+        <v>0.84673036295661552</v>
       </c>
       <c r="AZ18">
-        <v>0.39362028961660672</v>
+        <v>0.39362041088060662</v>
       </c>
     </row>
     <row r="19" spans="1:52" x14ac:dyDescent="0.25">
@@ -3684,10 +3684,10 @@
         <v>54</v>
       </c>
       <c r="D19">
-        <v>0.38214204584498229</v>
+        <v>0.38214204088911791</v>
       </c>
       <c r="E19">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -3696,139 +3696,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H19">
-        <v>0.48720312438578028</v>
+        <v>0.4872031234156875</v>
       </c>
       <c r="I19">
-        <v>1.8169230191893541E-2</v>
+        <v>1.8169231996863381E-2</v>
       </c>
       <c r="J19">
-        <v>-2.4090244565841381E-2</v>
+        <v>-2.4090242689278049E-2</v>
       </c>
       <c r="K19">
-        <v>0.49977994028783218</v>
+        <v>0.49977994164686851</v>
       </c>
       <c r="L19">
-        <v>4.794434664392333E-2</v>
+        <v>4.7944351905335858E-2</v>
       </c>
       <c r="M19">
-        <v>-7.789115949750848E-2</v>
+        <v>-7.7891167693561567E-2</v>
       </c>
       <c r="N19">
-        <v>0.50359162197650531</v>
+        <v>0.50359161639529471</v>
       </c>
       <c r="O19">
-        <v>9.5430071114505077E-2</v>
+        <v>9.5430071754044166E-2</v>
       </c>
       <c r="P19">
-        <v>-9.4758592183586718E-2</v>
+        <v>-9.4758570100078807E-2</v>
       </c>
       <c r="Q19">
-        <v>0.50506133861577363</v>
+        <v>0.50506133933278019</v>
       </c>
       <c r="R19">
-        <v>0.33944359119992179</v>
+        <v>0.33944360765532677</v>
       </c>
       <c r="S19">
-        <v>-0.1012625582487755</v>
+        <v>-0.10126256369850239</v>
       </c>
       <c r="T19">
-        <v>0.44852924319062187</v>
+        <v>0.44852924043990872</v>
       </c>
       <c r="U19">
-        <v>0.43297019119527258</v>
+        <v>0.43297019867696751</v>
       </c>
       <c r="V19">
-        <v>0.13165676007514179</v>
+        <v>0.13165676880297669</v>
       </c>
       <c r="W19">
-        <v>0.41251036484308828</v>
+        <v>0.41251036065244329</v>
       </c>
       <c r="X19">
-        <v>0.54689377653779125</v>
+        <v>0.54689379497803448</v>
       </c>
       <c r="Y19">
-        <v>0.26538264307438802</v>
+        <v>0.26538265636617359</v>
       </c>
       <c r="Z19">
-        <v>0.3995381539033474</v>
+        <v>0.39953814911488122</v>
       </c>
       <c r="AA19">
-        <v>0.59091657266339737</v>
+        <v>0.59091659071003833</v>
       </c>
       <c r="AB19">
-        <v>0.31070789785609337</v>
+        <v>0.31070791300777928</v>
       </c>
       <c r="AC19">
-        <v>0.37540463258144668</v>
+        <v>0.37540462707255923</v>
       </c>
       <c r="AD19">
-        <v>0.64961400238846734</v>
+        <v>0.64961401561186383</v>
       </c>
       <c r="AE19">
-        <v>0.39158802694322642</v>
+        <v>0.39158804344010639</v>
       </c>
       <c r="AF19">
-        <v>0.36035302096348237</v>
+        <v>0.36035301218622617</v>
       </c>
       <c r="AG19">
-        <v>0.68967568965352744</v>
+        <v>0.68967570375235265</v>
       </c>
       <c r="AH19">
-        <v>0.43945448334210219</v>
+        <v>0.43945450907157863</v>
       </c>
       <c r="AI19">
-        <v>0.35507456569155083</v>
+        <v>0.35507460529862311</v>
       </c>
       <c r="AJ19">
-        <v>0.71711783620651204</v>
+        <v>0.7171178487271288</v>
       </c>
       <c r="AK19">
-        <v>0.45572669705598551</v>
+        <v>0.4557265827695377</v>
       </c>
       <c r="AL19">
-        <v>0.34774889037667861</v>
+        <v>0.34774888144490329</v>
       </c>
       <c r="AM19">
-        <v>0.7585600298529962</v>
+        <v>0.7585600472491445</v>
       </c>
       <c r="AN19">
-        <v>0.47783706620163352</v>
+        <v>0.47783709175872979</v>
       </c>
       <c r="AO19">
-        <v>0.34690132419107472</v>
+        <v>0.34690131379264028</v>
       </c>
       <c r="AP19">
-        <v>0.78287204269784361</v>
+        <v>0.78287206107908291</v>
       </c>
       <c r="AQ19">
-        <v>0.48026471719822911</v>
+        <v>0.48026474703305128</v>
       </c>
       <c r="AR19">
-        <v>0.34921365867251292</v>
+        <v>0.34921364726943599</v>
       </c>
       <c r="AS19">
-        <v>0.81284342673757726</v>
+        <v>0.81284345006218772</v>
       </c>
       <c r="AT19">
-        <v>0.47329560430145767</v>
+        <v>0.47329563747158843</v>
       </c>
       <c r="AU19">
-        <v>0.34675497691429741</v>
+        <v>0.34675496127429117</v>
       </c>
       <c r="AV19">
-        <v>0.82346829566520174</v>
+        <v>0.82346832145839521</v>
       </c>
       <c r="AW19">
-        <v>0.48050467460297408</v>
+        <v>0.4805047202101968</v>
       </c>
       <c r="AX19">
-        <v>0.34876387694606992</v>
+        <v>0.3487638543990409</v>
       </c>
       <c r="AY19">
-        <v>0.84355646176530119</v>
+        <v>0.8435564912511343</v>
       </c>
       <c r="AZ19">
-        <v>0.47438743650092141</v>
+        <v>0.47438750339779001</v>
       </c>
     </row>
     <row r="20" spans="1:52" x14ac:dyDescent="0.25">
@@ -3842,10 +3842,10 @@
         <v>54</v>
       </c>
       <c r="D20">
-        <v>0.37551046554323381</v>
+        <v>0.37551045084276208</v>
       </c>
       <c r="E20">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -3854,139 +3854,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H20">
-        <v>0.48746894815545888</v>
+        <v>0.48746894713223882</v>
       </c>
       <c r="I20">
-        <v>1.7425025914442279E-2</v>
+        <v>1.7425027715664791E-2</v>
       </c>
       <c r="J20">
-        <v>-2.5210624954087012E-2</v>
+        <v>-2.521062285346648E-2</v>
       </c>
       <c r="K20">
-        <v>0.49731500890112551</v>
+        <v>0.4973150106726793</v>
       </c>
       <c r="L20">
-        <v>4.2953618687562312E-2</v>
+        <v>4.2953624887443587E-2</v>
       </c>
       <c r="M20">
-        <v>-6.7202189948162031E-2</v>
+        <v>-6.7202199818920033E-2</v>
       </c>
       <c r="N20">
-        <v>0.50143733893693343</v>
+        <v>0.50143733769528787</v>
       </c>
       <c r="O20">
-        <v>0.12319325492344881</v>
+        <v>0.1231932545672068</v>
       </c>
       <c r="P20">
-        <v>-8.5168737124641972E-2</v>
+        <v>-8.5168734044690123E-2</v>
       </c>
       <c r="Q20">
-        <v>0.47883892194393612</v>
+        <v>0.47883892094549702</v>
       </c>
       <c r="R20">
-        <v>0.29359125827548538</v>
+        <v>0.29359126617618969</v>
       </c>
       <c r="S20">
-        <v>1.0385040688713411E-2</v>
+        <v>1.038504268887494E-2</v>
       </c>
       <c r="T20">
-        <v>0.43938253546396722</v>
+        <v>0.43938253292612611</v>
       </c>
       <c r="U20">
-        <v>0.40913441314017018</v>
+        <v>0.40913442019973167</v>
       </c>
       <c r="V20">
-        <v>0.16671312223890239</v>
+        <v>0.1667131300601995</v>
       </c>
       <c r="W20">
-        <v>0.43011875825750678</v>
+        <v>0.4301187535699495</v>
       </c>
       <c r="X20">
-        <v>0.52590943628770381</v>
+        <v>0.52590943085993658</v>
       </c>
       <c r="Y20">
-        <v>0.2014136265641584</v>
+        <v>0.2014136422060788</v>
       </c>
       <c r="Z20">
-        <v>0.4000811353698322</v>
+        <v>0.4000811290897559</v>
       </c>
       <c r="AA20">
-        <v>0.56567024861459481</v>
+        <v>0.56567024898940366</v>
       </c>
       <c r="AB20">
-        <v>0.30899183481191</v>
+        <v>0.30899185513048327</v>
       </c>
       <c r="AC20">
-        <v>0.37856017317553109</v>
+        <v>0.37856016780275858</v>
       </c>
       <c r="AD20">
-        <v>0.62487128034003758</v>
+        <v>0.62487129272396458</v>
       </c>
       <c r="AE20">
-        <v>0.38139676541062623</v>
+        <v>0.38139678163848501</v>
       </c>
       <c r="AF20">
-        <v>0.3685543436191091</v>
+        <v>0.3685543041129819</v>
       </c>
       <c r="AG20">
-        <v>0.64827440872503983</v>
+        <v>0.6482744214240167</v>
       </c>
       <c r="AH20">
-        <v>0.41370969945143138</v>
+        <v>0.41370982330948303</v>
       </c>
       <c r="AI20">
-        <v>0.35081711638328977</v>
+        <v>0.35081710354308371</v>
       </c>
       <c r="AJ20">
-        <v>0.69737652846681453</v>
+        <v>0.69737653868672178</v>
       </c>
       <c r="AK20">
-        <v>0.46870492804754349</v>
+        <v>0.46870496609958229</v>
       </c>
       <c r="AL20">
-        <v>0.34507386481663782</v>
+        <v>0.34507385775079158</v>
       </c>
       <c r="AM20">
-        <v>0.73433348612910221</v>
+        <v>0.7343335010839277</v>
       </c>
       <c r="AN20">
-        <v>0.48583833243855751</v>
+        <v>0.48583835236430589</v>
       </c>
       <c r="AO20">
-        <v>0.35048610115543261</v>
+        <v>0.35048609487118931</v>
       </c>
       <c r="AP20">
-        <v>0.7599303312899317</v>
+        <v>0.75993035044492085</v>
       </c>
       <c r="AQ20">
-        <v>0.4694202807533206</v>
+        <v>0.46942029848702199</v>
       </c>
       <c r="AR20">
-        <v>0.33361650387502573</v>
+        <v>0.33361649316294772</v>
       </c>
       <c r="AS20">
-        <v>0.78119831105733895</v>
+        <v>0.78119833317724097</v>
       </c>
       <c r="AT20">
-        <v>0.51941391332903275</v>
+        <v>0.5194139430593876</v>
       </c>
       <c r="AU20">
-        <v>0.33635450068294293</v>
+        <v>0.33635448426594899</v>
       </c>
       <c r="AV20">
-        <v>0.799336450346392</v>
+        <v>0.79933647730469148</v>
       </c>
       <c r="AW20">
-        <v>0.51149553953150706</v>
+        <v>0.5114955859836674</v>
       </c>
       <c r="AX20">
-        <v>0.3379979382747163</v>
+        <v>0.33799792532659961</v>
       </c>
       <c r="AY20">
-        <v>0.81547302786796427</v>
+        <v>0.81547305384162028</v>
       </c>
       <c r="AZ20">
-        <v>0.5066515670492453</v>
+        <v>0.50665160425129874</v>
       </c>
     </row>
     <row r="21" spans="1:52" x14ac:dyDescent="0.25">
@@ -4000,10 +4000,10 @@
         <v>54</v>
       </c>
       <c r="D21">
-        <v>0.43434065960212731</v>
+        <v>0.43434065232158142</v>
       </c>
       <c r="E21">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -4012,139 +4012,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H21">
-        <v>0.48649930624382381</v>
+        <v>0.48649930551418419</v>
       </c>
       <c r="I21">
-        <v>4.1089356843310047E-2</v>
+        <v>4.1089357104549203E-2</v>
       </c>
       <c r="J21">
-        <v>-2.1174623460256042E-2</v>
+        <v>-2.1174622580284349E-2</v>
       </c>
       <c r="K21">
-        <v>0.4905968691329825</v>
+        <v>0.49059686788647783</v>
       </c>
       <c r="L21">
-        <v>6.3580327580583074E-2</v>
+        <v>6.3580325921866243E-2</v>
       </c>
       <c r="M21">
-        <v>-3.8506677642957107E-2</v>
+        <v>-3.8506674555550152E-2</v>
       </c>
       <c r="N21">
-        <v>0.51321579703134468</v>
+        <v>0.51321580025013525</v>
       </c>
       <c r="O21">
-        <v>0.32012539162894332</v>
+        <v>0.32012539766793102</v>
       </c>
       <c r="P21">
-        <v>-0.1370404822597894</v>
+        <v>-0.13704049894549189</v>
       </c>
       <c r="Q21">
-        <v>0.47423506590125869</v>
+        <v>0.47423506714687419</v>
       </c>
       <c r="R21">
-        <v>0.35679843171217679</v>
+        <v>0.35679845100015067</v>
       </c>
       <c r="S21">
-        <v>2.9142550496288239E-2</v>
+        <v>2.9142543519039429E-2</v>
       </c>
       <c r="T21">
-        <v>0.45357315470192272</v>
+        <v>0.45357315696257589</v>
       </c>
       <c r="U21">
-        <v>0.43531180943972658</v>
+        <v>0.43531183336966128</v>
       </c>
       <c r="V21">
-        <v>0.11207045341260451</v>
+        <v>0.112070442437223</v>
       </c>
       <c r="W21">
-        <v>0.44599359271177219</v>
+        <v>0.44599360134513072</v>
       </c>
       <c r="X21">
-        <v>0.48179017786302342</v>
+        <v>0.48179017966276061</v>
       </c>
       <c r="Y21">
-        <v>0.1415339034862747</v>
+        <v>0.1415338686180094</v>
       </c>
       <c r="Z21">
-        <v>0.43663237007772993</v>
+        <v>0.43663236927926768</v>
       </c>
       <c r="AA21">
-        <v>0.58345730401322471</v>
+        <v>0.5834573058116852</v>
       </c>
       <c r="AB21">
-        <v>0.1769481958881558</v>
+        <v>0.17694819713363871</v>
       </c>
       <c r="AC21">
-        <v>0.42347697862149491</v>
+        <v>0.42347697142431923</v>
       </c>
       <c r="AD21">
-        <v>0.66450886397384723</v>
+        <v>0.66450886404713516</v>
       </c>
       <c r="AE21">
-        <v>0.22567303564964711</v>
+        <v>0.22567306026999859</v>
       </c>
       <c r="AF21">
-        <v>0.40317831663427439</v>
+        <v>0.40317830812077521</v>
       </c>
       <c r="AG21">
-        <v>0.70488011949186391</v>
+        <v>0.70488013071076816</v>
       </c>
       <c r="AH21">
-        <v>0.29810304139179461</v>
+        <v>0.29810306944639081</v>
       </c>
       <c r="AI21">
-        <v>0.39230699758791338</v>
+        <v>0.39230697921566537</v>
       </c>
       <c r="AJ21">
-        <v>0.75040187871077224</v>
+        <v>0.75040190553772756</v>
       </c>
       <c r="AK21">
-        <v>0.33544682788979829</v>
+        <v>0.33544688876497297</v>
       </c>
       <c r="AL21">
-        <v>0.38547256273374109</v>
+        <v>0.38547253188076269</v>
       </c>
       <c r="AM21">
-        <v>0.77983324933465425</v>
+        <v>0.77983329045044658</v>
       </c>
       <c r="AN21">
-        <v>0.358431520517835</v>
+        <v>0.35843162183169991</v>
       </c>
       <c r="AO21">
-        <v>0.3890510151476711</v>
+        <v>0.38905097098166791</v>
       </c>
       <c r="AP21">
-        <v>0.80629398277440045</v>
+        <v>0.80629403259132426</v>
       </c>
       <c r="AQ21">
-        <v>0.34640200339408489</v>
+        <v>0.34640215048495532</v>
       </c>
       <c r="AR21">
-        <v>0.39717891088670698</v>
+        <v>0.39717885581831369</v>
       </c>
       <c r="AS21">
-        <v>0.83626434818344608</v>
+        <v>0.83626441605163448</v>
       </c>
       <c r="AT21">
-        <v>0.31867495096664972</v>
+        <v>0.31867513874989101</v>
       </c>
       <c r="AU21">
-        <v>0.39925508125006859</v>
+        <v>0.39925499771984801</v>
       </c>
       <c r="AV21">
-        <v>0.87020554853114895</v>
+        <v>0.87020563886719238</v>
       </c>
       <c r="AW21">
-        <v>0.31136396955093099</v>
+        <v>0.31136425663507711</v>
       </c>
       <c r="AX21">
-        <v>0.39764975560799248</v>
+        <v>0.39764965047254808</v>
       </c>
       <c r="AY21">
-        <v>0.89009248901896054</v>
+        <v>0.8900925892396544</v>
       </c>
       <c r="AZ21">
-        <v>0.31683170444123188</v>
+        <v>0.31683206434129779</v>
       </c>
     </row>
     <row r="22" spans="1:52" x14ac:dyDescent="0.25">
@@ -4158,10 +4158,10 @@
         <v>54</v>
       </c>
       <c r="D22">
-        <v>0.45203959391939391</v>
+        <v>0.45203957681490292</v>
       </c>
       <c r="E22">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -4170,139 +4170,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H22">
-        <v>0.48665555471799099</v>
+        <v>0.4866555540427932</v>
       </c>
       <c r="I22">
-        <v>4.1026671695396533E-2</v>
+        <v>4.1026671925903813E-2</v>
       </c>
       <c r="J22">
-        <v>-2.1853971970998819E-2</v>
+        <v>-2.1853971330517589E-2</v>
       </c>
       <c r="K22">
-        <v>0.491298054238268</v>
+        <v>0.49129805264720638</v>
       </c>
       <c r="L22">
-        <v>6.3591509970379323E-2</v>
+        <v>6.3591508212408221E-2</v>
       </c>
       <c r="M22">
-        <v>-4.1524660839614168E-2</v>
+        <v>-4.1524656305807588E-2</v>
       </c>
       <c r="N22">
-        <v>0.5139603526543699</v>
+        <v>0.51396035478691848</v>
       </c>
       <c r="O22">
-        <v>0.31878409915890599</v>
+        <v>0.31878410466119439</v>
       </c>
       <c r="P22">
-        <v>-0.14042674129951571</v>
+        <v>-0.1404267532979486</v>
       </c>
       <c r="Q22">
-        <v>0.47349708993492601</v>
+        <v>0.47349709207633928</v>
       </c>
       <c r="R22">
-        <v>0.35436105668175688</v>
+        <v>0.35436107488577129</v>
       </c>
       <c r="S22">
-        <v>3.2250244775841208E-2</v>
+        <v>3.2250234049591639E-2</v>
       </c>
       <c r="T22">
-        <v>0.45659063054140231</v>
+        <v>0.45659063390360649</v>
       </c>
       <c r="U22">
-        <v>0.42679028908400751</v>
+        <v>0.42679031111471821</v>
       </c>
       <c r="V22">
-        <v>0.1002674167234207</v>
+        <v>0.1002674014771492</v>
       </c>
       <c r="W22">
-        <v>0.44982049643952893</v>
+        <v>0.44982049346353398</v>
       </c>
       <c r="X22">
-        <v>0.46922262700080752</v>
+        <v>0.46922263202055509</v>
       </c>
       <c r="Y22">
-        <v>0.12675269611685791</v>
+        <v>0.12675270654116469</v>
       </c>
       <c r="Z22">
-        <v>0.44216862645213351</v>
+        <v>0.44216861858901929</v>
       </c>
       <c r="AA22">
-        <v>0.57083393422514428</v>
+        <v>0.57083394284656386</v>
       </c>
       <c r="AB22">
-        <v>0.15585649536508961</v>
+        <v>0.1558565235520819</v>
       </c>
       <c r="AC22">
-        <v>0.43551896080835151</v>
+        <v>0.43551894628582433</v>
       </c>
       <c r="AD22">
-        <v>0.6426272872669806</v>
+        <v>0.64262729699870169</v>
       </c>
       <c r="AE22">
-        <v>0.1810250657068796</v>
+        <v>0.18102511856949299</v>
       </c>
       <c r="AF22">
-        <v>0.41380038501761712</v>
+        <v>0.41380036399826647</v>
       </c>
       <c r="AG22">
-        <v>0.69052443553571319</v>
+        <v>0.69052445315413813</v>
       </c>
       <c r="AH22">
-        <v>0.26067326575409622</v>
+        <v>0.26067333938362069</v>
       </c>
       <c r="AI22">
-        <v>0.40276409165002558</v>
+        <v>0.40276406655863911</v>
       </c>
       <c r="AJ22">
-        <v>0.73747330854418713</v>
+        <v>0.73747333842517881</v>
       </c>
       <c r="AK22">
-        <v>0.29959170344723662</v>
+        <v>0.29959178910908563</v>
       </c>
       <c r="AL22">
-        <v>0.39690458016353419</v>
+        <v>0.39690454034187062</v>
       </c>
       <c r="AM22">
-        <v>0.77989723216402262</v>
+        <v>0.77989728855700691</v>
       </c>
       <c r="AN22">
-        <v>0.31973247533750698</v>
+        <v>0.31973261027946459</v>
       </c>
       <c r="AO22">
-        <v>0.39732490338402121</v>
+        <v>0.39732484091998688</v>
       </c>
       <c r="AP22">
-        <v>0.81159297482506532</v>
+        <v>0.81159304609665495</v>
       </c>
       <c r="AQ22">
-        <v>0.31818215186229809</v>
+        <v>0.31818236468385169</v>
       </c>
       <c r="AR22">
-        <v>0.40009442063896511</v>
+        <v>0.40009432452480742</v>
       </c>
       <c r="AS22">
-        <v>0.84401065846625167</v>
+        <v>0.84401074571749501</v>
       </c>
       <c r="AT22">
-        <v>0.30851287217781859</v>
+        <v>0.30851320262251958</v>
       </c>
       <c r="AU22">
-        <v>0.39994639267154147</v>
+        <v>0.39994626939223538</v>
       </c>
       <c r="AV22">
-        <v>0.86368421626472025</v>
+        <v>0.86368430984430544</v>
       </c>
       <c r="AW22">
-        <v>0.30929233473357381</v>
+        <v>0.3092927589052239</v>
       </c>
       <c r="AX22">
-        <v>0.40156531473617901</v>
+        <v>0.40156516657238478</v>
       </c>
       <c r="AY22">
-        <v>0.88025483370620483</v>
+        <v>0.88025492692307128</v>
       </c>
       <c r="AZ22">
-        <v>0.30359242665530661</v>
+        <v>0.30359293903141071</v>
       </c>
     </row>
     <row r="23" spans="1:52" x14ac:dyDescent="0.25">
@@ -4316,10 +4316,10 @@
         <v>54</v>
       </c>
       <c r="D23">
-        <v>0.38684311063141641</v>
+        <v>0.38684310745954331</v>
       </c>
       <c r="E23">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -4328,139 +4328,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H23">
-        <v>0.48641006007626009</v>
+        <v>0.48641005936616932</v>
       </c>
       <c r="I23">
-        <v>2.5990674199879878E-2</v>
+        <v>2.599067460579307E-2</v>
       </c>
       <c r="J23">
-        <v>-2.075998764515289E-2</v>
+        <v>-2.0759986857734409E-2</v>
       </c>
       <c r="K23">
-        <v>0.50255194622171784</v>
+        <v>0.5025519588730426</v>
       </c>
       <c r="L23">
-        <v>0.1250768615259352</v>
+        <v>0.12507688718599019</v>
       </c>
       <c r="M23">
-        <v>-9.0065791659010769E-2</v>
+        <v>-9.0065848923880837E-2</v>
       </c>
       <c r="N23">
-        <v>0.46716517125688389</v>
+        <v>0.46716518394357581</v>
       </c>
       <c r="O23">
-        <v>0.24000080640490801</v>
+        <v>0.2400008046141906</v>
       </c>
       <c r="P23">
-        <v>5.7964283717133122E-2</v>
+        <v>5.796423039403005E-2</v>
       </c>
       <c r="Q23">
-        <v>0.45483476525401467</v>
+        <v>0.45483477530257133</v>
       </c>
       <c r="R23">
-        <v>0.32180316787372909</v>
+        <v>0.32180314286705991</v>
       </c>
       <c r="S23">
-        <v>0.10708105243739741</v>
+        <v>0.10708101158103581</v>
       </c>
       <c r="T23">
-        <v>0.4077453216677896</v>
+        <v>0.40774532742691078</v>
       </c>
       <c r="U23">
-        <v>0.54020349373340926</v>
+        <v>0.54020347392341006</v>
       </c>
       <c r="V23">
-        <v>0.28236190816712081</v>
+        <v>0.28236188632339199</v>
       </c>
       <c r="W23">
-        <v>0.38206011588720729</v>
+        <v>0.38206011638941961</v>
       </c>
       <c r="X23">
-        <v>0.62745618298539951</v>
+        <v>0.62745618374168477</v>
       </c>
       <c r="Y23">
-        <v>0.36993885188782522</v>
+        <v>0.36993884874603961</v>
       </c>
       <c r="Z23">
-        <v>0.37027111353144371</v>
+        <v>0.37027110970414018</v>
       </c>
       <c r="AA23">
-        <v>0.6821213281629086</v>
+        <v>0.68212134181132</v>
       </c>
       <c r="AB23">
-        <v>0.40812804974572597</v>
+        <v>0.40812806061198847</v>
       </c>
       <c r="AC23">
-        <v>0.36015452088274208</v>
+        <v>0.36015450608704758</v>
       </c>
       <c r="AD23">
-        <v>0.74161636673477305</v>
+        <v>0.74161640023449138</v>
       </c>
       <c r="AE23">
-        <v>0.44002175237835323</v>
+        <v>0.44002179706192729</v>
       </c>
       <c r="AF23">
-        <v>0.35179268756629872</v>
+        <v>0.35179266119591007</v>
       </c>
       <c r="AG23">
-        <v>0.77088810976110167</v>
+        <v>0.77088815132433186</v>
       </c>
       <c r="AH23">
-        <v>0.46565103053022178</v>
+        <v>0.46565110946645127</v>
       </c>
       <c r="AI23">
-        <v>0.34831477714526382</v>
+        <v>0.34831472075114639</v>
       </c>
       <c r="AJ23">
-        <v>0.81684739029796805</v>
+        <v>0.81684744005195664</v>
       </c>
       <c r="AK23">
-        <v>0.47604944811635519</v>
+        <v>0.47604961645089389</v>
       </c>
       <c r="AL23">
-        <v>0.34807887759774098</v>
+        <v>0.34807879322085788</v>
       </c>
       <c r="AM23">
-        <v>0.84709277860876486</v>
+        <v>0.84709285835910508</v>
       </c>
       <c r="AN23">
-        <v>0.4766983703181959</v>
+        <v>0.47669862263851048</v>
       </c>
       <c r="AO23">
-        <v>0.35524127854079218</v>
+        <v>0.35524114995298622</v>
       </c>
       <c r="AP23">
-        <v>0.88225342552783137</v>
+        <v>0.8822534735005072</v>
       </c>
       <c r="AQ23">
-        <v>0.45495381775046112</v>
+        <v>0.45495421081313969</v>
       </c>
       <c r="AR23">
-        <v>0.3611786889595503</v>
+        <v>0.36117853945863793</v>
       </c>
       <c r="AS23">
-        <v>0.89525940391817027</v>
+        <v>0.89525944172493466</v>
       </c>
       <c r="AT23">
-        <v>0.43651517225991382</v>
+        <v>0.43651563770860979</v>
       </c>
       <c r="AU23">
-        <v>0.36678142781348722</v>
+        <v>0.36678127089583862</v>
       </c>
       <c r="AV23">
-        <v>0.91118000838705382</v>
+        <v>0.9111800344299541</v>
       </c>
       <c r="AW23">
-        <v>0.41884805339375769</v>
+        <v>0.41884854930881299</v>
       </c>
       <c r="AX23">
-        <v>0.37458118072150381</v>
+        <v>0.37458100451114429</v>
       </c>
       <c r="AY23">
-        <v>0.92846474012299496</v>
+        <v>0.9284647390034414</v>
       </c>
       <c r="AZ23">
-        <v>0.39361937346418963</v>
+        <v>0.39361994275437701</v>
       </c>
     </row>
     <row r="24" spans="1:52" x14ac:dyDescent="0.25">
@@ -4474,10 +4474,10 @@
         <v>54</v>
       </c>
       <c r="D24">
-        <v>0.45670108643464991</v>
+        <v>0.45670107287750311</v>
       </c>
       <c r="E24">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -4486,139 +4486,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H24">
-        <v>0.49084085590133492</v>
+        <v>0.49084085513375858</v>
       </c>
       <c r="I24">
-        <v>4.0241060451025046E-3</v>
+        <v>4.0241071440696441E-3</v>
       </c>
       <c r="J24">
-        <v>-3.9445118665311578E-2</v>
+        <v>-3.9445117653746968E-2</v>
       </c>
       <c r="K24">
-        <v>0.51345877487269043</v>
+        <v>0.51345877484122404</v>
       </c>
       <c r="L24">
-        <v>2.3860091435280121E-2</v>
+        <v>2.3860097489060261E-2</v>
       </c>
       <c r="M24">
-        <v>-0.13750307392636649</v>
+        <v>-0.13750307622271951</v>
       </c>
       <c r="N24">
-        <v>0.51721857221126921</v>
+        <v>0.51721856997490345</v>
       </c>
       <c r="O24">
-        <v>4.0779241932935029E-2</v>
+        <v>4.0779240981021148E-2</v>
       </c>
       <c r="P24">
-        <v>-0.15429810777929881</v>
+        <v>-0.1542981002565757</v>
       </c>
       <c r="Q24">
-        <v>0.51077633512413068</v>
+        <v>0.51077633383101606</v>
       </c>
       <c r="R24">
-        <v>6.9302444643982941E-2</v>
+        <v>6.9302428101138291E-2</v>
       </c>
       <c r="S24">
-        <v>-0.12580297072886051</v>
+        <v>-0.1258029674204946</v>
       </c>
       <c r="T24">
-        <v>0.51221064385192561</v>
+        <v>0.51221064075853806</v>
       </c>
       <c r="U24">
-        <v>0.10409418996357681</v>
+        <v>0.10409419721890779</v>
       </c>
       <c r="V24">
-        <v>-0.13219155533749821</v>
+        <v>-0.13219154458994839</v>
       </c>
       <c r="W24">
-        <v>0.49557177641210631</v>
+        <v>0.49557177611268732</v>
       </c>
       <c r="X24">
-        <v>0.16688937517765831</v>
+        <v>0.1668893858889838</v>
       </c>
       <c r="Y24">
-        <v>-5.9800571242552537E-2</v>
+        <v>-5.9800571894684899E-2</v>
       </c>
       <c r="Z24">
-        <v>0.51067299154166479</v>
+        <v>0.5106729902749807</v>
       </c>
       <c r="AA24">
-        <v>0.21632663366324351</v>
+        <v>0.21632665903603021</v>
       </c>
       <c r="AB24">
-        <v>-0.12566425862777861</v>
+        <v>-0.12566425519846411</v>
       </c>
       <c r="AC24">
-        <v>0.48967582619882072</v>
+        <v>0.48967581810034022</v>
       </c>
       <c r="AD24">
-        <v>0.39030100817815128</v>
+        <v>0.39030103657485199</v>
       </c>
       <c r="AE24">
-        <v>-3.5122388929873079E-2</v>
+        <v>-3.5122356939814352E-2</v>
       </c>
       <c r="AF24">
-        <v>0.44117349952279822</v>
+        <v>0.4411734822367307</v>
       </c>
       <c r="AG24">
-        <v>0.59899742886894713</v>
+        <v>0.59899747296008976</v>
       </c>
       <c r="AH24">
-        <v>0.15942691998486419</v>
+        <v>0.15942698392741531</v>
       </c>
       <c r="AI24">
-        <v>0.42342689939123779</v>
+        <v>0.42342687976036358</v>
       </c>
       <c r="AJ24">
-        <v>0.658126669164246</v>
+        <v>0.65812670963580477</v>
       </c>
       <c r="AK24">
-        <v>0.22593317665289819</v>
+        <v>0.22593324672109569</v>
       </c>
       <c r="AL24">
-        <v>0.41325087404006111</v>
+        <v>0.41325084583123528</v>
       </c>
       <c r="AM24">
-        <v>0.70870551161424822</v>
+        <v>0.70870556728871015</v>
       </c>
       <c r="AN24">
-        <v>0.26265842062076178</v>
+        <v>0.26265851974479298</v>
       </c>
       <c r="AO24">
-        <v>0.419353732307365</v>
+        <v>0.41935369270067457</v>
       </c>
       <c r="AP24">
-        <v>0.77381711405560583</v>
+        <v>0.77381716315058457</v>
       </c>
       <c r="AQ24">
-        <v>0.24062645307844921</v>
+        <v>0.2406265954169047</v>
       </c>
       <c r="AR24">
-        <v>0.4371730471141535</v>
+        <v>0.4371729881487203</v>
       </c>
       <c r="AS24">
-        <v>0.82899126543991186</v>
+        <v>0.82899130668780474</v>
       </c>
       <c r="AT24">
-        <v>0.17440852219163039</v>
+        <v>0.1744087433223932</v>
       </c>
       <c r="AU24">
-        <v>0.45040906262009389</v>
+        <v>0.45040900246086091</v>
       </c>
       <c r="AV24">
-        <v>0.85405412322545304</v>
+        <v>0.85405416196784523</v>
       </c>
       <c r="AW24">
-        <v>0.1236621607726464</v>
+        <v>0.1236623933407259</v>
       </c>
       <c r="AX24">
-        <v>0.46692033756607199</v>
+        <v>0.4669202749641192</v>
       </c>
       <c r="AY24">
-        <v>0.87383134195692902</v>
+        <v>0.87383137772526409</v>
       </c>
       <c r="AZ24">
-        <v>5.7889422342563217E-2</v>
+        <v>5.7889673623331188E-2</v>
       </c>
     </row>
     <row r="25" spans="1:52" x14ac:dyDescent="0.25">
@@ -4632,10 +4632,10 @@
         <v>54</v>
       </c>
       <c r="D25">
-        <v>0.46292553105899958</v>
+        <v>0.46292552083936178</v>
       </c>
       <c r="E25">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -4644,139 +4644,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H25">
-        <v>0.4909172440776281</v>
+        <v>0.49091724280103488</v>
       </c>
       <c r="I25">
-        <v>4.3094230432864089E-3</v>
+        <v>4.3094241242033196E-3</v>
       </c>
       <c r="J25">
-        <v>-3.9777296594468603E-2</v>
+        <v>-3.9777293418867182E-2</v>
       </c>
       <c r="K25">
-        <v>0.51552829204001127</v>
+        <v>0.51552829400907429</v>
       </c>
       <c r="L25">
-        <v>3.2378311250585212E-2</v>
+        <v>3.2378317972490363E-2</v>
       </c>
       <c r="M25">
-        <v>-0.14668964214482461</v>
+        <v>-0.14668965337197251</v>
       </c>
       <c r="N25">
-        <v>0.5170112988978578</v>
+        <v>0.51701129808444102</v>
       </c>
       <c r="O25">
-        <v>5.5858196619136491E-2</v>
+        <v>5.5858193124414202E-2</v>
       </c>
       <c r="P25">
-        <v>-0.1533578638397971</v>
+        <v>-0.1533578625891889</v>
       </c>
       <c r="Q25">
-        <v>0.50825812721050745</v>
+        <v>0.50825812554403116</v>
       </c>
       <c r="R25">
-        <v>9.1165869063928096E-2</v>
+        <v>9.1165855068491619E-2</v>
       </c>
       <c r="S25">
-        <v>-0.1146524771681655</v>
+        <v>-0.11465247225525919</v>
       </c>
       <c r="T25">
-        <v>0.50728782560199037</v>
+        <v>0.50728782983649912</v>
       </c>
       <c r="U25">
-        <v>0.10053802017923801</v>
+        <v>0.1005380178253785</v>
       </c>
       <c r="V25">
-        <v>-0.11040132119996469</v>
+        <v>-0.1104013421500827</v>
       </c>
       <c r="W25">
-        <v>0.50363016532486304</v>
+        <v>0.50363016413669259</v>
       </c>
       <c r="X25">
-        <v>0.1492382330199343</v>
+        <v>0.1492382391986273</v>
       </c>
       <c r="Y25">
-        <v>-9.4466973290522532E-2</v>
+        <v>-9.4466970452539684E-2</v>
       </c>
       <c r="Z25">
-        <v>0.51989461052946928</v>
+        <v>0.51989460840551438</v>
       </c>
       <c r="AA25">
-        <v>0.1952794039534389</v>
+        <v>0.1952794106328104</v>
       </c>
       <c r="AB25">
-        <v>-0.16652272291310249</v>
+        <v>-0.16652271598573321</v>
       </c>
       <c r="AC25">
-        <v>0.51009626442061784</v>
+        <v>0.51009625851038742</v>
       </c>
       <c r="AD25">
-        <v>0.40824623509049718</v>
+        <v>0.4082462603235556</v>
       </c>
       <c r="AE25">
-        <v>-0.1235094222071005</v>
+        <v>-0.123509398416531</v>
       </c>
       <c r="AF25">
-        <v>0.49013716119695527</v>
+        <v>0.49013715325021678</v>
       </c>
       <c r="AG25">
-        <v>0.4804746026009773</v>
+        <v>0.48047462727115808</v>
       </c>
       <c r="AH25">
-        <v>-3.708598462337484E-2</v>
+        <v>-3.7085953145773648E-2</v>
       </c>
       <c r="AI25">
-        <v>0.4360107644005235</v>
+        <v>0.43601074863349581</v>
       </c>
       <c r="AJ25">
-        <v>0.65204145359185739</v>
+        <v>0.65204148838583498</v>
       </c>
       <c r="AK25">
-        <v>0.1791094753449648</v>
+        <v>0.1791095328053324</v>
       </c>
       <c r="AL25">
-        <v>0.42708482958390043</v>
+        <v>0.42708481084661309</v>
       </c>
       <c r="AM25">
-        <v>0.68089886193698468</v>
+        <v>0.68089890479021342</v>
       </c>
       <c r="AN25">
-        <v>0.21260536822661169</v>
+        <v>0.21260543567343521</v>
       </c>
       <c r="AO25">
-        <v>0.41891227686980481</v>
+        <v>0.41891224321986908</v>
       </c>
       <c r="AP25">
-        <v>0.73885717335773005</v>
+        <v>0.73885723289342775</v>
       </c>
       <c r="AQ25">
-        <v>0.24242481607851149</v>
+        <v>0.24242493598919079</v>
       </c>
       <c r="AR25">
-        <v>0.42902420474469199</v>
+        <v>0.42902416900941431</v>
       </c>
       <c r="AS25">
-        <v>0.78417302334471717</v>
+        <v>0.78417307356711508</v>
       </c>
       <c r="AT25">
-        <v>0.20534391953058251</v>
+        <v>0.20534405023493801</v>
       </c>
       <c r="AU25">
-        <v>0.44214590277087018</v>
+        <v>0.44214580868698261</v>
       </c>
       <c r="AV25">
-        <v>0.83532572885583645</v>
+        <v>0.83532577171903133</v>
       </c>
       <c r="AW25">
-        <v>0.1557113190798044</v>
+        <v>0.15571167041122411</v>
       </c>
       <c r="AX25">
-        <v>0.45845970228363692</v>
+        <v>0.45845963383867938</v>
       </c>
       <c r="AY25">
-        <v>0.85457085353377538</v>
+        <v>0.85457089495924188</v>
       </c>
       <c r="AZ25">
-        <v>9.232544023041396E-2</v>
+        <v>9.2325707394342413E-2</v>
       </c>
     </row>
     <row r="26" spans="1:52" x14ac:dyDescent="0.25">
@@ -4790,10 +4790,10 @@
         <v>54</v>
       </c>
       <c r="D26">
-        <v>0.4786279528763045</v>
+        <v>0.47862794806971332</v>
       </c>
       <c r="E26">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -4802,139 +4802,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H26">
-        <v>0.4898144279153937</v>
+        <v>0.48981442694343841</v>
       </c>
       <c r="I26">
-        <v>4.5115758022381547E-3</v>
+        <v>4.5115768336430051E-3</v>
       </c>
       <c r="J26">
-        <v>-3.5097712286716702E-2</v>
+        <v>-3.5097710407953453E-2</v>
       </c>
       <c r="K26">
-        <v>0.51599420586704747</v>
+        <v>0.51599420568509224</v>
       </c>
       <c r="L26">
-        <v>4.2986577335233478E-2</v>
+        <v>4.2986583380857153E-2</v>
       </c>
       <c r="M26">
-        <v>-0.14879105688454899</v>
+        <v>-0.14879105855500549</v>
       </c>
       <c r="N26">
-        <v>0.51128512070217924</v>
+        <v>0.51128511984929792</v>
       </c>
       <c r="O26">
-        <v>5.3846063107582109E-2</v>
+        <v>5.3846064717660853E-2</v>
       </c>
       <c r="P26">
-        <v>-0.12803031401314871</v>
+        <v>-0.12803031259691211</v>
       </c>
       <c r="Q26">
-        <v>0.50025646497664622</v>
+        <v>0.50025646437219007</v>
       </c>
       <c r="R26">
-        <v>9.3828776130196023E-2</v>
+        <v>9.3828767648290956E-2</v>
       </c>
       <c r="S26">
-        <v>-7.9896874659333081E-2</v>
+        <v>-7.9896874242994298E-2</v>
       </c>
       <c r="T26">
-        <v>0.50995449625790423</v>
+        <v>0.50995450679224119</v>
       </c>
       <c r="U26">
-        <v>0.12756442766076559</v>
+        <v>0.12756443271744219</v>
       </c>
       <c r="V26">
-        <v>-0.12227197322723481</v>
+        <v>-0.1222720215886136</v>
       </c>
       <c r="W26">
-        <v>0.50260912822016146</v>
+        <v>0.50260912624619092</v>
       </c>
       <c r="X26">
-        <v>0.17382783107113589</v>
+        <v>0.1738278405175451</v>
       </c>
       <c r="Y26">
-        <v>-9.0310684316499315E-2</v>
+        <v>-9.0310678106499523E-2</v>
       </c>
       <c r="Z26">
-        <v>0.47256909666798252</v>
+        <v>0.47256909220429938</v>
       </c>
       <c r="AA26">
-        <v>0.38262073098669658</v>
+        <v>0.38262074819531389</v>
       </c>
       <c r="AB26">
-        <v>3.6102404273648747E-2</v>
+        <v>3.6102420411032059E-2</v>
       </c>
       <c r="AC26">
-        <v>0.48644632571732888</v>
+        <v>0.48644632095289669</v>
       </c>
       <c r="AD26">
-        <v>0.5394091989830625</v>
+        <v>0.53940897783352815</v>
       </c>
       <c r="AE26">
-        <v>-2.162712005884888E-2</v>
+        <v>-2.1627102204836639E-2</v>
       </c>
       <c r="AF26">
-        <v>0.45010823219807422</v>
+        <v>0.45010822142943402</v>
       </c>
       <c r="AG26">
-        <v>0.59617405090056796</v>
+        <v>0.59617407411652901</v>
       </c>
       <c r="AH26">
-        <v>0.12541476290537859</v>
+        <v>0.12541480281147671</v>
       </c>
       <c r="AI26">
-        <v>0.42492224233635478</v>
+        <v>0.42492222560698001</v>
       </c>
       <c r="AJ26">
-        <v>0.68599492626470093</v>
+        <v>0.68599496888052602</v>
       </c>
       <c r="AK26">
-        <v>0.22055014877228521</v>
+        <v>0.22055020845188661</v>
       </c>
       <c r="AL26">
-        <v>0.42332909760507781</v>
+        <v>0.42332907289395078</v>
       </c>
       <c r="AM26">
-        <v>0.73349701285873659</v>
+        <v>0.7334970670812091</v>
       </c>
       <c r="AN26">
-        <v>0.22621452131920969</v>
+        <v>0.22621460992759199</v>
       </c>
       <c r="AO26">
-        <v>0.43054999418000578</v>
+        <v>0.43054995046795791</v>
       </c>
       <c r="AP26">
-        <v>0.79978645290582151</v>
+        <v>0.79978650369228454</v>
       </c>
       <c r="AQ26">
-        <v>0.1993860266546244</v>
+        <v>0.1993861876788191</v>
       </c>
       <c r="AR26">
-        <v>0.44104811147467521</v>
+        <v>0.44104805806330788</v>
       </c>
       <c r="AS26">
-        <v>0.8323180962943092</v>
+        <v>0.83231814727166953</v>
       </c>
       <c r="AT26">
-        <v>0.1598328053354878</v>
+        <v>0.15983300686615901</v>
       </c>
       <c r="AU26">
-        <v>0.45416677251806759</v>
+        <v>0.45416670947591542</v>
       </c>
       <c r="AV26">
-        <v>0.85149513052569836</v>
+        <v>0.85149517605887826</v>
       </c>
       <c r="AW26">
-        <v>0.1091875732390951</v>
+        <v>0.10918781841140179</v>
       </c>
       <c r="AX26">
-        <v>0.47396244400570048</v>
+        <v>0.47396237694877652</v>
       </c>
       <c r="AY26">
-        <v>0.87951965063471194</v>
+        <v>0.87951969372879579</v>
       </c>
       <c r="AZ26">
-        <v>2.9955480566373541E-2</v>
+        <v>2.995575295616499E-2</v>
       </c>
     </row>
     <row r="27" spans="1:52" x14ac:dyDescent="0.25">
@@ -4948,10 +4948,10 @@
         <v>54</v>
       </c>
       <c r="D27">
-        <v>0.43045241404720758</v>
+        <v>0.4304523982536731</v>
       </c>
       <c r="E27">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -4960,139 +4960,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H27">
-        <v>0.49152318222970087</v>
+        <v>0.49152318070346518</v>
       </c>
       <c r="I27">
-        <v>4.4682365466739427E-3</v>
+        <v>4.4682375780392691E-3</v>
       </c>
       <c r="J27">
-        <v>-4.2397773388044818E-2</v>
+        <v>-4.2397769087745271E-2</v>
       </c>
       <c r="K27">
-        <v>0.51712216160679403</v>
+        <v>0.51712216059881844</v>
       </c>
       <c r="L27">
-        <v>3.9949619159763812E-2</v>
+        <v>3.9949624703860209E-2</v>
       </c>
       <c r="M27">
-        <v>-0.15383300861581761</v>
+        <v>-0.153833006585951</v>
       </c>
       <c r="N27">
-        <v>0.51199770028545044</v>
+        <v>0.5119976990112689</v>
       </c>
       <c r="O27">
-        <v>4.9336512840770792E-2</v>
+        <v>4.9336513866740428E-2</v>
       </c>
       <c r="P27">
-        <v>-0.13115286184412711</v>
+        <v>-0.13115285868488791</v>
       </c>
       <c r="Q27">
-        <v>0.50245388225549292</v>
+        <v>0.50245387931436558</v>
       </c>
       <c r="R27">
-        <v>8.1227026943181069E-2</v>
+        <v>8.122701919031361E-2</v>
       </c>
       <c r="S27">
-        <v>-8.9353757599278938E-2</v>
+        <v>-8.9353747261256111E-2</v>
       </c>
       <c r="T27">
-        <v>0.510174480100408</v>
+        <v>0.51017447946150207</v>
       </c>
       <c r="U27">
-        <v>0.1063328784705342</v>
+        <v>0.1063328803850716</v>
       </c>
       <c r="V27">
-        <v>-0.1231433059374802</v>
+        <v>-0.1231433055534126</v>
       </c>
       <c r="W27">
-        <v>0.50353866348298382</v>
+        <v>0.50353866094610389</v>
       </c>
       <c r="X27">
-        <v>0.13592962497852931</v>
+        <v>0.13592962857297439</v>
       </c>
       <c r="Y27">
-        <v>-9.415957885176808E-2</v>
+        <v>-9.4159570290525949E-2</v>
       </c>
       <c r="Z27">
-        <v>0.4772989297118666</v>
+        <v>0.4772989283818555</v>
       </c>
       <c r="AA27">
-        <v>0.26541631577655361</v>
+        <v>0.26541632753512762</v>
       </c>
       <c r="AB27">
-        <v>1.6865610991641911E-2</v>
+        <v>1.6865614307032949E-2</v>
       </c>
       <c r="AC27">
-        <v>0.48742849737944832</v>
+        <v>0.48742849161418339</v>
       </c>
       <c r="AD27">
-        <v>0.38408904700765623</v>
+        <v>0.38408881360330999</v>
       </c>
       <c r="AE27">
-        <v>-2.553581902148705E-2</v>
+        <v>-2.5535796693541741E-2</v>
       </c>
       <c r="AF27">
-        <v>0.45489002696255909</v>
+        <v>0.45489002061356748</v>
       </c>
       <c r="AG27">
-        <v>0.4502150183085093</v>
+        <v>0.4502150401179883</v>
       </c>
       <c r="AH27">
-        <v>0.1067170811013983</v>
+        <v>0.10671710472772521</v>
       </c>
       <c r="AI27">
-        <v>0.41344870113575238</v>
+        <v>0.41344868328915307</v>
       </c>
       <c r="AJ27">
-        <v>0.56123293425674947</v>
+        <v>0.56123297396148419</v>
       </c>
       <c r="AK27">
-        <v>0.26213123495200819</v>
+        <v>0.26213129706204358</v>
       </c>
       <c r="AL27">
-        <v>0.40339228042029618</v>
+        <v>0.4033922589223683</v>
       </c>
       <c r="AM27">
-        <v>0.58878083120857216</v>
+        <v>0.58878087275230917</v>
       </c>
       <c r="AN27">
-        <v>0.29765731605259721</v>
+        <v>0.29765738941777869</v>
       </c>
       <c r="AO27">
-        <v>0.40133419542249538</v>
+        <v>0.40133416406006961</v>
       </c>
       <c r="AP27">
-        <v>0.64731181509278524</v>
+        <v>0.64731187605004159</v>
       </c>
       <c r="AQ27">
-        <v>0.30436050077153037</v>
+        <v>0.30436060803439802</v>
       </c>
       <c r="AR27">
-        <v>0.39838639721305152</v>
+        <v>0.39838636079699791</v>
       </c>
       <c r="AS27">
-        <v>0.66912407871426427</v>
+        <v>0.66912416153496734</v>
       </c>
       <c r="AT27">
-        <v>0.31459199577835639</v>
+        <v>0.31459211944413568</v>
       </c>
       <c r="AU27">
-        <v>0.40433435816753999</v>
+        <v>0.40433430782719321</v>
       </c>
       <c r="AV27">
-        <v>0.6965298643550879</v>
+        <v>0.69652994170331572</v>
       </c>
       <c r="AW27">
-        <v>0.29381747684173459</v>
+        <v>0.29381765134603582</v>
       </c>
       <c r="AX27">
-        <v>0.40772676446344258</v>
+        <v>0.40772671303798902</v>
       </c>
       <c r="AY27">
-        <v>0.71413434239129692</v>
+        <v>0.7141344176503388</v>
       </c>
       <c r="AZ27">
-        <v>0.28189050314478081</v>
+        <v>0.28189068281315582</v>
       </c>
     </row>
     <row r="28" spans="1:52" x14ac:dyDescent="0.25">
@@ -5106,10 +5106,10 @@
         <v>54</v>
       </c>
       <c r="D28">
-        <v>0.43423574797661779</v>
+        <v>0.43423573076663607</v>
       </c>
       <c r="E28">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -5118,139 +5118,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H28">
-        <v>0.49045831879986868</v>
+        <v>0.49045831741188117</v>
       </c>
       <c r="I28">
-        <v>4.2715912371162901E-3</v>
+        <v>4.2715923181940729E-3</v>
       </c>
       <c r="J28">
-        <v>-3.784190472112952E-2</v>
+        <v>-3.7841901065829971E-2</v>
       </c>
       <c r="K28">
-        <v>0.513635414085997</v>
+        <v>0.5136354144099472</v>
       </c>
       <c r="L28">
-        <v>3.0064623539895589E-2</v>
+        <v>3.0064629815460871E-2</v>
       </c>
       <c r="M28">
-        <v>-0.13832858407417589</v>
+        <v>-0.1383285880651218</v>
       </c>
       <c r="N28">
-        <v>0.51589101565095041</v>
+        <v>0.5158910136161432</v>
       </c>
       <c r="O28">
-        <v>5.1581456367723599E-2</v>
+        <v>5.1581452997081938E-2</v>
       </c>
       <c r="P28">
-        <v>-0.1484779268095717</v>
+        <v>-0.14847792022206541</v>
       </c>
       <c r="Q28">
-        <v>0.50726596908348853</v>
+        <v>0.50726596707778426</v>
       </c>
       <c r="R28">
-        <v>7.9996517159706126E-2</v>
+        <v>7.9996504907564603E-2</v>
       </c>
       <c r="S28">
-        <v>-0.1105304560027613</v>
+        <v>-0.1105304495465612</v>
       </c>
       <c r="T28">
-        <v>0.50594369030665443</v>
+        <v>0.5059436918607414</v>
       </c>
       <c r="U28">
-        <v>8.6902813175912641E-2</v>
+        <v>8.6902810870610914E-2</v>
       </c>
       <c r="V28">
-        <v>-0.10473490231742801</v>
+        <v>-0.10473491145973381</v>
       </c>
       <c r="W28">
-        <v>0.5013718557118596</v>
+        <v>0.5013718556781761</v>
       </c>
       <c r="X28">
-        <v>0.1191872070461673</v>
+        <v>0.11918720953643409</v>
       </c>
       <c r="Y28">
-        <v>-8.4908990926140557E-2</v>
+        <v>-8.4908993081280179E-2</v>
       </c>
       <c r="Z28">
-        <v>0.51309959035175345</v>
+        <v>0.51309958942939127</v>
       </c>
       <c r="AA28">
-        <v>0.14361305235956759</v>
+        <v>0.14361305456682419</v>
       </c>
       <c r="AB28">
-        <v>-0.13677070765079161</v>
+        <v>-0.1367707060718564</v>
       </c>
       <c r="AC28">
-        <v>0.50727419780884797</v>
+        <v>0.5072741940598402</v>
       </c>
       <c r="AD28">
-        <v>0.28287169268106721</v>
+        <v>0.28287170756567331</v>
       </c>
       <c r="AE28">
-        <v>-0.1117303173615906</v>
+        <v>-0.1117303029179762</v>
       </c>
       <c r="AF28">
-        <v>0.4892539073006138</v>
+        <v>0.48925390079922632</v>
       </c>
       <c r="AG28">
-        <v>0.3426432595422696</v>
+        <v>0.34264327525957949</v>
       </c>
       <c r="AH28">
-        <v>-3.349959485105114E-2</v>
+        <v>-3.349956968306729E-2</v>
       </c>
       <c r="AI28">
-        <v>0.43155938203771321</v>
+        <v>0.43155936541878759</v>
       </c>
       <c r="AJ28">
-        <v>0.54606203016531918</v>
+        <v>0.54606207488773217</v>
       </c>
       <c r="AK28">
-        <v>0.19547600202477011</v>
+        <v>0.1954760622715763</v>
       </c>
       <c r="AL28">
-        <v>0.41582130500402043</v>
+        <v>0.41582128377673733</v>
       </c>
       <c r="AM28">
-        <v>0.56536704139065574</v>
+        <v>0.56536708570777972</v>
       </c>
       <c r="AN28">
-        <v>0.25339280145519438</v>
+        <v>0.25339287610184941</v>
       </c>
       <c r="AO28">
-        <v>0.41237240590702878</v>
+        <v>0.41237237974817598</v>
       </c>
       <c r="AP28">
-        <v>0.5850188627355899</v>
+        <v>0.5850189082855568</v>
       </c>
       <c r="AQ28">
-        <v>0.26572643567535642</v>
+        <v>0.26572652737854929</v>
       </c>
       <c r="AR28">
-        <v>0.41098568409237213</v>
+        <v>0.4109856534941897</v>
       </c>
       <c r="AS28">
-        <v>0.63471064049487125</v>
+        <v>0.63471069612208186</v>
       </c>
       <c r="AT28">
-        <v>0.27036663591825438</v>
+        <v>0.27036674323538751</v>
       </c>
       <c r="AU28">
-        <v>0.41686930362727281</v>
+        <v>0.41686926646424488</v>
       </c>
       <c r="AV28">
-        <v>0.6658325874848765</v>
+        <v>0.66583265353209842</v>
       </c>
       <c r="AW28">
-        <v>0.24920426205017859</v>
+        <v>0.24920439471795311</v>
       </c>
       <c r="AX28">
-        <v>0.41629913972875809</v>
+        <v>0.41629909374093449</v>
       </c>
       <c r="AY28">
-        <v>0.69344590242982163</v>
+        <v>0.69344597674342612</v>
       </c>
       <c r="AZ28">
-        <v>0.25130323487400208</v>
+        <v>0.25130339872573659</v>
       </c>
     </row>
     <row r="29" spans="1:52" x14ac:dyDescent="0.25">
@@ -5264,10 +5264,10 @@
         <v>54</v>
       </c>
       <c r="D29">
-        <v>0.42830593424911062</v>
+        <v>0.42830591702343612</v>
       </c>
       <c r="E29">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -5276,139 +5276,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H29">
-        <v>0.49109875151938293</v>
+        <v>0.49109875028303801</v>
       </c>
       <c r="I29">
-        <v>4.2739176383839173E-3</v>
+        <v>4.2739187198790329E-3</v>
       </c>
       <c r="J29">
-        <v>-4.0553326876614677E-2</v>
+        <v>-4.0553323869142788E-2</v>
       </c>
       <c r="K29">
-        <v>0.51580068780360755</v>
+        <v>0.51580068747582641</v>
       </c>
       <c r="L29">
-        <v>3.0101609073948321E-2</v>
+        <v>3.010161535960287E-2</v>
       </c>
       <c r="M29">
-        <v>-0.1479538162195814</v>
+        <v>-0.14795381723129719</v>
       </c>
       <c r="N29">
-        <v>0.51788896269479301</v>
+        <v>0.5178889607240168</v>
       </c>
       <c r="O29">
-        <v>5.1594011440552652E-2</v>
+        <v>5.159400811555015E-2</v>
       </c>
       <c r="P29">
-        <v>-0.15743990045793591</v>
+        <v>-0.15743989414484519</v>
       </c>
       <c r="Q29">
-        <v>0.51019934872703798</v>
+        <v>0.51019934720418114</v>
       </c>
       <c r="R29">
-        <v>8.0198404108143717E-2</v>
+        <v>8.0198392049107614E-2</v>
       </c>
       <c r="S29">
-        <v>-0.12338240862939261</v>
+        <v>-0.1233824043914946</v>
       </c>
       <c r="T29">
-        <v>0.50768941055962935</v>
+        <v>0.50768941362305908</v>
       </c>
       <c r="U29">
-        <v>8.6993281029002834E-2</v>
+        <v>8.6993278540946517E-2</v>
       </c>
       <c r="V29">
-        <v>-0.11226507714031531</v>
+        <v>-0.1122650929425321</v>
       </c>
       <c r="W29">
-        <v>0.50308242283971394</v>
+        <v>0.50308242258930802</v>
       </c>
       <c r="X29">
-        <v>0.1191538987768315</v>
+        <v>0.1191539009786237</v>
       </c>
       <c r="Y29">
-        <v>-9.217840080306676E-2</v>
+        <v>-9.2178402100686757E-2</v>
       </c>
       <c r="Z29">
-        <v>0.51391605663294826</v>
+        <v>0.51391605492551817</v>
       </c>
       <c r="AA29">
-        <v>0.14333903311070281</v>
+        <v>0.14333903470550299</v>
       </c>
       <c r="AB29">
-        <v>-0.14017573173242789</v>
+        <v>-0.1401757267375508</v>
       </c>
       <c r="AC29">
-        <v>0.50914488190950336</v>
+        <v>0.5091448789121229</v>
       </c>
       <c r="AD29">
-        <v>0.27954022387911559</v>
+        <v>0.27954023813186901</v>
       </c>
       <c r="AE29">
-        <v>-0.1197166476653018</v>
+        <v>-0.1197166368532586</v>
       </c>
       <c r="AF29">
-        <v>0.49254501416219909</v>
+        <v>0.49254500861050549</v>
       </c>
       <c r="AG29">
-        <v>0.34010804505163578</v>
+        <v>0.34010806018411949</v>
       </c>
       <c r="AH29">
-        <v>-4.7758584417506571E-2</v>
+        <v>-4.7758563081416808E-2</v>
       </c>
       <c r="AI29">
-        <v>0.42740971677830891</v>
+        <v>0.42740970129471262</v>
       </c>
       <c r="AJ29">
-        <v>0.54378180221090877</v>
+        <v>0.54378184739365087</v>
       </c>
       <c r="AK29">
-        <v>0.21084603881324121</v>
+        <v>0.21084609406124169</v>
       </c>
       <c r="AL29">
-        <v>0.41211150955870213</v>
+        <v>0.41211149004804498</v>
       </c>
       <c r="AM29">
-        <v>0.56086920279862285</v>
+        <v>0.56086924701387175</v>
       </c>
       <c r="AN29">
-        <v>0.26673410807023251</v>
+        <v>0.26673417590672621</v>
       </c>
       <c r="AO29">
-        <v>0.40467316118618352</v>
+        <v>0.40467313636363811</v>
       </c>
       <c r="AP29">
-        <v>0.58045257393691019</v>
+        <v>0.58045261855820107</v>
       </c>
       <c r="AQ29">
-        <v>0.29311776172071929</v>
+        <v>0.2931178468116154</v>
       </c>
       <c r="AR29">
-        <v>0.40242034631081619</v>
+        <v>0.40242031529106759</v>
       </c>
       <c r="AS29">
-        <v>0.63050714257378848</v>
+        <v>0.63050719538782085</v>
       </c>
       <c r="AT29">
-        <v>0.30076538012438409</v>
+        <v>0.30076548560564648</v>
       </c>
       <c r="AU29">
-        <v>0.40499617321696502</v>
+        <v>0.40499612125089041</v>
       </c>
       <c r="AV29">
-        <v>0.66303492553637677</v>
+        <v>0.66303498902719538</v>
       </c>
       <c r="AW29">
-        <v>0.2916632986213416</v>
+        <v>0.29166347821874211</v>
       </c>
       <c r="AX29">
-        <v>0.40270974325315562</v>
+        <v>0.40270969764904518</v>
       </c>
       <c r="AY29">
-        <v>0.69040204188488485</v>
+        <v>0.69040211651373895</v>
       </c>
       <c r="AZ29">
-        <v>0.2996887411334816</v>
+        <v>0.29968889769792301</v>
       </c>
     </row>
     <row r="30" spans="1:52" x14ac:dyDescent="0.25">
@@ -5422,10 +5422,10 @@
         <v>54</v>
       </c>
       <c r="D30">
-        <v>0.42836598283845218</v>
+        <v>0.42836596726858722</v>
       </c>
       <c r="E30">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -5434,139 +5434,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H30">
-        <v>0.49056835026501422</v>
+        <v>0.49056834881260408</v>
       </c>
       <c r="I30">
-        <v>4.2682062254995046E-3</v>
+        <v>4.268207306704408E-3</v>
       </c>
       <c r="J30">
-        <v>-3.831418182318809E-2</v>
+        <v>-3.831417789801763E-2</v>
       </c>
       <c r="K30">
-        <v>0.51470086938864601</v>
+        <v>0.51470087047308333</v>
       </c>
       <c r="L30">
-        <v>2.9796361649277681E-2</v>
+        <v>2.9796367855983049E-2</v>
       </c>
       <c r="M30">
-        <v>-0.14302718790381119</v>
+        <v>-0.14302719526659141</v>
       </c>
       <c r="N30">
-        <v>0.51761869495375812</v>
+        <v>0.51761869376080105</v>
       </c>
       <c r="O30">
-        <v>5.1097530884575248E-2</v>
+        <v>5.109752756434871E-2</v>
       </c>
       <c r="P30">
-        <v>-0.15614759837233461</v>
+        <v>-0.15614759556024069</v>
       </c>
       <c r="Q30">
-        <v>0.5095751340266671</v>
+        <v>0.50957513242787911</v>
       </c>
       <c r="R30">
-        <v>7.8903000420392222E-2</v>
+        <v>7.8902987929326818E-2</v>
       </c>
       <c r="S30">
-        <v>-0.12049862851248461</v>
+        <v>-0.1204986238320105</v>
       </c>
       <c r="T30">
-        <v>0.50843246116609753</v>
+        <v>0.50843246323739255</v>
       </c>
       <c r="U30">
-        <v>8.583229403234871E-2</v>
+        <v>8.5832292205604177E-2</v>
       </c>
       <c r="V30">
-        <v>-0.11542928046734501</v>
+        <v>-0.115429291985469</v>
       </c>
       <c r="W30">
-        <v>0.50282164538063201</v>
+        <v>0.50282164463750589</v>
       </c>
       <c r="X30">
-        <v>0.1170728819946687</v>
+        <v>0.1170728838830707</v>
       </c>
       <c r="Y30">
-        <v>-9.097631206091919E-2</v>
+        <v>-9.0976311190799408E-2</v>
       </c>
       <c r="Z30">
-        <v>0.51704836713102298</v>
+        <v>0.51704836684593791</v>
       </c>
       <c r="AA30">
-        <v>0.14011365562926559</v>
+        <v>0.14011365677110471</v>
       </c>
       <c r="AB30">
-        <v>-0.15390521041131441</v>
+        <v>-0.1539052115419052</v>
       </c>
       <c r="AC30">
-        <v>0.51268397971054358</v>
+        <v>0.51268398072305643</v>
       </c>
       <c r="AD30">
-        <v>0.27337111888778792</v>
+        <v>0.27337113233537369</v>
       </c>
       <c r="AE30">
-        <v>-0.1350466831810582</v>
+        <v>-0.13504668996925831</v>
       </c>
       <c r="AF30">
-        <v>0.49585815305899078</v>
+        <v>0.49585815085217699</v>
       </c>
       <c r="AG30">
-        <v>0.33550754304124969</v>
+        <v>0.33550755697075307</v>
       </c>
       <c r="AH30">
-        <v>-6.1618431112419048E-2</v>
+        <v>-6.1618424221266052E-2</v>
       </c>
       <c r="AI30">
-        <v>0.43037387782571401</v>
+        <v>0.43037386437466169</v>
       </c>
       <c r="AJ30">
-        <v>0.53741179082747981</v>
+        <v>0.53741183338190779</v>
       </c>
       <c r="AK30">
-        <v>0.20021368233568659</v>
+        <v>0.20021373055609271</v>
       </c>
       <c r="AL30">
-        <v>0.41562949455532727</v>
+        <v>0.41562947753326968</v>
       </c>
       <c r="AM30">
-        <v>0.55389722456647306</v>
+        <v>0.5538972656355764</v>
       </c>
       <c r="AN30">
-        <v>0.25418407903060369</v>
+        <v>0.25418413856555933</v>
       </c>
       <c r="AO30">
-        <v>0.40870432100148019</v>
+        <v>0.40870429919817902</v>
       </c>
       <c r="AP30">
-        <v>0.5719122784040479</v>
+        <v>0.57191231868804926</v>
       </c>
       <c r="AQ30">
-        <v>0.27866226840155078</v>
+        <v>0.2786623438566127</v>
       </c>
       <c r="AR30">
-        <v>0.40610755915014018</v>
+        <v>0.40610753566305707</v>
       </c>
       <c r="AS30">
-        <v>0.62381267524270245</v>
+        <v>0.62381272095988349</v>
       </c>
       <c r="AT30">
-        <v>0.28782913077550948</v>
+        <v>0.2878292114540254</v>
       </c>
       <c r="AU30">
-        <v>0.40607026527137008</v>
+        <v>0.40607023809085852</v>
       </c>
       <c r="AV30">
-        <v>0.65874692065484475</v>
+        <v>0.65874697620220535</v>
       </c>
       <c r="AW30">
-        <v>0.28789339018815191</v>
+        <v>0.28789348391854802</v>
       </c>
       <c r="AX30">
-        <v>0.40188037506755819</v>
+        <v>0.40188034000265699</v>
       </c>
       <c r="AY30">
-        <v>0.68488138508211382</v>
+        <v>0.6848814517713655</v>
       </c>
       <c r="AZ30">
-        <v>0.30260014931532342</v>
+        <v>0.30260026933995637</v>
       </c>
     </row>
     <row r="31" spans="1:52" x14ac:dyDescent="0.25">
@@ -5580,10 +5580,10 @@
         <v>54</v>
       </c>
       <c r="D31">
-        <v>0.43156295318636789</v>
+        <v>0.43156293853259431</v>
       </c>
       <c r="E31">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -5592,139 +5592,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H31">
-        <v>0.49153778706848872</v>
+        <v>0.49153778604134418</v>
       </c>
       <c r="I31">
-        <v>4.2588073478485589E-3</v>
+        <v>4.2588084306390828E-3</v>
       </c>
       <c r="J31">
-        <v>-4.2422741215078393E-2</v>
+        <v>-4.2422739102868798E-2</v>
       </c>
       <c r="K31">
-        <v>0.51511182289253643</v>
+        <v>0.51511182237071529</v>
       </c>
       <c r="L31">
-        <v>2.934379951341792E-2</v>
+        <v>2.9343805695007271E-2</v>
       </c>
       <c r="M31">
-        <v>-0.14491231685552011</v>
+        <v>-0.14491231699162521</v>
       </c>
       <c r="N31">
-        <v>0.51706185718216091</v>
+        <v>0.51706185522135195</v>
       </c>
       <c r="O31">
-        <v>5.0393432873455102E-2</v>
+        <v>5.039342970641103E-2</v>
       </c>
       <c r="P31">
-        <v>-0.1537228337438859</v>
+        <v>-0.15372282746792071</v>
       </c>
       <c r="Q31">
-        <v>0.50895500715006758</v>
+        <v>0.50895500478890598</v>
       </c>
       <c r="R31">
-        <v>7.6915187121059048E-2</v>
+        <v>7.6915174422480304E-2</v>
       </c>
       <c r="S31">
-        <v>-0.11785106946828761</v>
+        <v>-0.1178510613871207</v>
       </c>
       <c r="T31">
-        <v>0.50720373751275649</v>
+        <v>0.50720373951734909</v>
       </c>
       <c r="U31">
-        <v>8.4214272057643647E-2</v>
+        <v>8.4214271387480055E-2</v>
       </c>
       <c r="V31">
-        <v>-0.1102408660278711</v>
+        <v>-0.1102408772198878</v>
       </c>
       <c r="W31">
-        <v>0.5015370170926623</v>
+        <v>0.50153701570115816</v>
       </c>
       <c r="X31">
-        <v>0.11402698584245199</v>
+        <v>0.1140269879618679</v>
       </c>
       <c r="Y31">
-        <v>-8.5539583889990667E-2</v>
+        <v>-8.553958021073535E-2</v>
       </c>
       <c r="Z31">
-        <v>0.51327177177469507</v>
+        <v>0.51327177025134885</v>
       </c>
       <c r="AA31">
-        <v>0.13535266672202731</v>
+        <v>0.13535266822345679</v>
       </c>
       <c r="AB31">
-        <v>-0.13736251335144309</v>
+        <v>-0.13736250908203851</v>
       </c>
       <c r="AC31">
-        <v>0.50896645114546035</v>
+        <v>0.50896644628641663</v>
       </c>
       <c r="AD31">
-        <v>0.26113938896819738</v>
+        <v>0.26113940437003502</v>
       </c>
       <c r="AE31">
-        <v>-0.1193058994781326</v>
+        <v>-0.1193058809055404</v>
       </c>
       <c r="AF31">
-        <v>0.49240108883206429</v>
+        <v>0.49240108384361941</v>
       </c>
       <c r="AG31">
-        <v>0.32652637382786792</v>
+        <v>0.32652639004692169</v>
       </c>
       <c r="AH31">
-        <v>-4.7607132409206533E-2</v>
+        <v>-4.7607113703182789E-2</v>
       </c>
       <c r="AI31">
-        <v>0.43184864312999821</v>
+        <v>0.43184862943743813</v>
       </c>
       <c r="AJ31">
-        <v>0.5290370001838085</v>
+        <v>0.52903704329030399</v>
       </c>
       <c r="AK31">
-        <v>0.19420506203296989</v>
+        <v>0.19420511125112391</v>
       </c>
       <c r="AL31">
-        <v>0.41531307485617819</v>
+        <v>0.41531305787830869</v>
       </c>
       <c r="AM31">
-        <v>0.54743171204040375</v>
+        <v>0.54743175404362066</v>
       </c>
       <c r="AN31">
-        <v>0.25542254903204847</v>
+        <v>0.25542260827834701</v>
       </c>
       <c r="AO31">
-        <v>0.40832568516423928</v>
+        <v>0.40832566701495587</v>
       </c>
       <c r="AP31">
-        <v>0.56073128304814768</v>
+        <v>0.56073132238258361</v>
       </c>
       <c r="AQ31">
-        <v>0.28022837561489577</v>
+        <v>0.28022843809663361</v>
       </c>
       <c r="AR31">
-        <v>0.40284074076993243</v>
+        <v>0.40284072052227871</v>
       </c>
       <c r="AS31">
-        <v>0.61434595549521542</v>
+        <v>0.61434599200753937</v>
       </c>
       <c r="AT31">
-        <v>0.29944601812110871</v>
+        <v>0.29944608684325258</v>
       </c>
       <c r="AU31">
-        <v>0.4047374832315439</v>
+        <v>0.4047374779618787</v>
       </c>
       <c r="AV31">
-        <v>0.6562354190144466</v>
+        <v>0.65623546321071902</v>
       </c>
       <c r="AW31">
-        <v>0.29294318178999251</v>
+        <v>0.29294320096314153</v>
       </c>
       <c r="AX31">
-        <v>0.39901834935250208</v>
+        <v>0.39901832416401373</v>
       </c>
       <c r="AY31">
-        <v>0.68048616849060528</v>
+        <v>0.68048622493990485</v>
       </c>
       <c r="AZ31">
-        <v>0.31262369790353478</v>
+        <v>0.31262378337214419</v>
       </c>
     </row>
     <row r="32" spans="1:52" x14ac:dyDescent="0.25">
@@ -5738,10 +5738,10 @@
         <v>54</v>
       </c>
       <c r="D32">
-        <v>0.44034820542876751</v>
+        <v>0.44034818632816891</v>
       </c>
       <c r="E32">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -5750,139 +5750,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H32">
-        <v>0.49094532016184578</v>
+        <v>0.49094531879273978</v>
       </c>
       <c r="I32">
-        <v>4.2818080040885054E-3</v>
+        <v>4.2818090844515266E-3</v>
       </c>
       <c r="J32">
-        <v>-3.9930359939206357E-2</v>
+        <v>-3.9930356365712238E-2</v>
       </c>
       <c r="K32">
-        <v>0.51548311618794729</v>
+        <v>0.51548311532580215</v>
       </c>
       <c r="L32">
-        <v>3.0627409550839198E-2</v>
+        <v>3.0627415906930969E-2</v>
       </c>
       <c r="M32">
-        <v>-0.1465127467827731</v>
+        <v>-0.14651274541339099</v>
       </c>
       <c r="N32">
-        <v>0.51817797464646886</v>
+        <v>0.5181779725838469</v>
       </c>
       <c r="O32">
-        <v>5.2596778047859338E-2</v>
+        <v>5.2596774592268643E-2</v>
       </c>
       <c r="P32">
-        <v>-0.15867130046508671</v>
+        <v>-0.15867129371685629</v>
       </c>
       <c r="Q32">
-        <v>0.51032694379816457</v>
+        <v>0.51032694204872675</v>
       </c>
       <c r="R32">
-        <v>8.2482889436295115E-2</v>
+        <v>8.2482877231539797E-2</v>
       </c>
       <c r="S32">
-        <v>-0.1238106440316538</v>
+        <v>-0.123810638727119</v>
       </c>
       <c r="T32">
-        <v>0.50806061535316327</v>
+        <v>0.50806061549492787</v>
       </c>
       <c r="U32">
-        <v>8.9582347797478978E-2</v>
+        <v>8.9582344690760762E-2</v>
       </c>
       <c r="V32">
-        <v>-0.1138376360943303</v>
+        <v>-0.1138376392837093</v>
       </c>
       <c r="W32">
-        <v>0.50237617463211603</v>
+        <v>0.50237617360562326</v>
       </c>
       <c r="X32">
-        <v>0.12422767308070359</v>
+        <v>0.12422767615545829</v>
       </c>
       <c r="Y32">
-        <v>-8.9044001999902242E-2</v>
+        <v>-8.9043999877861185E-2</v>
       </c>
       <c r="Z32">
-        <v>0.51703597477103735</v>
+        <v>0.51703597322344408</v>
       </c>
       <c r="AA32">
-        <v>0.15152849795969039</v>
+        <v>0.15152850102178211</v>
       </c>
       <c r="AB32">
-        <v>-0.15370217589589791</v>
+        <v>-0.15370217142916551</v>
       </c>
       <c r="AC32">
-        <v>0.50590073542233382</v>
+        <v>0.5059007312918451</v>
       </c>
       <c r="AD32">
-        <v>0.29776500972150638</v>
+        <v>0.29776502611641409</v>
       </c>
       <c r="AE32">
-        <v>-0.1046709616488484</v>
+        <v>-0.1046709459425882</v>
       </c>
       <c r="AF32">
-        <v>0.48898233617644671</v>
+        <v>0.48898232929545232</v>
       </c>
       <c r="AG32">
-        <v>0.35654928979417089</v>
+        <v>0.35654930790963058</v>
       </c>
       <c r="AH32">
-        <v>-3.2059657977283093E-2</v>
+        <v>-3.2059631136027417E-2</v>
       </c>
       <c r="AI32">
-        <v>0.43172607364412813</v>
+        <v>0.431726054635098</v>
       </c>
       <c r="AJ32">
-        <v>0.56041558804054958</v>
+        <v>0.5604156369961133</v>
       </c>
       <c r="AK32">
-        <v>0.1947871721389815</v>
+        <v>0.19478724131629449</v>
       </c>
       <c r="AL32">
-        <v>0.41594602117936469</v>
+        <v>0.41594599518745379</v>
       </c>
       <c r="AM32">
-        <v>0.57913463323317738</v>
+        <v>0.57913468376737831</v>
       </c>
       <c r="AN32">
-        <v>0.25285255574778492</v>
+        <v>0.25285264757430409</v>
       </c>
       <c r="AO32">
-        <v>0.40978096617440662</v>
+        <v>0.40978093295553092</v>
       </c>
       <c r="AP32">
-        <v>0.60311179266697335</v>
+        <v>0.60311184947792773</v>
       </c>
       <c r="AQ32">
-        <v>0.2748833047793221</v>
+        <v>0.27488342082252831</v>
       </c>
       <c r="AR32">
-        <v>0.41177486850295719</v>
+        <v>0.41177483104277618</v>
       </c>
       <c r="AS32">
-        <v>0.65195024138525581</v>
+        <v>0.65195030876561899</v>
       </c>
       <c r="AT32">
-        <v>0.26755114029377491</v>
+        <v>0.26755127201627182</v>
       </c>
       <c r="AU32">
-        <v>0.42084939671058119</v>
+        <v>0.42084934920345041</v>
       </c>
       <c r="AV32">
-        <v>0.68873739549867397</v>
+        <v>0.68873747212875491</v>
       </c>
       <c r="AW32">
-        <v>0.23502528348344109</v>
+        <v>0.23502545447041071</v>
       </c>
       <c r="AX32">
-        <v>0.42450027034088672</v>
+        <v>0.42450020718699538</v>
       </c>
       <c r="AY32">
-        <v>0.72336410701100906</v>
+        <v>0.72336418677244108</v>
       </c>
       <c r="AZ32">
-        <v>0.2216042435995759</v>
+        <v>0.22160447411245959</v>
       </c>
     </row>
     <row r="33" spans="1:52" x14ac:dyDescent="0.25">
@@ -5896,10 +5896,10 @@
         <v>54</v>
       </c>
       <c r="D33">
-        <v>0.43564505322639019</v>
+        <v>0.43564503574727731</v>
       </c>
       <c r="E33">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -5908,139 +5908,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H33">
-        <v>0.49124882340209602</v>
+        <v>0.49124882194619901</v>
       </c>
       <c r="I33">
-        <v>4.2790407504683659E-3</v>
+        <v>4.279041831223962E-3</v>
       </c>
       <c r="J33">
-        <v>-4.1226438291630238E-2</v>
+        <v>-4.1226434318130042E-2</v>
       </c>
       <c r="K33">
-        <v>0.51663095758372679</v>
+        <v>0.51663095908351231</v>
       </c>
       <c r="L33">
-        <v>3.04478541674057E-2</v>
+        <v>3.044786050457415E-2</v>
       </c>
       <c r="M33">
-        <v>-0.1516714023690903</v>
+        <v>-0.15167141156264149</v>
       </c>
       <c r="N33">
-        <v>0.51958425520759977</v>
+        <v>0.51958425348762205</v>
       </c>
       <c r="O33">
-        <v>5.2243691301747441E-2</v>
+        <v>5.2243687895735413E-2</v>
       </c>
       <c r="P33">
-        <v>-0.1649546506758251</v>
+        <v>-0.16495464546846389</v>
       </c>
       <c r="Q33">
-        <v>0.51123185443573149</v>
+        <v>0.51123185189124565</v>
       </c>
       <c r="R33">
-        <v>8.1601782384637445E-2</v>
+        <v>8.1601770269224772E-2</v>
       </c>
       <c r="S33">
-        <v>-0.12788141077995269</v>
+        <v>-0.12788140203365581</v>
       </c>
       <c r="T33">
-        <v>0.50839531697940454</v>
+        <v>0.50839532017246514</v>
       </c>
       <c r="U33">
-        <v>8.8589400372864779E-2</v>
+        <v>8.8589397543773707E-2</v>
       </c>
       <c r="V33">
-        <v>-0.1153150275457443</v>
+        <v>-0.11531504402864851</v>
       </c>
       <c r="W33">
-        <v>0.50358748021699418</v>
+        <v>0.50358748073648985</v>
       </c>
       <c r="X33">
-        <v>0.1222752070789668</v>
+        <v>0.1222752100356809</v>
       </c>
       <c r="Y33">
-        <v>-9.4274230545046689E-2</v>
+        <v>-9.4274235271546866E-2</v>
       </c>
       <c r="Z33">
-        <v>0.51702983258543855</v>
+        <v>0.51702983155541304</v>
       </c>
       <c r="AA33">
-        <v>0.14837028136149</v>
+        <v>0.1483702843113324</v>
       </c>
       <c r="AB33">
-        <v>-0.1539660306036181</v>
+        <v>-0.15396602855228861</v>
       </c>
       <c r="AC33">
-        <v>0.50812362308011239</v>
+        <v>0.50812362121397614</v>
       </c>
       <c r="AD33">
-        <v>0.29059903871317311</v>
+        <v>0.29059905508900891</v>
       </c>
       <c r="AE33">
-        <v>-0.11487675357554381</v>
+        <v>-0.11487674782874339</v>
       </c>
       <c r="AF33">
-        <v>0.49157923489052519</v>
+        <v>0.4915792289306451</v>
       </c>
       <c r="AG33">
-        <v>0.34903457744039179</v>
+        <v>0.3490345954182198</v>
       </c>
       <c r="AH33">
-        <v>-4.3309287835111752E-2</v>
+        <v>-4.3309264792086022E-2</v>
       </c>
       <c r="AI33">
-        <v>0.42845460371542771</v>
+        <v>0.42845458663294428</v>
       </c>
       <c r="AJ33">
-        <v>0.55619123631141654</v>
+        <v>0.55619128397597772</v>
       </c>
       <c r="AK33">
-        <v>0.20690325765777251</v>
+        <v>0.20690331908809079</v>
       </c>
       <c r="AL33">
-        <v>0.41483293690998307</v>
+        <v>0.41483291335118072</v>
       </c>
       <c r="AM33">
-        <v>0.57557728470460279</v>
+        <v>0.57557733301282787</v>
       </c>
       <c r="AN33">
-        <v>0.25706716129850488</v>
+        <v>0.25706724409141002</v>
       </c>
       <c r="AO33">
-        <v>0.40862003984777667</v>
+        <v>0.40862001161663752</v>
       </c>
       <c r="AP33">
-        <v>0.59878975077916963</v>
+        <v>0.59878980275500981</v>
       </c>
       <c r="AQ33">
-        <v>0.27905128009925079</v>
+        <v>0.27905137810137598</v>
       </c>
       <c r="AR33">
-        <v>0.41118011766856122</v>
+        <v>0.41118008258922623</v>
       </c>
       <c r="AS33">
-        <v>0.64512836979347576</v>
+        <v>0.64512842883887145</v>
       </c>
       <c r="AT33">
-        <v>0.26964248250227141</v>
+        <v>0.26964260500246262</v>
       </c>
       <c r="AU33">
-        <v>0.41800496465750342</v>
+        <v>0.41800492076377632</v>
       </c>
       <c r="AV33">
-        <v>0.6819351328332548</v>
+        <v>0.68193520140896058</v>
       </c>
       <c r="AW33">
-        <v>0.2451782876971271</v>
+        <v>0.24517844405572239</v>
       </c>
       <c r="AX33">
-        <v>0.42282489638831022</v>
+        <v>0.42282484467237907</v>
       </c>
       <c r="AY33">
-        <v>0.71666688209573526</v>
+        <v>0.71666695559674354</v>
       </c>
       <c r="AZ33">
-        <v>0.22753724503712161</v>
+        <v>0.22753743186638609</v>
       </c>
     </row>
     <row r="34" spans="1:52" x14ac:dyDescent="0.25">
@@ -6054,10 +6054,10 @@
         <v>54</v>
       </c>
       <c r="D34">
-        <v>0.44445866963454728</v>
+        <v>0.44445865013920688</v>
       </c>
       <c r="E34">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -6066,139 +6066,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H34">
-        <v>0.49122108915430251</v>
+        <v>0.49122108751707821</v>
       </c>
       <c r="I34">
-        <v>4.277046288847175E-3</v>
+        <v>4.2770473697607558E-3</v>
       </c>
       <c r="J34">
-        <v>-4.1074718625314442E-2</v>
+        <v>-4.1074713911075617E-2</v>
       </c>
       <c r="K34">
-        <v>0.51564082080001061</v>
+        <v>0.51564082021511914</v>
       </c>
       <c r="L34">
-        <v>3.0309042330907369E-2</v>
+        <v>3.030904863490913E-2</v>
       </c>
       <c r="M34">
-        <v>-0.14724295200378071</v>
+        <v>-0.14724295183046099</v>
       </c>
       <c r="N34">
-        <v>0.51854939250015686</v>
+        <v>0.51854939029629887</v>
       </c>
       <c r="O34">
-        <v>5.1945396054190018E-2</v>
+        <v>5.1945392668664048E-2</v>
       </c>
       <c r="P34">
-        <v>-0.1603009167988951</v>
+        <v>-0.1603009094227566</v>
       </c>
       <c r="Q34">
-        <v>0.51074233321774987</v>
+        <v>0.51074233121841528</v>
       </c>
       <c r="R34">
-        <v>8.0931589316865726E-2</v>
+        <v>8.0931577229734541E-2</v>
       </c>
       <c r="S34">
-        <v>-0.1257114164204283</v>
+        <v>-0.1257114099298571</v>
       </c>
       <c r="T34">
-        <v>0.50842564910401666</v>
+        <v>0.50842564305949767</v>
       </c>
       <c r="U34">
-        <v>8.7833284896834729E-2</v>
+        <v>8.7833282206515872E-2</v>
       </c>
       <c r="V34">
-        <v>-0.11544802432454949</v>
+        <v>-0.1154480005302935</v>
       </c>
       <c r="W34">
-        <v>0.50238105602166994</v>
+        <v>0.50238105609715444</v>
       </c>
       <c r="X34">
-        <v>0.1207537701050124</v>
+        <v>0.1207537727870529</v>
       </c>
       <c r="Y34">
-        <v>-8.9146536317300476E-2</v>
+        <v>-8.9146538787700375E-2</v>
       </c>
       <c r="Z34">
-        <v>0.51461215460054111</v>
+        <v>0.51461215469551613</v>
       </c>
       <c r="AA34">
-        <v>0.14577835016402629</v>
+        <v>0.1457783527294263</v>
       </c>
       <c r="AB34">
-        <v>-0.14307748280130311</v>
+        <v>-0.14307748570512641</v>
       </c>
       <c r="AC34">
-        <v>0.50794795933492576</v>
+        <v>0.50794795189723407</v>
       </c>
       <c r="AD34">
-        <v>0.28341146369225811</v>
+        <v>0.28341147915543119</v>
       </c>
       <c r="AE34">
-        <v>-0.1139687374578484</v>
+        <v>-0.1139687075811484</v>
       </c>
       <c r="AF34">
-        <v>0.49355031009859551</v>
+        <v>0.49355030370810282</v>
       </c>
       <c r="AG34">
-        <v>0.34158718166672802</v>
+        <v>0.34158719848134472</v>
       </c>
       <c r="AH34">
-        <v>-5.1603352150574613E-2</v>
+        <v>-5.1603327332943517E-2</v>
       </c>
       <c r="AI34">
-        <v>0.43353772374017779</v>
+        <v>0.43353770554997278</v>
       </c>
       <c r="AJ34">
-        <v>0.5536917589081003</v>
+        <v>0.5536918040780715</v>
       </c>
       <c r="AK34">
-        <v>0.1885443579908293</v>
+        <v>0.18854442430111881</v>
       </c>
       <c r="AL34">
-        <v>0.41757527057124483</v>
+        <v>0.41757524727433259</v>
       </c>
       <c r="AM34">
-        <v>0.57265951864600373</v>
+        <v>0.57265956390459827</v>
       </c>
       <c r="AN34">
-        <v>0.2472954703415618</v>
+        <v>0.2472955526713726</v>
       </c>
       <c r="AO34">
-        <v>0.40905687555455927</v>
+        <v>0.40905684732712511</v>
       </c>
       <c r="AP34">
-        <v>0.59458987731079571</v>
+        <v>0.59458992512193842</v>
       </c>
       <c r="AQ34">
-        <v>0.27760736982739709</v>
+        <v>0.2776074679277018</v>
       </c>
       <c r="AR34">
-        <v>0.40947671446480921</v>
+        <v>0.40947668150206801</v>
       </c>
       <c r="AS34">
-        <v>0.63917937877439346</v>
+        <v>0.63917943422750612</v>
       </c>
       <c r="AT34">
-        <v>0.27589761357676612</v>
+        <v>0.27589772828579578</v>
       </c>
       <c r="AU34">
-        <v>0.41506095769804008</v>
+        <v>0.41506091617856983</v>
       </c>
       <c r="AV34">
-        <v>0.67647442306818162</v>
+        <v>0.67647449108786617</v>
       </c>
       <c r="AW34">
-        <v>0.25572119833032941</v>
+        <v>0.25572134513055739</v>
       </c>
       <c r="AX34">
-        <v>0.41669677844207609</v>
+        <v>0.41669672930211299</v>
       </c>
       <c r="AY34">
-        <v>0.70704568697974235</v>
+        <v>0.70704576255391904</v>
       </c>
       <c r="AZ34">
-        <v>0.25001437574410817</v>
+        <v>0.25001455058431199</v>
       </c>
     </row>
     <row r="35" spans="1:52" x14ac:dyDescent="0.25">
@@ -6212,10 +6212,10 @@
         <v>54</v>
       </c>
       <c r="D35">
-        <v>0.44212103897975419</v>
+        <v>0.44212102451297752</v>
       </c>
       <c r="E35">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -6224,139 +6224,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H35">
-        <v>0.49071966734472511</v>
+        <v>0.49071966602224393</v>
       </c>
       <c r="I35">
-        <v>4.2764117459701536E-3</v>
+        <v>4.2764128268142354E-3</v>
       </c>
       <c r="J35">
-        <v>-3.8950254876399068E-2</v>
+        <v>-3.8950251505011899E-2</v>
       </c>
       <c r="K35">
-        <v>0.51541478831808318</v>
+        <v>0.51541478791464501</v>
       </c>
       <c r="L35">
-        <v>3.022108980082738E-2</v>
+        <v>3.0221096065626729E-2</v>
       </c>
       <c r="M35">
-        <v>-0.14619186951923069</v>
+        <v>-0.14619187018002769</v>
       </c>
       <c r="N35">
-        <v>0.51811759739626917</v>
+        <v>0.51811759528611889</v>
       </c>
       <c r="O35">
-        <v>5.1751254022393889E-2</v>
+        <v>5.1751250636233197E-2</v>
       </c>
       <c r="P35">
-        <v>-0.15832109244478121</v>
+        <v>-0.15832108548847601</v>
       </c>
       <c r="Q35">
-        <v>0.51035410029965267</v>
+        <v>0.51035409832299905</v>
       </c>
       <c r="R35">
-        <v>8.0551509568969726E-2</v>
+        <v>8.0551497389752758E-2</v>
       </c>
       <c r="S35">
-        <v>-0.12388812181905889</v>
+        <v>-0.12388811557186991</v>
       </c>
       <c r="T35">
-        <v>0.50903622376296542</v>
+        <v>0.50903622675348137</v>
       </c>
       <c r="U35">
-        <v>8.744542453443982E-2</v>
+        <v>8.7445421977263904E-2</v>
       </c>
       <c r="V35">
-        <v>-0.118058327673457</v>
+        <v>-0.1180583431945996</v>
       </c>
       <c r="W35">
-        <v>0.50344278242374108</v>
+        <v>0.50344278747470106</v>
       </c>
       <c r="X35">
-        <v>0.1199948009518418</v>
+        <v>0.11999480332922401</v>
       </c>
       <c r="Y35">
-        <v>-9.3662158009411287E-2</v>
+        <v>-9.3662182178177705E-2</v>
       </c>
       <c r="Z35">
-        <v>0.51451853342959897</v>
+        <v>0.51451852951047838</v>
       </c>
       <c r="AA35">
-        <v>0.1443712916351968</v>
+        <v>0.14437129374406951</v>
       </c>
       <c r="AB35">
-        <v>-0.1425697226495812</v>
+        <v>-0.1425697081024796</v>
       </c>
       <c r="AC35">
-        <v>0.50727257660921954</v>
+        <v>0.50727257373239154</v>
       </c>
       <c r="AD35">
-        <v>0.27912289969483139</v>
+        <v>0.27912291435765052</v>
       </c>
       <c r="AE35">
-        <v>-0.1107170773503912</v>
+        <v>-0.1107170672085586</v>
       </c>
       <c r="AF35">
-        <v>0.49183082701209452</v>
+        <v>0.49183082224867869</v>
       </c>
       <c r="AG35">
-        <v>0.33698100261944641</v>
+        <v>0.33698101857877738</v>
       </c>
       <c r="AH35">
-        <v>-4.4079106632974499E-2</v>
+        <v>-4.4079088732337082E-2</v>
       </c>
       <c r="AI35">
-        <v>0.42869847422318841</v>
+        <v>0.42869845992594402</v>
       </c>
       <c r="AJ35">
-        <v>0.5489795080566745</v>
+        <v>0.54897955191084791</v>
       </c>
       <c r="AK35">
-        <v>0.206552472395126</v>
+        <v>0.20655252346401401</v>
       </c>
       <c r="AL35">
-        <v>0.41331945193115222</v>
+        <v>0.41331943295964108</v>
       </c>
       <c r="AM35">
-        <v>0.56705080260140073</v>
+        <v>0.56705084618537338</v>
       </c>
       <c r="AN35">
-        <v>0.26260873769053</v>
+        <v>0.26260880373968332</v>
       </c>
       <c r="AO35">
-        <v>0.40559842017559089</v>
+        <v>0.40559839556329957</v>
       </c>
       <c r="AP35">
-        <v>0.58687579093622289</v>
+        <v>0.58687583615924321</v>
       </c>
       <c r="AQ35">
-        <v>0.28981143243686253</v>
+        <v>0.28981151710473169</v>
       </c>
       <c r="AR35">
-        <v>0.4056074006080489</v>
+        <v>0.40560737500972632</v>
       </c>
       <c r="AS35">
-        <v>0.62878095843534421</v>
+        <v>0.62878101162123823</v>
       </c>
       <c r="AT35">
-        <v>0.28956317209979188</v>
+        <v>0.28956326018623307</v>
       </c>
       <c r="AU35">
-        <v>0.40979386839227427</v>
+        <v>0.40979383545194781</v>
       </c>
       <c r="AV35">
-        <v>0.66507592054899145</v>
+        <v>0.66507598737171647</v>
       </c>
       <c r="AW35">
-        <v>0.27463999330015482</v>
+        <v>0.27464010813377271</v>
       </c>
       <c r="AX35">
-        <v>0.41173949573377172</v>
+        <v>0.41173945257310229</v>
       </c>
       <c r="AY35">
-        <v>0.69230549287568999</v>
+        <v>0.69230556915944153</v>
       </c>
       <c r="AZ35">
-        <v>0.26760676563451169</v>
+        <v>0.26760691747887588</v>
       </c>
     </row>
     <row r="36" spans="1:52" x14ac:dyDescent="0.25">
@@ -6370,10 +6370,10 @@
         <v>54</v>
       </c>
       <c r="D36">
-        <v>0.4349566203011388</v>
+        <v>0.43495660487307058</v>
       </c>
       <c r="E36">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -6382,139 +6382,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H36">
-        <v>0.49117238703708038</v>
+        <v>0.49117238475080849</v>
       </c>
       <c r="I36">
-        <v>4.2700312108244756E-3</v>
+        <v>4.2700322940000257E-3</v>
       </c>
       <c r="J36">
-        <v>-4.0888338554719593E-2</v>
+        <v>-4.0888331078335158E-2</v>
       </c>
       <c r="K36">
-        <v>0.51629998747460826</v>
+        <v>0.51629998625590312</v>
       </c>
       <c r="L36">
-        <v>2.9786004075662561E-2</v>
+        <v>2.9786010311872672E-2</v>
       </c>
       <c r="M36">
-        <v>-0.15019906974330749</v>
+        <v>-0.1501990668105069</v>
       </c>
       <c r="N36">
-        <v>0.51946627692433278</v>
+        <v>0.51946627511539689</v>
       </c>
       <c r="O36">
-        <v>5.0891025084559338E-2</v>
+        <v>5.089102192244932E-2</v>
       </c>
       <c r="P36">
-        <v>-0.16442235868016819</v>
+        <v>-0.16442235308362901</v>
       </c>
       <c r="Q36">
-        <v>0.51105221562021852</v>
+        <v>0.51105221506247245</v>
       </c>
       <c r="R36">
-        <v>7.8942402227826114E-2</v>
+        <v>7.8942390202142554E-2</v>
       </c>
       <c r="S36">
-        <v>-0.12709331955034059</v>
+        <v>-0.12709331958200151</v>
       </c>
       <c r="T36">
-        <v>0.50854461191671518</v>
+        <v>0.50854461306005017</v>
       </c>
       <c r="U36">
-        <v>8.5787865159294929E-2</v>
+        <v>8.5787863640840012E-2</v>
       </c>
       <c r="V36">
-        <v>-0.1160448961145298</v>
+        <v>-0.1160449037262717</v>
       </c>
       <c r="W36">
-        <v>0.50238405844104439</v>
+        <v>0.50238405517299134</v>
       </c>
       <c r="X36">
-        <v>0.11665485223806341</v>
+        <v>0.1166548543161202</v>
       </c>
       <c r="Y36">
-        <v>-8.9163496589467775E-2</v>
+        <v>-8.9163484606672158E-2</v>
       </c>
       <c r="Z36">
-        <v>0.51439617683401184</v>
+        <v>0.51439618482875038</v>
       </c>
       <c r="AA36">
-        <v>0.13874401685706339</v>
+        <v>0.13874401826593141</v>
       </c>
       <c r="AB36">
-        <v>-0.14198023397930781</v>
+        <v>-0.14198027217189019</v>
       </c>
       <c r="AC36">
-        <v>0.50846279054444965</v>
+        <v>0.5084627865734721</v>
       </c>
       <c r="AD36">
-        <v>0.26194291603370429</v>
+        <v>0.26194293154732018</v>
       </c>
       <c r="AE36">
-        <v>-0.1160937129387354</v>
+        <v>-0.11609369814962781</v>
       </c>
       <c r="AF36">
-        <v>0.49385402514583338</v>
+        <v>0.4938540213528369</v>
       </c>
       <c r="AG36">
-        <v>0.32385166863929321</v>
+        <v>0.32385168614784032</v>
       </c>
       <c r="AH36">
-        <v>-5.2889113977765821E-2</v>
+        <v>-5.2889100125996708E-2</v>
       </c>
       <c r="AI36">
-        <v>0.43412631323835688</v>
+        <v>0.43412629894010168</v>
       </c>
       <c r="AJ36">
-        <v>0.52581901912260043</v>
+        <v>0.52581906540211643</v>
       </c>
       <c r="AK36">
-        <v>0.18620915505921221</v>
+        <v>0.18620920681491701</v>
       </c>
       <c r="AL36">
-        <v>0.41930163338938292</v>
+        <v>0.41930161744631173</v>
       </c>
       <c r="AM36">
-        <v>0.5511301573220877</v>
+        <v>0.55113019960735521</v>
       </c>
       <c r="AN36">
-        <v>0.24103757684532201</v>
+        <v>0.24103763298944239</v>
       </c>
       <c r="AO36">
-        <v>0.40927828716210718</v>
+        <v>0.40927826888987112</v>
       </c>
       <c r="AP36">
-        <v>0.56629007935229447</v>
+        <v>0.5662901151941826</v>
       </c>
       <c r="AQ36">
-        <v>0.27686260342530028</v>
+        <v>0.27686266655348057</v>
       </c>
       <c r="AR36">
-        <v>0.40437924209511539</v>
+        <v>0.40437921877992572</v>
       </c>
       <c r="AS36">
-        <v>0.60623226217611559</v>
+        <v>0.60623230203581424</v>
       </c>
       <c r="AT36">
-        <v>0.29397230279253911</v>
+        <v>0.29397238264340769</v>
       </c>
       <c r="AU36">
-        <v>0.4052297780432349</v>
+        <v>0.40522975290107038</v>
       </c>
       <c r="AV36">
-        <v>0.65081137840293857</v>
+        <v>0.65081142474662079</v>
       </c>
       <c r="AW36">
-        <v>0.29091898041305581</v>
+        <v>0.29091906662425349</v>
       </c>
       <c r="AX36">
-        <v>0.40022957155273781</v>
+        <v>0.40022954178389752</v>
       </c>
       <c r="AY36">
-        <v>0.6789380197197723</v>
+        <v>0.67893807697789921</v>
       </c>
       <c r="AZ36">
-        <v>0.30799879370042921</v>
+        <v>0.30799889493794391</v>
       </c>
     </row>
     <row r="37" spans="1:52" x14ac:dyDescent="0.25">
@@ -6528,10 +6528,10 @@
         <v>54</v>
       </c>
       <c r="D37">
-        <v>0.49782313095488639</v>
+        <v>0.49782312649356131</v>
       </c>
       <c r="E37">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -6540,139 +6540,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H37">
-        <v>0.4919198086754264</v>
+        <v>0.49191980661618512</v>
       </c>
       <c r="I37">
-        <v>8.0685025790296905E-3</v>
+        <v>8.0685030507827715E-3</v>
       </c>
       <c r="J37">
-        <v>-4.4113674927854563E-2</v>
+        <v>-4.4113668352507837E-2</v>
       </c>
       <c r="K37">
-        <v>0.52190961635902278</v>
+        <v>0.52190961822159987</v>
       </c>
       <c r="L37">
-        <v>0.12995202337705769</v>
+        <v>0.12995205222296741</v>
       </c>
       <c r="M37">
-        <v>-0.175483125865217</v>
+        <v>-0.17548313661302939</v>
       </c>
       <c r="N37">
-        <v>0.50898344348839064</v>
+        <v>0.50898343168295657</v>
       </c>
       <c r="O37">
-        <v>0.15768412734458301</v>
+        <v>0.15768414533256039</v>
       </c>
       <c r="P37">
-        <v>-0.11802818912202449</v>
+        <v>-0.1180281404629052</v>
       </c>
       <c r="Q37">
-        <v>0.49776038660198918</v>
+        <v>0.49776037580138788</v>
       </c>
       <c r="R37">
-        <v>0.23329263860119631</v>
+        <v>0.23329265842170721</v>
       </c>
       <c r="S37">
-        <v>-6.9351008383463933E-2</v>
+        <v>-6.9350964261526496E-2</v>
       </c>
       <c r="T37">
-        <v>0.50084029270245767</v>
+        <v>0.50084027503170758</v>
       </c>
       <c r="U37">
-        <v>0.4019382314400769</v>
+        <v>0.40193832658703721</v>
       </c>
       <c r="V37">
-        <v>-8.2934323840841956E-2</v>
+        <v>-8.2934250818829242E-2</v>
       </c>
       <c r="W37">
-        <v>0.49828410593836642</v>
+        <v>0.49828407024335358</v>
       </c>
       <c r="X37">
-        <v>0.48591012727667832</v>
+        <v>0.48591025788149261</v>
       </c>
       <c r="Y37">
-        <v>-7.1953488757154085E-2</v>
+        <v>-7.1953337915740545E-2</v>
       </c>
       <c r="Z37">
-        <v>0.47544934867927952</v>
+        <v>0.47544928282744731</v>
       </c>
       <c r="AA37">
-        <v>0.60609429019242511</v>
+        <v>0.60609441716536372</v>
       </c>
       <c r="AB37">
-        <v>2.3893056001588989E-2</v>
+        <v>2.3893324192988959E-2</v>
       </c>
       <c r="AC37">
-        <v>0.47212695572113922</v>
+        <v>0.47212688756429327</v>
       </c>
       <c r="AD37">
-        <v>0.63298279564488447</v>
+        <v>0.63298289751112202</v>
       </c>
       <c r="AE37">
-        <v>3.7510526644607987E-2</v>
+        <v>3.7510802072269978E-2</v>
       </c>
       <c r="AF37">
-        <v>0.47113862955828317</v>
+        <v>0.47113856440527191</v>
       </c>
       <c r="AG37">
-        <v>0.67774934666832676</v>
+        <v>0.67774942729748566</v>
       </c>
       <c r="AH37">
-        <v>4.1388868770309471E-2</v>
+        <v>4.1389131695451539E-2</v>
       </c>
       <c r="AI37">
-        <v>0.46510684027846633</v>
+        <v>0.46510679392100951</v>
       </c>
       <c r="AJ37">
-        <v>0.74044223582422508</v>
+        <v>0.74044231986537079</v>
       </c>
       <c r="AK37">
-        <v>6.5777093693206404E-2</v>
+        <v>6.5777277944746138E-2</v>
       </c>
       <c r="AL37">
-        <v>0.46793742549203171</v>
+        <v>0.46793735421122878</v>
       </c>
       <c r="AM37">
-        <v>0.77853963037030383</v>
+        <v>0.77853973593764381</v>
       </c>
       <c r="AN37">
-        <v>5.4300084127794537E-2</v>
+        <v>5.4300371568012158E-2</v>
       </c>
       <c r="AO37">
-        <v>0.47701509017744198</v>
+        <v>0.47701425515929202</v>
       </c>
       <c r="AP37">
-        <v>0.81545592172788983</v>
+        <v>0.8154560385617422</v>
       </c>
       <c r="AQ37">
-        <v>1.676680796652711E-2</v>
+        <v>1.6770388045024811E-2</v>
       </c>
       <c r="AR37">
-        <v>0.46750780612300252</v>
+        <v>0.46750773923012751</v>
       </c>
       <c r="AS37">
-        <v>0.84456913233868924</v>
+        <v>0.84456926974132773</v>
       </c>
       <c r="AT37">
-        <v>5.5579052844758309E-2</v>
+        <v>5.5579319322966822E-2</v>
       </c>
       <c r="AU37">
-        <v>0.46148691751296589</v>
+        <v>0.4614868102514279</v>
       </c>
       <c r="AV37">
-        <v>0.86291946078677473</v>
+        <v>0.8629195964297609</v>
       </c>
       <c r="AW37">
-        <v>7.964499935825782E-2</v>
+        <v>7.964542489521538E-2</v>
       </c>
       <c r="AX37">
-        <v>0.45793509749039019</v>
+        <v>0.4579349467324057</v>
       </c>
       <c r="AY37">
-        <v>0.87286031609356374</v>
+        <v>0.87286044694620357</v>
       </c>
       <c r="AZ37">
-        <v>9.3786713005232128E-2</v>
+        <v>9.3787308386547863E-2</v>
       </c>
     </row>
     <row r="38" spans="1:52" x14ac:dyDescent="0.25">
@@ -6686,10 +6686,10 @@
         <v>54</v>
       </c>
       <c r="D38">
-        <v>0.44703539543075949</v>
+        <v>0.44703537880018918</v>
       </c>
       <c r="E38">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -6698,139 +6698,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H38">
-        <v>0.49140660858498891</v>
+        <v>0.49140660661784602</v>
       </c>
       <c r="I38">
-        <v>5.4126613144279689E-3</v>
+        <v>5.4126620723161656E-3</v>
       </c>
       <c r="J38">
-        <v>-4.1883431641257289E-2</v>
+        <v>-4.1883425517003303E-2</v>
       </c>
       <c r="K38">
-        <v>0.51724961450647533</v>
+        <v>0.51724961510506673</v>
       </c>
       <c r="L38">
-        <v>7.481637422829035E-2</v>
+        <v>7.4816401980715264E-2</v>
       </c>
       <c r="M38">
-        <v>-0.15445228235198319</v>
+        <v>-0.15445228749166631</v>
       </c>
       <c r="N38">
-        <v>0.51122350542524009</v>
+        <v>0.51122350205332667</v>
       </c>
       <c r="O38">
-        <v>9.8963492672560327E-2</v>
+        <v>9.896349936012494E-2</v>
       </c>
       <c r="P38">
-        <v>-0.12784625387170359</v>
+        <v>-0.12784624140588161</v>
       </c>
       <c r="Q38">
-        <v>0.49096581673241729</v>
+        <v>0.49096581828122171</v>
       </c>
       <c r="R38">
-        <v>0.23224353051383301</v>
+        <v>0.2322435501311958</v>
       </c>
       <c r="S38">
-        <v>-4.0565253910211402E-2</v>
+        <v>-4.0565262983788333E-2</v>
       </c>
       <c r="T38">
-        <v>0.47443577002934012</v>
+        <v>0.47443576454517788</v>
       </c>
       <c r="U38">
-        <v>0.41161306670956449</v>
+        <v>0.41161310216415781</v>
       </c>
       <c r="V38">
-        <v>2.8011579037234939E-2</v>
+        <v>2.8011599196157162E-2</v>
       </c>
       <c r="W38">
-        <v>0.45091442582629798</v>
+        <v>0.45091441293130968</v>
       </c>
       <c r="X38">
-        <v>0.48267073029577789</v>
+        <v>0.48267078777093309</v>
       </c>
       <c r="Y38">
-        <v>0.1221403107065583</v>
+        <v>0.1221403587938286</v>
       </c>
       <c r="Z38">
-        <v>0.4136228713402178</v>
+        <v>0.41362284912295522</v>
       </c>
       <c r="AA38">
-        <v>0.52710930842807979</v>
+        <v>0.52710937461531526</v>
       </c>
       <c r="AB38">
-        <v>0.26156140484610091</v>
+        <v>0.26156148260983081</v>
       </c>
       <c r="AC38">
-        <v>0.41761538732219028</v>
+        <v>0.41761534961611008</v>
       </c>
       <c r="AD38">
-        <v>0.57184402455458883</v>
+        <v>0.5718440947656831</v>
       </c>
       <c r="AE38">
-        <v>0.24719653218532939</v>
+        <v>0.24719666633837201</v>
       </c>
       <c r="AF38">
-        <v>0.42927386151298141</v>
+        <v>0.4292738145702818</v>
       </c>
       <c r="AG38">
-        <v>0.62171963732300439</v>
+        <v>0.62171970365655016</v>
       </c>
       <c r="AH38">
-        <v>0.20448935939244009</v>
+        <v>0.20448953139750331</v>
       </c>
       <c r="AI38">
-        <v>0.43469465607819568</v>
+        <v>0.43469460297724738</v>
       </c>
       <c r="AJ38">
-        <v>0.65131767453639178</v>
+        <v>0.651317743260722</v>
       </c>
       <c r="AK38">
-        <v>0.1839617255291692</v>
+        <v>0.18396192299791789</v>
       </c>
       <c r="AL38">
-        <v>0.43114313465675208</v>
+        <v>0.43114307521654888</v>
       </c>
       <c r="AM38">
-        <v>0.69853993506564216</v>
+        <v>0.69853999093328312</v>
       </c>
       <c r="AN38">
-        <v>0.1972729978514326</v>
+        <v>0.19727321761874961</v>
       </c>
       <c r="AO38">
-        <v>0.42994224017711091</v>
+        <v>0.4299421860654884</v>
       </c>
       <c r="AP38">
-        <v>0.73489164658082584</v>
+        <v>0.73489169708416036</v>
       </c>
       <c r="AQ38">
-        <v>0.20154332563146729</v>
+        <v>0.20154352518796581</v>
       </c>
       <c r="AR38">
-        <v>0.42019082020596749</v>
+        <v>0.42019078541071042</v>
       </c>
       <c r="AS38">
-        <v>0.77523364313075038</v>
+        <v>0.77523370118359369</v>
       </c>
       <c r="AT38">
-        <v>0.23716393375164671</v>
+        <v>0.2371640590564052</v>
       </c>
       <c r="AU38">
-        <v>0.41321159801345908</v>
+        <v>0.41321155075687921</v>
       </c>
       <c r="AV38">
-        <v>0.81173244435016378</v>
+        <v>0.81173249754808718</v>
       </c>
       <c r="AW38">
-        <v>0.26205071389851903</v>
+        <v>0.26205088198078391</v>
       </c>
       <c r="AX38">
-        <v>0.41173407890628588</v>
+        <v>0.41173402958521382</v>
       </c>
       <c r="AY38">
-        <v>0.8332971542273826</v>
+        <v>0.83329720110766881</v>
       </c>
       <c r="AZ38">
-        <v>0.2671213185713931</v>
+        <v>0.26712149378368899</v>
       </c>
     </row>
     <row r="39" spans="1:52" x14ac:dyDescent="0.25">
@@ -6844,10 +6844,10 @@
         <v>54</v>
       </c>
       <c r="D39">
-        <v>0.44541558320593488</v>
+        <v>0.44541557894798078</v>
       </c>
       <c r="E39">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -6856,139 +6856,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H39">
-        <v>0.49178728290194468</v>
+        <v>0.49178728225797502</v>
       </c>
       <c r="I39">
-        <v>5.5290654399238193E-3</v>
+        <v>5.529066213672551E-3</v>
       </c>
       <c r="J39">
-        <v>-4.3500613226694879E-2</v>
+        <v>-4.3500612753008212E-2</v>
       </c>
       <c r="K39">
-        <v>0.51664599939489464</v>
+        <v>0.51664600065427269</v>
       </c>
       <c r="L39">
-        <v>7.3821742043001404E-2</v>
+        <v>7.3821759580318891E-2</v>
       </c>
       <c r="M39">
-        <v>-0.15177463102381569</v>
+        <v>-0.1517746390815112</v>
       </c>
       <c r="N39">
-        <v>0.50950185562830241</v>
+        <v>0.50950185527471048</v>
       </c>
       <c r="O39">
-        <v>9.2845422372864306E-2</v>
+        <v>9.2845426646397167E-2</v>
       </c>
       <c r="P39">
-        <v>-0.12023340205068039</v>
+        <v>-0.1202334030118983</v>
       </c>
       <c r="Q39">
-        <v>0.48756013242173701</v>
+        <v>0.48756015319028978</v>
       </c>
       <c r="R39">
-        <v>0.197261889210572</v>
+        <v>0.19726189275823119</v>
       </c>
       <c r="S39">
-        <v>-2.59626656364405E-2</v>
+        <v>-2.5962755478086939E-2</v>
       </c>
       <c r="T39">
-        <v>0.47830999788559858</v>
+        <v>0.47831005326972659</v>
       </c>
       <c r="U39">
-        <v>0.31983891437928641</v>
+        <v>0.31983892176555712</v>
       </c>
       <c r="V39">
-        <v>1.202174813282653E-2</v>
+        <v>1.202151099338742E-2</v>
       </c>
       <c r="W39">
-        <v>0.45683451518874008</v>
+        <v>0.45683451141045389</v>
       </c>
       <c r="X39">
-        <v>0.39217555455193742</v>
+        <v>0.39217557975206119</v>
       </c>
       <c r="Y39">
-        <v>9.8782147739196469E-2</v>
+        <v>9.8782160973481442E-2</v>
       </c>
       <c r="Z39">
-        <v>0.42258843917474131</v>
+        <v>0.42258842788524631</v>
       </c>
       <c r="AA39">
-        <v>0.48278295066506371</v>
+        <v>0.48278298703210221</v>
       </c>
       <c r="AB39">
-        <v>0.22914328601230249</v>
+        <v>0.22914332537372181</v>
       </c>
       <c r="AC39">
-        <v>0.42122583718849732</v>
+        <v>0.4212258637268485</v>
       </c>
       <c r="AD39">
-        <v>0.52578976768357943</v>
+        <v>0.52578981782794854</v>
       </c>
       <c r="AE39">
-        <v>0.23388777809278949</v>
+        <v>0.23388768391744821</v>
       </c>
       <c r="AF39">
-        <v>0.41724190607971978</v>
+        <v>0.41724190697384977</v>
       </c>
       <c r="AG39">
-        <v>0.59576706862509665</v>
+        <v>0.59576712818198474</v>
       </c>
       <c r="AH39">
-        <v>0.2481730872492991</v>
+        <v>0.24817308421298481</v>
       </c>
       <c r="AI39">
-        <v>0.41643795231477992</v>
+        <v>0.41643791618596171</v>
       </c>
       <c r="AJ39">
-        <v>0.61750715884766805</v>
+        <v>0.61750722085636545</v>
       </c>
       <c r="AK39">
-        <v>0.2509705945330406</v>
+        <v>0.250970722729285</v>
       </c>
       <c r="AL39">
-        <v>0.41540675938758798</v>
+        <v>0.41540672968778869</v>
       </c>
       <c r="AM39">
-        <v>0.65154061865334145</v>
+        <v>0.6515406672903632</v>
       </c>
       <c r="AN39">
-        <v>0.25454335078558638</v>
+        <v>0.25454345632551167</v>
       </c>
       <c r="AO39">
-        <v>0.40598968838143951</v>
+        <v>0.40598964997751902</v>
       </c>
       <c r="AP39">
-        <v>0.6926819377512371</v>
+        <v>0.69268199782913553</v>
       </c>
       <c r="AQ39">
-        <v>0.28759747598024321</v>
+        <v>0.28759761015984708</v>
       </c>
       <c r="AR39">
-        <v>0.40456736366579787</v>
+        <v>0.4045673123228643</v>
       </c>
       <c r="AS39">
-        <v>0.73803395953282047</v>
+        <v>0.7380340290631997</v>
       </c>
       <c r="AT39">
-        <v>0.29235512084607462</v>
+        <v>0.29235529966105328</v>
       </c>
       <c r="AU39">
-        <v>0.40673163586730332</v>
+        <v>0.4067315828910496</v>
       </c>
       <c r="AV39">
-        <v>0.77067959067772662</v>
+        <v>0.77067966087453255</v>
       </c>
       <c r="AW39">
-        <v>0.2845620359837035</v>
+        <v>0.28456222032646761</v>
       </c>
       <c r="AX39">
-        <v>0.40433324580421642</v>
+        <v>0.40433318251718292</v>
       </c>
       <c r="AY39">
-        <v>0.80585807866695158</v>
+        <v>0.80585813968615549</v>
       </c>
       <c r="AZ39">
-        <v>0.29291609845912681</v>
+        <v>0.29291631779592481</v>
       </c>
     </row>
     <row r="40" spans="1:52" x14ac:dyDescent="0.25">
@@ -7002,10 +7002,10 @@
         <v>54</v>
       </c>
       <c r="D40">
-        <v>0.48743337502873452</v>
+        <v>0.48743335987097391</v>
       </c>
       <c r="E40">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -7014,139 +7014,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H40">
-        <v>0.49632535162293528</v>
+        <v>0.49632534880785389</v>
       </c>
       <c r="I40">
-        <v>1.395523663929743E-2</v>
+        <v>1.3955235311359121E-2</v>
       </c>
       <c r="J40">
-        <v>-6.2947686544932269E-2</v>
+        <v>-6.2947676768261893E-2</v>
       </c>
       <c r="K40">
-        <v>0.50040299419778711</v>
+        <v>0.5004029937255382</v>
       </c>
       <c r="L40">
-        <v>4.7827316566120708E-2</v>
+        <v>4.78273174361461E-2</v>
       </c>
       <c r="M40">
-        <v>-8.0590003236113344E-2</v>
+        <v>-8.0590003529615123E-2</v>
       </c>
       <c r="N40">
-        <v>0.47916986986196419</v>
+        <v>0.47916986836035069</v>
       </c>
       <c r="O40">
-        <v>0.2218584575686143</v>
+        <v>0.22185846847522639</v>
       </c>
       <c r="P40">
-        <v>8.9044704630449247E-3</v>
+        <v>8.9044743886788277E-3</v>
       </c>
       <c r="Q40">
-        <v>0.48831537854992157</v>
+        <v>0.48831538432107741</v>
       </c>
       <c r="R40">
-        <v>0.24637327984575541</v>
+        <v>0.24637326896854009</v>
       </c>
       <c r="S40">
-        <v>-2.902724034806773E-2</v>
+        <v>-2.902726708639684E-2</v>
       </c>
       <c r="T40">
-        <v>0.46082537880174362</v>
+        <v>0.46082536487436859</v>
       </c>
       <c r="U40">
-        <v>0.43809184967021081</v>
+        <v>0.43809192122148138</v>
       </c>
       <c r="V40">
-        <v>8.3371800345987013E-2</v>
+        <v>8.3371853754735284E-2</v>
       </c>
       <c r="W40">
-        <v>0.44389162383421532</v>
+        <v>0.44389160309694969</v>
       </c>
       <c r="X40">
-        <v>0.52128604752599261</v>
+        <v>0.52128609130223036</v>
       </c>
       <c r="Y40">
-        <v>0.1493010931918449</v>
+        <v>0.14930117076048419</v>
       </c>
       <c r="Z40">
-        <v>0.45251527608069569</v>
+        <v>0.45251523223355311</v>
       </c>
       <c r="AA40">
-        <v>0.57804056357203226</v>
+        <v>0.57804066366570506</v>
       </c>
       <c r="AB40">
-        <v>0.115824183607929</v>
+        <v>0.11582435386659511</v>
       </c>
       <c r="AC40">
-        <v>0.46497635724029601</v>
+        <v>0.46497629819483283</v>
       </c>
       <c r="AD40">
-        <v>0.66026220293707338</v>
+        <v>0.66026228380904006</v>
       </c>
       <c r="AE40">
-        <v>6.6237636918007894E-2</v>
+        <v>6.6237870691255293E-2</v>
       </c>
       <c r="AF40">
-        <v>0.46004473290108883</v>
+        <v>0.46004469715326562</v>
       </c>
       <c r="AG40">
-        <v>0.70764985470212993</v>
+        <v>0.70764989961892732</v>
       </c>
       <c r="AH40">
-        <v>8.5765026763350488E-2</v>
+        <v>8.5765170118046394E-2</v>
       </c>
       <c r="AI40">
-        <v>0.4467327645774139</v>
+        <v>0.44673270474666688</v>
       </c>
       <c r="AJ40">
-        <v>0.75820310832830173</v>
+        <v>0.75820317545050786</v>
       </c>
       <c r="AK40">
-        <v>0.13760204355872591</v>
+        <v>0.13760227484166729</v>
       </c>
       <c r="AL40">
-        <v>0.44418617054271647</v>
+        <v>0.44418613545459951</v>
       </c>
       <c r="AM40">
-        <v>0.78047768687647845</v>
+        <v>0.78047774761360644</v>
       </c>
       <c r="AN40">
-        <v>0.14748476775318539</v>
+        <v>0.14748490073055981</v>
       </c>
       <c r="AO40">
-        <v>0.43608835388039752</v>
+        <v>0.43608831378874519</v>
       </c>
       <c r="AP40">
-        <v>0.80564142829896812</v>
+        <v>0.80564150155006242</v>
       </c>
       <c r="AQ40">
-        <v>0.17806124672047419</v>
+        <v>0.17806139615541819</v>
       </c>
       <c r="AR40">
-        <v>0.43717019265143742</v>
+        <v>0.43717012269130501</v>
       </c>
       <c r="AS40">
-        <v>0.82783709414262341</v>
+        <v>0.82783715117017098</v>
       </c>
       <c r="AT40">
-        <v>0.1740535842982604</v>
+        <v>0.17405384701126331</v>
       </c>
       <c r="AU40">
-        <v>0.44579380711079591</v>
+        <v>0.44579370980079108</v>
       </c>
       <c r="AV40">
-        <v>0.84801566639344805</v>
+        <v>0.84801573523666807</v>
       </c>
       <c r="AW40">
-        <v>0.1410756782304598</v>
+        <v>0.14107605045315821</v>
       </c>
       <c r="AX40">
-        <v>0.46089319832122821</v>
+        <v>0.46089306842908512</v>
       </c>
       <c r="AY40">
-        <v>0.86953989128962228</v>
+        <v>0.86953993830981902</v>
       </c>
       <c r="AZ40">
-        <v>8.1874842195512582E-2</v>
+        <v>8.1875356750094927E-2</v>
       </c>
     </row>
     <row r="41" spans="1:52" x14ac:dyDescent="0.25">
@@ -7160,10 +7160,10 @@
         <v>54</v>
       </c>
       <c r="D41">
-        <v>0.49527175250890521</v>
+        <v>0.49527175092661618</v>
       </c>
       <c r="E41">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -7172,139 +7172,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H41">
-        <v>0.49511011312985459</v>
+        <v>0.49511011139463751</v>
       </c>
       <c r="I41">
-        <v>5.1478956046953288E-2</v>
+        <v>5.1478957702189021E-2</v>
       </c>
       <c r="J41">
-        <v>-5.7688305220132158E-2</v>
+        <v>-5.7688300049711122E-2</v>
       </c>
       <c r="K41">
-        <v>0.53416831469080583</v>
+        <v>0.53416831377720109</v>
       </c>
       <c r="L41">
-        <v>0.21233247630720131</v>
+        <v>0.21233248500280419</v>
       </c>
       <c r="M41">
-        <v>-0.23164583237433509</v>
+        <v>-0.23164583082977691</v>
       </c>
       <c r="N41">
-        <v>0.51722437984661973</v>
+        <v>0.51722437799343457</v>
       </c>
       <c r="O41">
-        <v>0.35294763387554989</v>
+        <v>0.35294762985493039</v>
       </c>
       <c r="P41">
-        <v>-0.15477045682602419</v>
+        <v>-0.1547704510342178</v>
       </c>
       <c r="Q41">
-        <v>0.52785258040998762</v>
+        <v>0.52785257608605274</v>
       </c>
       <c r="R41">
-        <v>0.42486543679572542</v>
+        <v>0.42486544358828299</v>
       </c>
       <c r="S41">
-        <v>-0.20298565679968489</v>
+        <v>-0.20298563941518061</v>
       </c>
       <c r="T41">
-        <v>0.51179357880375043</v>
+        <v>0.51179357949427684</v>
       </c>
       <c r="U41">
-        <v>0.51685613060563484</v>
+        <v>0.5168561218956027</v>
       </c>
       <c r="V41">
-        <v>-0.13063326587725549</v>
+        <v>-0.13063327118893919</v>
       </c>
       <c r="W41">
-        <v>0.51066567259242179</v>
+        <v>0.51066567580079814</v>
       </c>
       <c r="X41">
-        <v>0.56172233272395766</v>
+        <v>0.56172232174825221</v>
       </c>
       <c r="Y41">
-        <v>-0.12575524064482521</v>
+        <v>-0.12575525711784619</v>
       </c>
       <c r="Z41">
-        <v>0.50238423777643104</v>
+        <v>0.50238423938831889</v>
       </c>
       <c r="AA41">
-        <v>0.63701353162390761</v>
+        <v>0.63701353904512581</v>
       </c>
       <c r="AB41">
-        <v>-8.9881194713371013E-2</v>
+        <v>-8.9881203938190421E-2</v>
       </c>
       <c r="AC41">
-        <v>0.48401437857485963</v>
+        <v>0.48401437936164571</v>
       </c>
       <c r="AD41">
-        <v>0.67571913044223653</v>
+        <v>0.67571914031093827</v>
       </c>
       <c r="AE41">
-        <v>-1.1358904552366E-2</v>
+        <v>-1.135890990250751E-2</v>
       </c>
       <c r="AF41">
-        <v>0.49353824638645799</v>
+        <v>0.49353824981526778</v>
       </c>
       <c r="AG41">
-        <v>0.71086740195589093</v>
+        <v>0.71086741538781806</v>
       </c>
       <c r="AH41">
-        <v>-5.1685224126954372E-2</v>
+        <v>-5.1685240896283083E-2</v>
       </c>
       <c r="AI41">
-        <v>0.50009862705042774</v>
+        <v>0.50009862475868538</v>
       </c>
       <c r="AJ41">
-        <v>0.7524667813365058</v>
+        <v>0.75246682041064361</v>
       </c>
       <c r="AK41">
-        <v>-7.9862000623029908E-2</v>
+        <v>-7.9861992887017633E-2</v>
       </c>
       <c r="AL41">
-        <v>0.49808495445296741</v>
+        <v>0.49808494474329917</v>
       </c>
       <c r="AM41">
-        <v>0.77909964419938804</v>
+        <v>0.77909965847977447</v>
       </c>
       <c r="AN41">
-        <v>-7.1178431259326297E-2</v>
+        <v>-7.117839174226516E-2</v>
       </c>
       <c r="AO41">
-        <v>0.50500033943203682</v>
+        <v>0.50500032080682489</v>
       </c>
       <c r="AP41">
-        <v>0.816357834897663</v>
+        <v>0.81635784368175346</v>
       </c>
       <c r="AQ41">
-        <v>-0.10133037591420491</v>
+        <v>-0.1013302971467334</v>
       </c>
       <c r="AR41">
-        <v>0.517845955471122</v>
+        <v>0.51784593987113292</v>
       </c>
       <c r="AS41">
-        <v>0.84149460474403137</v>
+        <v>0.84149461102213408</v>
       </c>
       <c r="AT41">
-        <v>-0.15828359397581809</v>
+        <v>-0.15828352780028421</v>
       </c>
       <c r="AU41">
-        <v>0.51702940575244716</v>
+        <v>0.51702938490682004</v>
       </c>
       <c r="AV41">
-        <v>0.86403751279891372</v>
+        <v>0.86403751939925677</v>
       </c>
       <c r="AW41">
-        <v>-0.15462502713086229</v>
+        <v>-0.15462493611843839</v>
       </c>
       <c r="AX41">
-        <v>0.51893654189461158</v>
+        <v>0.51893652056049666</v>
       </c>
       <c r="AY41">
-        <v>0.88344656464115412</v>
+        <v>0.88344657311034713</v>
       </c>
       <c r="AZ41">
-        <v>-0.16325357741323099</v>
+        <v>-0.16325348406582599</v>
       </c>
     </row>
     <row r="42" spans="1:52" x14ac:dyDescent="0.25">
@@ -7318,10 +7318,10 @@
         <v>54</v>
       </c>
       <c r="D42">
-        <v>0.42253597756503952</v>
+        <v>0.42253598282731158</v>
       </c>
       <c r="E42">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -7330,139 +7330,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H42">
-        <v>0.48600140502236799</v>
+        <v>0.48600140450788148</v>
       </c>
       <c r="I42">
-        <v>4.6073340556472157E-2</v>
+        <v>4.6073340602729378E-2</v>
       </c>
       <c r="J42">
-        <v>-1.9069287103967009E-2</v>
+        <v>-1.9069287134258261E-2</v>
       </c>
       <c r="K42">
-        <v>0.50661525757321746</v>
+        <v>0.50661525524343731</v>
       </c>
       <c r="L42">
-        <v>9.4308105544466891E-2</v>
+        <v>9.4308098797083684E-2</v>
       </c>
       <c r="M42">
-        <v>-0.10778165519950569</v>
+        <v>-0.10778164737876821</v>
       </c>
       <c r="N42">
-        <v>0.53039151563451981</v>
+        <v>0.53039152307916682</v>
       </c>
       <c r="O42">
-        <v>0.31869009476159088</v>
+        <v>0.31869011548992959</v>
       </c>
       <c r="P42">
-        <v>-0.21488466458987551</v>
+        <v>-0.21488470160173409</v>
       </c>
       <c r="Q42">
-        <v>0.47758224751983391</v>
+        <v>0.47758224458368009</v>
       </c>
       <c r="R42">
-        <v>0.45443309267875581</v>
+        <v>0.45443310394206321</v>
       </c>
       <c r="S42">
-        <v>1.511624141421453E-2</v>
+        <v>1.5116251208281089E-2</v>
       </c>
       <c r="T42">
-        <v>0.44872758350825948</v>
+        <v>0.44872758891639519</v>
       </c>
       <c r="U42">
-        <v>0.56911282200955238</v>
+        <v>0.56911280493822214</v>
       </c>
       <c r="V42">
-        <v>0.1306858090360575</v>
+        <v>0.1306857861649858</v>
       </c>
       <c r="W42">
-        <v>0.43577907553744633</v>
+        <v>0.43577908717590053</v>
       </c>
       <c r="X42">
-        <v>0.6384772140733237</v>
+        <v>0.6384772001669744</v>
       </c>
       <c r="Y42">
-        <v>0.17993259341140319</v>
+        <v>0.17993254751958279</v>
       </c>
       <c r="Z42">
-        <v>0.40125502026986731</v>
+        <v>0.40125502614120501</v>
       </c>
       <c r="AA42">
-        <v>0.70462705293495498</v>
+        <v>0.70462704985494695</v>
       </c>
       <c r="AB42">
-        <v>0.30485572106898279</v>
+        <v>0.30485569915559652</v>
       </c>
       <c r="AC42">
-        <v>0.39894263342203851</v>
+        <v>0.39894264244690458</v>
       </c>
       <c r="AD42">
-        <v>0.74728635696623247</v>
+        <v>0.74728631794758571</v>
       </c>
       <c r="AE42">
-        <v>0.31284989829595722</v>
+        <v>0.31284986560888522</v>
       </c>
       <c r="AF42">
-        <v>0.40424457117904711</v>
+        <v>0.40424458082702069</v>
       </c>
       <c r="AG42">
-        <v>0.77023503861638976</v>
+        <v>0.77023502935852717</v>
       </c>
       <c r="AH42">
-        <v>0.29441603808694689</v>
+        <v>0.29441600261490591</v>
       </c>
       <c r="AI42">
-        <v>0.38866201897263131</v>
+        <v>0.38866202625037871</v>
       </c>
       <c r="AJ42">
-        <v>0.80512398972759358</v>
+        <v>0.80512398835231336</v>
       </c>
       <c r="AK42">
-        <v>0.34776030632228289</v>
+        <v>0.34776028031599132</v>
       </c>
       <c r="AL42">
-        <v>0.38617695684920889</v>
+        <v>0.38617696163974918</v>
       </c>
       <c r="AM42">
-        <v>0.83231970291755231</v>
+        <v>0.8323197080693876</v>
       </c>
       <c r="AN42">
-        <v>0.35605216296757869</v>
+        <v>0.35605214551071118</v>
       </c>
       <c r="AO42">
-        <v>0.38965707784482789</v>
+        <v>0.38965707684008161</v>
       </c>
       <c r="AP42">
-        <v>0.86481013440127774</v>
+        <v>0.86481014368455478</v>
       </c>
       <c r="AQ42">
-        <v>0.34436683625294201</v>
+        <v>0.34436683828112291</v>
       </c>
       <c r="AR42">
-        <v>0.39216898820542812</v>
+        <v>0.39216898519267579</v>
       </c>
       <c r="AS42">
-        <v>0.89121505461657469</v>
+        <v>0.89121506695482078</v>
       </c>
       <c r="AT42">
-        <v>0.33593094280302832</v>
+        <v>0.33593095163286663</v>
       </c>
       <c r="AU42">
-        <v>0.39181191558158168</v>
+        <v>0.39181190608309041</v>
       </c>
       <c r="AV42">
-        <v>0.89950850579567765</v>
+        <v>0.89950851953355604</v>
       </c>
       <c r="AW42">
-        <v>0.33697768078189361</v>
+        <v>0.33697771148250227</v>
       </c>
       <c r="AX42">
-        <v>0.39575228446973609</v>
+        <v>0.39575229059537159</v>
       </c>
       <c r="AY42">
-        <v>0.91740578922838001</v>
+        <v>0.91740581014035516</v>
       </c>
       <c r="AZ42">
-        <v>0.32344020538308171</v>
+        <v>0.32344018383280598</v>
       </c>
     </row>
     <row r="43" spans="1:52" x14ac:dyDescent="0.25">
@@ -7476,10 +7476,10 @@
         <v>54</v>
       </c>
       <c r="D43">
-        <v>0.44851976172644958</v>
+        <v>0.44851976491433382</v>
       </c>
       <c r="E43">
-        <v>0.48594555921399668</v>
+        <v>0.48594555869191192</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -7488,139 +7488,139 @@
         <v>-1.8778932657874E-2</v>
       </c>
       <c r="H43">
-        <v>0.48815377260013287</v>
+        <v>0.48815377147493189</v>
       </c>
       <c r="I43">
-        <v>2.8507118307790291E-2</v>
+        <v>2.850711963277908E-2</v>
       </c>
       <c r="J43">
-        <v>-2.8114284332585809E-2</v>
+        <v>-2.8114281789071729E-2</v>
       </c>
       <c r="K43">
-        <v>0.50599327566250929</v>
+        <v>0.50599327589396337</v>
       </c>
       <c r="L43">
-        <v>0.13286649259230851</v>
+        <v>0.1328664986789091</v>
       </c>
       <c r="M43">
-        <v>-0.1048979121825331</v>
+        <v>-0.1048979155820612</v>
       </c>
       <c r="N43">
-        <v>0.50092087399772034</v>
+        <v>0.50092086973424732</v>
       </c>
       <c r="O43">
-        <v>0.31074621179279999</v>
+        <v>0.31074620283564319</v>
       </c>
       <c r="P43">
-        <v>-8.3253286653680397E-2</v>
+        <v>-8.3253270603570642E-2</v>
       </c>
       <c r="Q43">
-        <v>0.47241513008970509</v>
+        <v>0.47241512954591169</v>
       </c>
       <c r="R43">
-        <v>0.44244407091100207</v>
+        <v>0.44244405836996881</v>
       </c>
       <c r="S43">
-        <v>3.6544672004669002E-2</v>
+        <v>3.6544672032378538E-2</v>
       </c>
       <c r="T43">
-        <v>0.43475859359608682</v>
+        <v>0.43475859955998147</v>
       </c>
       <c r="U43">
-        <v>0.54346723933109986</v>
+        <v>0.54346722604813869</v>
       </c>
       <c r="V43">
-        <v>0.1839319398098265</v>
+        <v>0.18393191564202299</v>
       </c>
       <c r="W43">
-        <v>0.42681391290918608</v>
+        <v>0.4268139162276729</v>
       </c>
       <c r="X43">
-        <v>0.58299744807508469</v>
+        <v>0.58299743920441149</v>
       </c>
       <c r="Y43">
-        <v>0.21354510291239551</v>
+        <v>0.21354508900784711</v>
       </c>
       <c r="Z43">
-        <v>0.41167163720432332</v>
+        <v>0.41167164133925072</v>
       </c>
       <c r="AA43">
-        <v>0.64366071036377381</v>
+        <v>0.64366070523375019</v>
       </c>
       <c r="AB43">
-        <v>0.26831085959738321</v>
+        <v>0.26831084338092742</v>
       </c>
       <c r="AC43">
-        <v>0.4096004610723129</v>
+        <v>0.4096004621123624</v>
       </c>
       <c r="AD43">
-        <v>0.69607588723516078</v>
+        <v>0.69607588741298576</v>
       </c>
       <c r="AE43">
-        <v>0.27569443569344448</v>
+        <v>0.27569443082205602</v>
       </c>
       <c r="AF43">
-        <v>0.41924294059576672</v>
+        <v>0.41924294585682959</v>
       </c>
       <c r="AG43">
-        <v>0.7528593865477613</v>
+        <v>0.75285939038831284</v>
       </c>
       <c r="AH43">
-        <v>0.2409840730559126</v>
+        <v>0.2409840502016235</v>
       </c>
       <c r="AI43">
-        <v>0.41100971559088462</v>
+        <v>0.4110097118712539</v>
       </c>
       <c r="AJ43">
-        <v>0.79504152905438774</v>
+        <v>0.79504153748585271</v>
       </c>
       <c r="AK43">
-        <v>0.27050098016592888</v>
+        <v>0.27050099171046271</v>
       </c>
       <c r="AL43">
-        <v>0.40825337835860198</v>
+        <v>0.40825337019753533</v>
       </c>
       <c r="AM43">
-        <v>0.82519696683903776</v>
+        <v>0.82519698160949151</v>
       </c>
       <c r="AN43">
-        <v>0.28011319188975842</v>
+        <v>0.28011321925171151</v>
       </c>
       <c r="AO43">
-        <v>0.41033959415354382</v>
+        <v>0.41033957996539389</v>
       </c>
       <c r="AP43">
-        <v>0.85271498755345121</v>
+        <v>0.85271500471049444</v>
       </c>
       <c r="AQ43">
-        <v>0.27275574364154909</v>
+        <v>0.27275579249228599</v>
       </c>
       <c r="AR43">
-        <v>0.4167864181533153</v>
+        <v>0.41678639796102879</v>
       </c>
       <c r="AS43">
-        <v>0.86910436658770696</v>
+        <v>0.86910438285906366</v>
       </c>
       <c r="AT43">
-        <v>0.24948657488714179</v>
+        <v>0.24948664609493729</v>
       </c>
       <c r="AU43">
-        <v>0.42448042841323108</v>
+        <v>0.42448040187337072</v>
       </c>
       <c r="AV43">
-        <v>0.88510518162256635</v>
+        <v>0.88510519860427528</v>
       </c>
       <c r="AW43">
-        <v>0.2214473741214405</v>
+        <v>0.22144746985028399</v>
       </c>
       <c r="AX43">
-        <v>0.4295930515079418</v>
+        <v>0.42959301627334312</v>
       </c>
       <c r="AY43">
-        <v>0.8986912103710879</v>
+        <v>0.89869122794951417</v>
       </c>
       <c r="AZ43">
-        <v>0.20263714220101439</v>
+        <v>0.2026372716096049</v>
       </c>
     </row>
   </sheetData>
